--- a/quizzes/sculpture-19e_20e.xlsx
+++ b/quizzes/sculpture-19e_20e.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W286"/>
+  <dimension ref="A1:W282"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="13.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -15040,7 +15040,7 @@
       <c r="C216" s="5" t="n"/>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -15058,13 +15058,13 @@
       <c r="I216" s="5" t="n"/>
       <c r="J216" s="5" t="inlineStr">
         <is>
-          <t>Ugolin et ses enfants</t>
+          <t>Adam et Ève</t>
         </is>
       </c>
       <c r="K216" s="5" t="n"/>
       <c r="L216" s="25" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4b/Rodin_et_Musee_d%27Orsay_75_%2812176538094%29.jpg/1280px-Rodin_et_Musee_d%27Orsay_75_%2812176538094%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Adam_MET_DP242351.jpg/960px-Adam_MET_DP242351.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M216" s="5" t="n"/>
@@ -15079,17 +15079,17 @@
       </c>
       <c r="S216" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T216" s="6" t="n">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="U216" s="6" t="n">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="V216" s="6" t="n">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="W216" s="6" t="n">
         <v>1</v>
@@ -15109,7 +15109,7 @@
       <c r="C217" s="5" t="n"/>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -15127,13 +15127,13 @@
       <c r="I217" s="5" t="n"/>
       <c r="J217" s="5" t="inlineStr">
         <is>
-          <t>Cybèle</t>
+          <t>"L'Homme qui marche"</t>
         </is>
       </c>
       <c r="K217" s="5" t="n"/>
       <c r="L217" s="25" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/Mus%C3%A9e_Rodin_%2837015958276%29.jpg/1280px-Mus%C3%A9e_Rodin_%2837015958276%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="M217" s="5" t="n"/>
@@ -15148,17 +15148,17 @@
       </c>
       <c r="S217" s="5" t="inlineStr">
         <is>
-          <t>Plâtre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T217" s="6" t="n">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="U217" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V217" s="6" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="W217" s="6" t="n">
         <v>1</v>
@@ -15178,7 +15178,7 @@
       <c r="C218" s="5" t="n"/>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -15196,13 +15196,13 @@
       <c r="I218" s="5" t="n"/>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>Adam et Ève</t>
+          <t>La Main de Dieu</t>
         </is>
       </c>
       <c r="K218" s="5" t="n"/>
       <c r="L218" s="25" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Adam_MET_DP242351.jpg/960px-Adam_MET_DP242351.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Auguste_rodin%2C_la_mano_di_dio%2C_1896-1908_%28fusione_del_1909-18%29.jpg/960px-Auguste_rodin%2C_la_mano_di_dio%2C_1896-1908_%28fusione_del_1909-18%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M218" s="5" t="n"/>
@@ -15221,13 +15221,13 @@
         </is>
       </c>
       <c r="T218" s="6" t="n">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="U218" s="6" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="V218" s="6" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="W218" s="6" t="n">
         <v>1</v>
@@ -15247,7 +15247,7 @@
       <c r="C219" s="5" t="n"/>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -15265,13 +15265,13 @@
       <c r="I219" s="5" t="n"/>
       <c r="J219" s="5" t="inlineStr">
         <is>
-          <t>"L'Homme qui marche"</t>
+          <t>La Cathédrale</t>
         </is>
       </c>
       <c r="K219" s="5" t="n"/>
       <c r="L219" s="25" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/aa/85_La_catedral.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="M219" s="5" t="n"/>
@@ -15286,17 +15286,17 @@
       </c>
       <c r="S219" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T219" s="6" t="n">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="U219" s="6" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="V219" s="6" t="n">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="W219" s="6" t="n">
         <v>1</v>
@@ -15305,28 +15305,28 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Medardo</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>Rosso</t>
         </is>
       </c>
       <c r="C220" s="5" t="n"/>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Collection privée</t>
         </is>
       </c>
       <c r="G220" s="5" t="n"/>
@@ -15334,13 +15334,13 @@
       <c r="I220" s="5" t="n"/>
       <c r="J220" s="5" t="inlineStr">
         <is>
-          <t>La Main de Dieu</t>
+          <t>Gavroche</t>
         </is>
       </c>
       <c r="K220" s="5" t="n"/>
-      <c r="L220" s="25" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Auguste_rodin%2C_la_mano_di_dio%2C_1896-1908_%28fusione_del_1909-18%29.jpg/960px-Auguste_rodin%2C_la_mano_di_dio%2C_1896-1908_%28fusione_del_1909-18%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L220" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Medardo_Rosso_-_Apr%C3%A8s_une_escapade_ou_Gavroche.jpg/960px-Medardo_Rosso_-_Apr%C3%A8s_une_escapade_ou_Gavroche.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="M220" s="5" t="n"/>
@@ -15355,47 +15355,47 @@
       </c>
       <c r="S220" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T220" s="6" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="U220" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="V220" s="6" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="W220" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Medardo</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>Rosso</t>
         </is>
       </c>
       <c r="C221" s="5" t="n"/>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Rovereto</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Museo d’arte moderna e contemporanea di Trento e Rovereto</t>
         </is>
       </c>
       <c r="G221" s="5" t="n"/>
@@ -15403,13 +15403,13 @@
       <c r="I221" s="5" t="n"/>
       <c r="J221" s="5" t="inlineStr">
         <is>
-          <t>La Cathédrale</t>
+          <t>Chair d'autrui</t>
         </is>
       </c>
       <c r="K221" s="5" t="n"/>
-      <c r="L221" s="25" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/aa/85_La_catedral.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+      <c r="L221" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Medardo_Rosso_%E2%80%93_Carne_altrui.tiff/lossy-page1-1280px-Medardo_Rosso_%E2%80%93_Carne_altrui.tiff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M221" s="5" t="n"/>
@@ -15424,37 +15424,37 @@
       </c>
       <c r="S221" s="5" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Cire sur plâtre</t>
         </is>
       </c>
       <c r="T221" s="6" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="U221" s="6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="V221" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="W221" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Medardo</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>Rosso</t>
         </is>
       </c>
       <c r="C222" s="5" t="n"/>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Musée du Petit Palais</t>
         </is>
       </c>
       <c r="G222" s="5" t="n"/>
@@ -15472,13 +15472,13 @@
       <c r="I222" s="5" t="n"/>
       <c r="J222" s="5" t="inlineStr">
         <is>
-          <t>La Muse Whistler nue</t>
+          <t>L'Âge d'or</t>
         </is>
       </c>
       <c r="K222" s="5" t="n"/>
-      <c r="L222" s="25" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b7/Rodin_Whistler_Muse.JPG/960px-Rodin_Whistler_Muse.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L222" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/L%27Age_d%27or%2C_PPS910.jpg/960px-L%27Age_d%27or%2C_PPS910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="M222" s="5" t="n"/>
@@ -15488,52 +15488,52 @@
       <c r="Q222" s="5" t="n"/>
       <c r="R222" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S222" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Cire sur plâtre</t>
         </is>
       </c>
       <c r="T222" s="6" t="n">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="U222" s="6" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="V222" s="6" t="n">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="W222" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Medardo</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>Rosso</t>
         </is>
       </c>
       <c r="C223" s="5" t="n"/>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Museum of Art</t>
         </is>
       </c>
       <c r="G223" s="5" t="n"/>
@@ -15541,13 +15541,13 @@
       <c r="I223" s="5" t="n"/>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>Le Secret</t>
+          <t>Enfant juif</t>
         </is>
       </c>
       <c r="K223" s="5" t="n"/>
-      <c r="L223" s="25" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Rodin_Museum_-_Joy_of_Museums_-_The_Secret.jpg/960px-Rodin_Museum_-_Joy_of_Museums_-_The_Secret.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L223" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Medardo_rosso%2C_il_ragazzo_ebreo%2C_1892_ca.jpg/960px-Medardo_rosso%2C_il_ragazzo_ebreo%2C_1892_ca.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="M223" s="5" t="n"/>
@@ -15562,296 +15562,286 @@
       </c>
       <c r="S223" s="5" t="inlineStr">
         <is>
+          <t>Cire sur plâtre</t>
+        </is>
+      </c>
+      <c r="T223" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="U223" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="V223" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="W223" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" ht="15" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>RUDE</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Musée du Louvre</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>"Buste du peintre français Jacques Louis David"</t>
+        </is>
+      </c>
+      <c r="L224" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/David_Rude_Louvre_LP1780.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+        </is>
+      </c>
+      <c r="R224" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S224" s="5" t="inlineStr">
+        <is>
           <t>Marbre</t>
         </is>
       </c>
-      <c r="T223" s="6" t="n">
-        <v>89</v>
-      </c>
-      <c r="U223" s="6" t="n">
+      <c r="T224" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="U224" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="V224" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="V223" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="W223" s="6" t="n">
+      <c r="W224" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="224" ht="15" customHeight="1">
-      <c r="A224" s="5" t="inlineStr">
-        <is>
-          <t>Medardo</t>
-        </is>
-      </c>
-      <c r="B224" s="5" t="inlineStr">
-        <is>
-          <t>Rosso</t>
-        </is>
-      </c>
-      <c r="C224" s="5" t="n"/>
-      <c r="D224" s="6" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="E224" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>Collection privée</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="n"/>
-      <c r="H224" s="5" t="n"/>
-      <c r="I224" s="5" t="n"/>
-      <c r="J224" s="5" t="inlineStr">
-        <is>
-          <t>Gavroche</t>
-        </is>
-      </c>
-      <c r="K224" s="5" t="n"/>
-      <c r="L224" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Medardo_Rosso_-_Apr%C3%A8s_une_escapade_ou_Gavroche.jpg/960px-Medardo_Rosso_-_Apr%C3%A8s_une_escapade_ou_Gavroche.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-        </is>
-      </c>
-      <c r="M224" s="5" t="n"/>
-      <c r="N224" s="5" t="n"/>
-      <c r="O224" s="5" t="n"/>
-      <c r="P224" s="5" t="n"/>
-      <c r="Q224" s="5" t="n"/>
-      <c r="R224" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S224" s="5" t="inlineStr">
+    <row r="225" ht="15" customHeight="1">
+      <c r="A225" s="19" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="B225" s="19" t="inlineStr">
+        <is>
+          <t>RUDE</t>
+        </is>
+      </c>
+      <c r="C225" s="19" t="n"/>
+      <c r="D225" s="23" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E225" s="19" t="inlineStr">
+        <is>
+          <t>Valence</t>
+        </is>
+      </c>
+      <c r="F225" s="19" t="inlineStr">
+        <is>
+          <t>Musée d’art et d’archéologie</t>
+        </is>
+      </c>
+      <c r="G225" s="19" t="n"/>
+      <c r="H225" s="19" t="n"/>
+      <c r="I225" s="19" t="n"/>
+      <c r="J225" s="19" t="inlineStr">
+        <is>
+          <t>"Jeune pêcheur napolitain jouant avec une tortue"</t>
+        </is>
+      </c>
+      <c r="K225" s="19" t="n"/>
+      <c r="L225" s="20" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg/1280px-Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M225" s="21" t="n"/>
+      <c r="N225" s="21" t="n"/>
+      <c r="O225" s="19" t="n"/>
+      <c r="P225" s="19" t="n"/>
+      <c r="Q225" s="19" t="n"/>
+      <c r="R225" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S225" s="22" t="inlineStr">
+        <is>
+          <t>Marbre pour la version originale au Louvre. Ici version en bronze.</t>
+        </is>
+      </c>
+      <c r="T225" s="23" t="n">
+        <v>82</v>
+      </c>
+      <c r="U225" s="23" t="n">
+        <v>88</v>
+      </c>
+      <c r="V225" s="23" t="n">
+        <v>48</v>
+      </c>
+      <c r="W225" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" ht="15" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>RUDE</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitan Museum of Art</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>"Tête du Guerrier"</t>
+        </is>
+      </c>
+      <c r="L226" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Head_of_the_Old_Warrior_%28T%C3%AAte_du_Guerrier%29_MET_63761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+        </is>
+      </c>
+      <c r="M226" s="4" t="inlineStr">
+        <is>
+          <t>Détail extrait du haut -relief "Départ des Volontaires"</t>
+        </is>
+      </c>
+      <c r="N226" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="R226" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S226" s="5" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T224" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="U224" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="V224" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="W224" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="225" ht="15" customHeight="1">
-      <c r="A225" s="5" t="inlineStr">
-        <is>
-          <t>Medardo</t>
-        </is>
-      </c>
-      <c r="B225" s="5" t="inlineStr">
-        <is>
-          <t>Rosso</t>
-        </is>
-      </c>
-      <c r="C225" s="5" t="n"/>
-      <c r="D225" s="6" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="E225" s="5" t="inlineStr">
-        <is>
-          <t>Rovereto</t>
-        </is>
-      </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>Museo d’arte moderna e contemporanea di Trento e Rovereto</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="n"/>
-      <c r="H225" s="5" t="n"/>
-      <c r="I225" s="5" t="n"/>
-      <c r="J225" s="5" t="inlineStr">
-        <is>
-          <t>Chair d'autrui</t>
-        </is>
-      </c>
-      <c r="K225" s="5" t="n"/>
-      <c r="L225" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Medardo_Rosso_%E2%80%93_Carne_altrui.tiff/lossy-page1-1280px-Medardo_Rosso_%E2%80%93_Carne_altrui.tiff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M225" s="5" t="n"/>
-      <c r="N225" s="5" t="n"/>
-      <c r="O225" s="5" t="n"/>
-      <c r="P225" s="5" t="n"/>
-      <c r="Q225" s="5" t="n"/>
-      <c r="R225" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S225" s="5" t="inlineStr">
-        <is>
-          <t>Cire sur plâtre</t>
-        </is>
-      </c>
-      <c r="T225" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="U225" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="V225" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="W225" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="226" ht="15" customHeight="1">
-      <c r="A226" s="5" t="inlineStr">
-        <is>
-          <t>Medardo</t>
-        </is>
-      </c>
-      <c r="B226" s="5" t="inlineStr">
-        <is>
-          <t>Rosso</t>
-        </is>
-      </c>
-      <c r="C226" s="5" t="n"/>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="E226" s="5" t="inlineStr">
+      <c r="T226" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="U226" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="V226" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="W226" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" ht="15" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>RUDE</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>1836</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="F226" s="5" t="inlineStr">
-        <is>
-          <t>Musée du Petit Palais</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="n"/>
-      <c r="H226" s="5" t="n"/>
-      <c r="I226" s="5" t="n"/>
-      <c r="J226" s="5" t="inlineStr">
-        <is>
-          <t>L'Âge d'or</t>
-        </is>
-      </c>
-      <c r="K226" s="5" t="n"/>
-      <c r="L226" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/L%27Age_d%27or%2C_PPS910.jpg/960px-L%27Age_d%27or%2C_PPS910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-        </is>
-      </c>
-      <c r="M226" s="5" t="n"/>
-      <c r="N226" s="5" t="n"/>
-      <c r="O226" s="5" t="n"/>
-      <c r="P226" s="5" t="n"/>
-      <c r="Q226" s="5" t="n"/>
-      <c r="R226" s="5" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Arc de Triomphe</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>"Le Départ des volontaires de 1792"</t>
+        </is>
+      </c>
+      <c r="L227" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M227" s="4" t="inlineStr">
+        <is>
+          <t>Façade Est du pied droit Nord de l'Arc de Triomphe</t>
+        </is>
+      </c>
+      <c r="N227" s="10" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg/1280px-Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="R227" s="5" t="inlineStr">
         <is>
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="S226" s="5" t="inlineStr">
-        <is>
-          <t>Cire sur plâtre</t>
-        </is>
-      </c>
-      <c r="T226" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="U226" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="V226" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="W226" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="227" ht="15" customHeight="1">
-      <c r="A227" s="5" t="inlineStr">
-        <is>
-          <t>Medardo</t>
-        </is>
-      </c>
-      <c r="B227" s="5" t="inlineStr">
-        <is>
-          <t>Rosso</t>
-        </is>
-      </c>
-      <c r="C227" s="5" t="n"/>
-      <c r="D227" s="6" t="inlineStr">
-        <is>
-          <t>1892</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>Museum of Art</t>
-        </is>
-      </c>
-      <c r="G227" s="5" t="n"/>
-      <c r="H227" s="5" t="n"/>
-      <c r="I227" s="5" t="n"/>
-      <c r="J227" s="5" t="inlineStr">
-        <is>
-          <t>Enfant juif</t>
-        </is>
-      </c>
-      <c r="K227" s="5" t="n"/>
-      <c r="L227" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Medardo_rosso%2C_il_ragazzo_ebreo%2C_1892_ca.jpg/960px-Medardo_rosso%2C_il_ragazzo_ebreo%2C_1892_ca.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-        </is>
-      </c>
-      <c r="M227" s="5" t="n"/>
-      <c r="N227" s="5" t="n"/>
-      <c r="O227" s="5" t="n"/>
-      <c r="P227" s="5" t="n"/>
-      <c r="Q227" s="5" t="n"/>
-      <c r="R227" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
       <c r="S227" s="5" t="inlineStr">
         <is>
-          <t>Cire sur plâtre</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T227" s="6" t="n">
-        <v>23</v>
+        <v>1160</v>
       </c>
       <c r="U227" s="6" t="n">
-        <v>18</v>
+        <v>600</v>
       </c>
       <c r="V227" s="6" t="n">
-        <v>15</v>
+        <v>263</v>
       </c>
       <c r="W227" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1">
@@ -15867,7 +15857,7 @@
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -15877,17 +15867,17 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Église de la Madeleine</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>"Buste du peintre français Jacques Louis David"</t>
+          <t>"Le Baptême du Christ"</t>
         </is>
       </c>
       <c r="L228" s="10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/David_Rude_Louvre_LP1780.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg/1280px-Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="R228" s="5" t="inlineStr">
@@ -15901,133 +15891,121 @@
         </is>
       </c>
       <c r="T228" s="6" t="n">
-        <v>96</v>
+        <v>315</v>
       </c>
       <c r="U228" s="6" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="V228" s="6" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="W228" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1">
-      <c r="A229" s="19" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>François</t>
         </is>
       </c>
-      <c r="B229" s="19" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>RUDE</t>
         </is>
       </c>
-      <c r="C229" s="19" t="n"/>
-      <c r="D229" s="23" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="E229" s="19" t="inlineStr">
-        <is>
-          <t>Valence</t>
-        </is>
-      </c>
-      <c r="F229" s="19" t="inlineStr">
-        <is>
-          <t>Musée d’art et d’archéologie</t>
-        </is>
-      </c>
-      <c r="G229" s="19" t="n"/>
-      <c r="H229" s="19" t="n"/>
-      <c r="I229" s="19" t="n"/>
-      <c r="J229" s="19" t="inlineStr">
-        <is>
-          <t>"Jeune pêcheur napolitain jouant avec une tortue"</t>
-        </is>
-      </c>
-      <c r="K229" s="19" t="n"/>
-      <c r="L229" s="20" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg/1280px-Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M229" s="21" t="n"/>
-      <c r="N229" s="21" t="n"/>
-      <c r="O229" s="19" t="n"/>
-      <c r="P229" s="19" t="n"/>
-      <c r="Q229" s="19" t="n"/>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Fixin</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Parc Noiset</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>"Napoléon s'éveillant à l'Immortalité"</t>
+        </is>
+      </c>
+      <c r="L229" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mus%C3%A9e_et_Parc_Noisot_005.jpg/1280px-Mus%C3%A9e_et_Parc_Noisot_005.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
       <c r="R229" s="5" t="inlineStr">
         <is>
           <t>Ronde-bosse</t>
         </is>
       </c>
-      <c r="S229" s="22" t="inlineStr">
-        <is>
-          <t>Marbre pour la version originale au Louvre. Ici version en bronze.</t>
-        </is>
-      </c>
-      <c r="T229" s="23" t="n">
-        <v>82</v>
-      </c>
-      <c r="U229" s="23" t="n">
-        <v>88</v>
-      </c>
-      <c r="V229" s="23" t="n">
-        <v>48</v>
+      <c r="S229" s="5" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T229" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="U229" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="V229" s="6" t="n">
+        <v>96</v>
       </c>
       <c r="W229" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="2" t="inlineStr">
+      <c r="A230" s="5" t="inlineStr">
         <is>
           <t>François</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B230" s="5" t="inlineStr">
         <is>
           <t>RUDE</t>
         </is>
       </c>
-      <c r="D230" s="6" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitan Museum of Art</t>
-        </is>
-      </c>
-      <c r="J230" s="2" t="inlineStr">
-        <is>
-          <t>"Tête du Guerrier"</t>
-        </is>
-      </c>
-      <c r="L230" s="10" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Head_of_the_Old_Warrior_%28T%C3%AAte_du_Guerrier%29_MET_63761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-        </is>
-      </c>
-      <c r="M230" s="4" t="inlineStr">
-        <is>
-          <t>Détail extrait du haut -relief "Départ des Volontaires"</t>
-        </is>
-      </c>
-      <c r="N230" s="10" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="6" t="n">
+        <v>1847</v>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Cimetière de Montmartre</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="5" t="n"/>
+      <c r="I230" s="5" t="n"/>
+      <c r="J230" s="5" t="inlineStr">
+        <is>
+          <t>"Gisant de Godefroy de Cavaignac"</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n"/>
+      <c r="L230" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Grave_of_Godefroy_Cavaignac_2012-10-09.jpg/1280px-Grave_of_Godefroy_Cavaignac_2012-10-09.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M230" s="5" t="n"/>
+      <c r="N230" s="5" t="n"/>
+      <c r="O230" s="5" t="n"/>
+      <c r="P230" s="5" t="n"/>
+      <c r="Q230" s="5" t="n"/>
       <c r="R230" s="5" t="inlineStr">
         <is>
           <t>Ronde-bosse</t>
@@ -16039,82 +16017,80 @@
         </is>
       </c>
       <c r="T230" s="6" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="U230" s="6" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="V230" s="6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="W230" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1">
-      <c r="A231" s="2" t="inlineStr">
+      <c r="A231" s="5" t="inlineStr">
         <is>
           <t>François</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B231" s="5" t="inlineStr">
         <is>
           <t>RUDE</t>
         </is>
       </c>
-      <c r="D231" s="6" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>Arc de Triomphe</t>
-        </is>
-      </c>
-      <c r="J231" s="2" t="inlineStr">
-        <is>
-          <t>"Le Départ des volontaires de 1792"</t>
-        </is>
-      </c>
-      <c r="L231" s="10" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M231" s="4" t="inlineStr">
-        <is>
-          <t>Façade Est du pied droit Nord de l'Arc de Triomphe</t>
-        </is>
-      </c>
-      <c r="N231" s="10" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg/1280px-Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="6" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Musée des Beaux-Arts</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
+      <c r="I231" s="5" t="n"/>
+      <c r="J231" s="5" t="inlineStr">
+        <is>
+          <t>"L'Amour dominateur du monde"</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/L%27Amour_dominateur_du_monde_%28Fran%C3%A7ois_Rude%29.JPG/960px-L%27Amour_dominateur_du_monde_%28Fran%C3%A7ois_Rude%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M231" s="5" t="n"/>
+      <c r="N231" s="5" t="n"/>
+      <c r="O231" s="5" t="n"/>
+      <c r="P231" s="5" t="n"/>
+      <c r="Q231" s="5" t="n"/>
       <c r="R231" s="5" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S231" s="5" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T231" s="6" t="n">
-        <v>1160</v>
+        <v>253</v>
       </c>
       <c r="U231" s="6" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="V231" s="6" t="n">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="W231" s="6" t="n">
         <v>1</v>
@@ -16123,96 +16099,93 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>SAINT-GAUDENS</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Église de la Madeleine</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>"Le Baptême du Christ"</t>
+          <t>"Monument à Robert Gould Shaw et au 54e régiment du Massachusetts"</t>
         </is>
       </c>
       <c r="L232" s="10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg/1280px-Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="R232" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S232" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T232" s="6" t="n">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="U232" s="6" t="n">
-        <v>175</v>
-      </c>
-      <c r="V232" s="6" t="n">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="W232" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>SAINT-GAUDENS</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Fixin</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>Parc Noiset</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>"Napoléon s'éveillant à l'Immortalité"</t>
+          <t>"Diane"</t>
         </is>
       </c>
       <c r="L233" s="10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mus%C3%A9e_et_Parc_Noisot_005.jpg/1280px-Mus%C3%A9e_et_Parc_Noisot_005.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ca/Diana_by_Augustus_Saint-Gaudens_01.jpg/960px-Diana_by_Augustus_Saint-Gaudens_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="R233" s="5" t="inlineStr">
@@ -16222,248 +16195,253 @@
       </c>
       <c r="S233" s="5" t="inlineStr">
         <is>
+          <t>Bronze doré</t>
+        </is>
+      </c>
+      <c r="T233" s="6" t="n">
+        <v>258</v>
+      </c>
+      <c r="U233" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="V233" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="W233" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" ht="15" customHeight="1">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Augustus</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>SAINT-GAUDENS</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Lincoln Park</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>"Abraham Lincoln"</t>
+        </is>
+      </c>
+      <c r="L234" s="10" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bb/Abraham_Lincoln_The_Man_Augustus_Saint-Gaudens_Chicago_2020-9458.jpg/960px-Abraham_Lincoln_The_Man_Augustus_Saint-Gaudens_Chicago_2020-9458.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="R234" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S234" s="5" t="inlineStr">
+        <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T233" s="6" t="n">
-        <v>215</v>
-      </c>
-      <c r="U233" s="6" t="n">
-        <v>195</v>
-      </c>
-      <c r="V233" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="W233" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" ht="15" customHeight="1">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
-        <is>
-          <t>RUDE</t>
-        </is>
-      </c>
-      <c r="C234" s="5" t="n"/>
-      <c r="D234" s="6" t="n">
-        <v>1847</v>
-      </c>
-      <c r="E234" s="5" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>Cimetière de Montmartre</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="n"/>
-      <c r="H234" s="5" t="n"/>
-      <c r="I234" s="5" t="n"/>
-      <c r="J234" s="5" t="inlineStr">
-        <is>
-          <t>"Gisant de Godefroy de Cavaignac"</t>
-        </is>
-      </c>
-      <c r="K234" s="5" t="n"/>
-      <c r="L234" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Grave_of_Godefroy_Cavaignac_2012-10-09.jpg/1280px-Grave_of_Godefroy_Cavaignac_2012-10-09.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M234" s="5" t="n"/>
-      <c r="N234" s="5" t="n"/>
-      <c r="O234" s="5" t="n"/>
-      <c r="P234" s="5" t="n"/>
-      <c r="Q234" s="5" t="n"/>
-      <c r="R234" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S234" s="5" t="inlineStr">
+      <c r="T234" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="U234" t="n">
+        <v>250</v>
+      </c>
+      <c r="V234" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="W234" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" ht="15" customHeight="1">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Augustus</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>SAINT-GAUDENS</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Merrick Park</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>"Le Puritain"</t>
+        </is>
+      </c>
+      <c r="L235" s="10" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/The_Puritan_by_Augustus_Saint-Gaudens_-_Springfield%2C_Massachusetts_-_DSC02513.JPG/960px-The_Puritan_by_Augustus_Saint-Gaudens_-_Springfield%2C_Massachusetts_-_DSC02513.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="R235" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S235" s="5" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T234" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="U234" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="V234" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="W234" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
-        <is>
-          <t>RUDE</t>
-        </is>
-      </c>
-      <c r="C235" s="5" t="n"/>
-      <c r="D235" s="6" t="n">
-        <v>1848</v>
-      </c>
-      <c r="E235" s="5" t="inlineStr">
-        <is>
-          <t>Dijon</t>
-        </is>
-      </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>Musée des Beaux-Arts</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="n"/>
-      <c r="H235" s="5" t="n"/>
-      <c r="I235" s="5" t="n"/>
-      <c r="J235" s="5" t="inlineStr">
-        <is>
-          <t>"L'Amour dominateur du monde"</t>
-        </is>
-      </c>
-      <c r="K235" s="5" t="n"/>
-      <c r="L235" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/L%27Amour_dominateur_du_monde_%28Fran%C3%A7ois_Rude%29.JPG/960px-L%27Amour_dominateur_du_monde_%28Fran%C3%A7ois_Rude%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M235" s="5" t="n"/>
-      <c r="N235" s="5" t="n"/>
-      <c r="O235" s="5" t="n"/>
-      <c r="P235" s="5" t="n"/>
-      <c r="Q235" s="5" t="n"/>
-      <c r="R235" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S235" s="5" t="inlineStr">
-        <is>
-          <t>Marbre</t>
-        </is>
-      </c>
       <c r="T235" s="6" t="n">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="U235" s="6" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="V235" s="6" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="W235" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="A236" s="2" t="inlineStr">
+      <c r="A236" s="5" t="inlineStr">
         <is>
           <t>Augustus</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B236" s="5" t="inlineStr">
         <is>
           <t>SAINT-GAUDENS</t>
         </is>
       </c>
+      <c r="C236" s="5" t="n"/>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="J236" s="2" t="inlineStr">
-        <is>
-          <t>"Monument à Robert Gould Shaw et au 54e régiment du Massachusetts"</t>
-        </is>
-      </c>
-      <c r="L236" s="10" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+          <t>1892-1903</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>Grand Army Plaza</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="5" t="n"/>
+      <c r="I236" s="5" t="n"/>
+      <c r="J236" s="5" t="inlineStr">
+        <is>
+          <t>"Monument au général Sherman"</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n"/>
+      <c r="L236" s="25" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M236" s="5" t="n"/>
+      <c r="N236" s="5" t="n"/>
+      <c r="O236" s="5" t="n"/>
+      <c r="P236" s="5" t="n"/>
+      <c r="Q236" s="5" t="n"/>
       <c r="R236" s="5" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S236" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T236" s="6" t="n">
-        <v>340</v>
+        <v>472</v>
       </c>
       <c r="U236" s="6" t="n">
-        <v>430</v>
+        <v>1295</v>
+      </c>
+      <c r="V236" s="6" t="n">
+        <v>935</v>
       </c>
       <c r="W236" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>Augustus</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>SAINT-GAUDENS</t>
-        </is>
-      </c>
-      <c r="D237" s="6" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitan Museum of Art</t>
-        </is>
-      </c>
-      <c r="J237" s="2" t="inlineStr">
-        <is>
-          <t>"Diane"</t>
-        </is>
-      </c>
-      <c r="L237" s="10" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ca/Diana_by_Augustus_Saint-Gaudens_01.jpg/960px-Diana_by_Augustus_Saint-Gaudens_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>SINDING</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="6" t="n">
+        <v>1888</v>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>Copenhague</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Ny Carlsberg Glyptotek</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="5" t="n"/>
+      <c r="I237" s="5" t="n"/>
+      <c r="J237" s="5" t="inlineStr">
+        <is>
+          <t>"Mère captive"</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n"/>
+      <c r="L237" s="8" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Captive_Mother_by_Stephan_Sinding.jpg/1280px-Captive_Mother_by_Stephan_Sinding.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M237" s="5" t="n"/>
+      <c r="N237" s="5" t="n"/>
+      <c r="O237" s="5" t="n"/>
+      <c r="P237" s="5" t="n"/>
+      <c r="Q237" s="5" t="n"/>
       <c r="R237" s="5" t="inlineStr">
         <is>
           <t>Ronde-bosse</t>
@@ -16471,58 +16449,66 @@
       </c>
       <c r="S237" s="5" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T237" s="6" t="n">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="U237" s="6" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="V237" s="6" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="W237" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>Augustus</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>SAINT-GAUDENS</t>
-        </is>
-      </c>
-      <c r="D238" s="6" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>Lincoln Park</t>
-        </is>
-      </c>
-      <c r="J238" s="2" t="inlineStr">
-        <is>
-          <t>"Abraham Lincoln"</t>
-        </is>
-      </c>
-      <c r="L238" s="10" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bb/Abraham_Lincoln_The_Man_Augustus_Saint-Gaudens_Chicago_2020-9458.jpg/960px-Abraham_Lincoln_The_Man_Augustus_Saint-Gaudens_Chicago_2020-9458.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>SINDING</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="6" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>Copenhague</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>Ny Carlsberg Glyptotek</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
+      <c r="I238" s="5" t="n"/>
+      <c r="J238" s="5" t="inlineStr">
+        <is>
+          <t>L'Esclave</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n"/>
+      <c r="L238" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ac/Stephan_Sinding-The_slave-Ny_Carlsberg_Glyptotek.jpg/1280px-Stephan_Sinding-The_slave-Ny_Carlsberg_Glyptotek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M238" s="5" t="n"/>
+      <c r="N238" s="5" t="n"/>
+      <c r="O238" s="5" t="n"/>
+      <c r="P238" s="5" t="n"/>
+      <c r="Q238" s="5" t="n"/>
       <c r="R238" s="5" t="inlineStr">
         <is>
           <t>Ronde-bosse</t>
@@ -16530,58 +16516,66 @@
       </c>
       <c r="S238" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T238" s="6" t="n">
-        <v>366</v>
-      </c>
-      <c r="U238" t="n">
-        <v>250</v>
+        <v>132</v>
+      </c>
+      <c r="U238" s="6" t="n">
+        <v>100</v>
       </c>
       <c r="V238" s="6" t="n">
-        <v>230</v>
+        <v>129</v>
       </c>
       <c r="W238" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>Augustus</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>SAINT-GAUDENS</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>Springfield</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>Merrick Park</t>
-        </is>
-      </c>
-      <c r="J239" s="2" t="inlineStr">
-        <is>
-          <t>"Le Puritain"</t>
-        </is>
-      </c>
-      <c r="L239" s="10" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/The_Puritan_by_Augustus_Saint-Gaudens_-_Springfield%2C_Massachusetts_-_DSC02513.JPG/960px-The_Puritan_by_Augustus_Saint-Gaudens_-_Springfield%2C_Massachusetts_-_DSC02513.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>SINDING</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="6" t="n">
+        <v>1899</v>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Place Studenterluden</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
+      <c r="J239" s="5" t="inlineStr">
+        <is>
+          <t>Monument à Henrik Ibsen</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n"/>
+      <c r="L239" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Ibsen_sculpture_Nationaltheatret.jpg/960px-Ibsen_sculpture_Nationaltheatret.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M239" s="5" t="n"/>
+      <c r="N239" s="5" t="n"/>
+      <c r="O239" s="5" t="n"/>
+      <c r="P239" s="5" t="n"/>
+      <c r="Q239" s="5" t="n"/>
       <c r="R239" s="5" t="inlineStr">
         <is>
           <t>Ronde-bosse</t>
@@ -16593,13 +16587,13 @@
         </is>
       </c>
       <c r="T239" s="6" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="U239" s="6" t="n">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="V239" s="6" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="W239" s="6" t="n">
         <v>3</v>
@@ -16608,28 +16602,26 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Stephan</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>SAINT-GAUDENS</t>
+          <t>SINDING</t>
         </is>
       </c>
       <c r="C240" s="5" t="n"/>
-      <c r="D240" s="6" t="inlineStr">
-        <is>
-          <t>1892-1903</t>
-        </is>
+      <c r="D240" s="6" t="n">
+        <v>1891</v>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Grand Army Plaza</t>
+          <t>Ny Carlsberg Glyptotek</t>
         </is>
       </c>
       <c r="G240" s="5" t="n"/>
@@ -16637,13 +16629,13 @@
       <c r="I240" s="5" t="n"/>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>"Monument au général Sherman"</t>
+          <t>Deux êtres humains</t>
         </is>
       </c>
       <c r="K240" s="5" t="n"/>
-      <c r="L240" s="25" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L240" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Stephan_Sinding_-_Un_homme_et_une_femme.jpg/1280px-Stephan_Sinding_-_Un_homme_et_une_femme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M240" s="5" t="n"/>
@@ -16658,17 +16650,17 @@
       </c>
       <c r="S240" s="5" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T240" s="6" t="n">
-        <v>472</v>
+        <v>107</v>
       </c>
       <c r="U240" s="6" t="n">
-        <v>1295</v>
+        <v>135</v>
       </c>
       <c r="V240" s="6" t="n">
-        <v>935</v>
+        <v>91</v>
       </c>
       <c r="W240" s="6" t="n">
         <v>3</v>
@@ -16677,26 +16669,28 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>Lorado</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>SINDING</t>
+          <t>TAFT</t>
         </is>
       </c>
       <c r="C241" s="5" t="n"/>
-      <c r="D241" s="6" t="n">
-        <v>1888</v>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>1920-1922</t>
+        </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Ny Carlsberg Glyptotek</t>
+          <t>Washington Park</t>
         </is>
       </c>
       <c r="G241" s="5" t="n"/>
@@ -16704,13 +16698,13 @@
       <c r="I241" s="5" t="n"/>
       <c r="J241" s="5" t="inlineStr">
         <is>
-          <t>"Mère captive"</t>
+          <t>La Fontaine du Temps</t>
         </is>
       </c>
       <c r="K241" s="5" t="n"/>
-      <c r="L241" s="8" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Captive_Mother_by_Stephan_Sinding.jpg/1280px-Captive_Mother_by_Stephan_Sinding.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L241" s="25" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="M241" s="5" t="n"/>
@@ -16720,22 +16714,22 @@
       <c r="Q241" s="5" t="n"/>
       <c r="R241" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S241" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Béton</t>
         </is>
       </c>
       <c r="T241" s="6" t="n">
-        <v>130</v>
+        <v>730</v>
       </c>
       <c r="U241" s="6" t="n">
-        <v>160</v>
+        <v>3866</v>
       </c>
       <c r="V241" s="6" t="n">
-        <v>110</v>
+        <v>716</v>
       </c>
       <c r="W241" s="6" t="n">
         <v>3</v>
@@ -16744,40 +16738,46 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>Lorado</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>SINDING</t>
+          <t>TAFT</t>
         </is>
       </c>
       <c r="C242" s="5" t="n"/>
-      <c r="D242" s="6" t="n">
-        <v>1878</v>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Ny Carlsberg Glyptotek</t>
+          <t>Art Institute of Chicago</t>
         </is>
       </c>
       <c r="G242" s="5" t="n"/>
-      <c r="H242" s="5" t="n"/>
+      <c r="H242" s="5" t="inlineStr">
+        <is>
+          <t>South Plaza</t>
+        </is>
+      </c>
       <c r="I242" s="5" t="n"/>
       <c r="J242" s="5" t="inlineStr">
         <is>
-          <t>L'Esclave</t>
+          <t>Statues de la Fontaine des Grands Lacs</t>
         </is>
       </c>
       <c r="K242" s="5" t="n"/>
       <c r="L242" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ac/Stephan_Sinding-The_slave-Ny_Carlsberg_Glyptotek.jpg/1280px-Stephan_Sinding-The_slave-Ny_Carlsberg_Glyptotek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M242" s="5" t="n"/>
@@ -16787,22 +16787,22 @@
       <c r="Q242" s="5" t="n"/>
       <c r="R242" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S242" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T242" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="U242" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="V242" s="6" t="n">
-        <v>129</v>
+        <v>670</v>
+      </c>
+      <c r="U242" t="n">
+        <v>500</v>
+      </c>
+      <c r="V242" t="n">
+        <v>500</v>
       </c>
       <c r="W242" s="6" t="n">
         <v>3</v>
@@ -16811,26 +16811,28 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>Lorado</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>SINDING</t>
+          <t>TAFT</t>
         </is>
       </c>
       <c r="C243" s="5" t="n"/>
-      <c r="D243" s="6" t="n">
-        <v>1899</v>
+      <c r="D243" s="6" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>Oslo</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Place Studenterluden</t>
+          <t>Lowden State Park</t>
         </is>
       </c>
       <c r="G243" s="5" t="n"/>
@@ -16838,13 +16840,13 @@
       <c r="I243" s="5" t="n"/>
       <c r="J243" s="5" t="inlineStr">
         <is>
-          <t>Monument à Henrik Ibsen</t>
+          <t>Statue de Black Hawk</t>
         </is>
       </c>
       <c r="K243" s="5" t="n"/>
       <c r="L243" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Ibsen_sculpture_Nationaltheatret.jpg/960px-Ibsen_sculpture_Nationaltheatret.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/Black_Hawk_by_Lorado_Taft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="M243" s="5" t="n"/>
@@ -16859,17 +16861,17 @@
       </c>
       <c r="S243" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Béton</t>
         </is>
       </c>
       <c r="T243" s="6" t="n">
-        <v>280</v>
+        <v>1463</v>
       </c>
       <c r="U243" s="6" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="V243" s="6" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="W243" s="6" t="n">
         <v>3</v>
@@ -16878,26 +16880,28 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>Lorado</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>SINDING</t>
+          <t>TAFT</t>
         </is>
       </c>
       <c r="C244" s="5" t="n"/>
-      <c r="D244" s="6" t="n">
-        <v>1891</v>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Ny Carlsberg Glyptotek</t>
+          <t>Carle Park</t>
         </is>
       </c>
       <c r="G244" s="5" t="n"/>
@@ -16905,13 +16909,13 @@
       <c r="I244" s="5" t="n"/>
       <c r="J244" s="5" t="inlineStr">
         <is>
-          <t>Deux êtres humains</t>
+          <t>Lincoln l'Avocat</t>
         </is>
       </c>
       <c r="K244" s="5" t="n"/>
       <c r="L244" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Stephan_Sinding_-_Un_homme_et_une_femme.jpg/1280px-Stephan_Sinding_-_Un_homme_et_une_femme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/31/Lincoln_by_Taft.jpg/960px-Lincoln_by_Taft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M244" s="5" t="n"/>
@@ -16926,17 +16930,17 @@
       </c>
       <c r="S244" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T244" s="6" t="n">
-        <v>107</v>
+        <v>305</v>
       </c>
       <c r="U244" s="6" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="V244" s="6" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="W244" s="6" t="n">
         <v>3</v>
@@ -16945,28 +16949,26 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>Lorado</t>
+          <t>Hamo</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>TAFT</t>
+          <t>THORNYCROFT</t>
         </is>
       </c>
       <c r="C245" s="5" t="n"/>
-      <c r="D245" s="6" t="inlineStr">
-        <is>
-          <t>1920-1922</t>
-        </is>
+      <c r="D245" s="6" t="n">
+        <v>1881</v>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Washington Park</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="G245" s="5" t="n"/>
@@ -16974,13 +16976,13 @@
       <c r="I245" s="5" t="n"/>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>La Fontaine du Temps</t>
+          <t>"Teucer"</t>
         </is>
       </c>
       <c r="K245" s="5" t="n"/>
-      <c r="L245" s="25" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+      <c r="L245" s="8" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Hamo_Thornycroft-Teucer-07211.jpg/960px-Hamo_Thornycroft-Teucer-07211.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M245" s="5" t="n"/>
@@ -16990,22 +16992,22 @@
       <c r="Q245" s="5" t="n"/>
       <c r="R245" s="5" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S245" s="5" t="inlineStr">
         <is>
-          <t>Béton</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T245" s="6" t="n">
-        <v>730</v>
+        <v>241</v>
       </c>
       <c r="U245" s="6" t="n">
-        <v>3866</v>
+        <v>151</v>
       </c>
       <c r="V245" s="6" t="n">
-        <v>716</v>
+        <v>66</v>
       </c>
       <c r="W245" s="6" t="n">
         <v>3</v>
@@ -17014,46 +17016,40 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>Lorado</t>
+          <t>Hamo</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>TAFT</t>
+          <t>THORNYCROFT</t>
         </is>
       </c>
       <c r="C246" s="5" t="n"/>
-      <c r="D246" s="6" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
+      <c r="D246" s="6" t="n">
+        <v>1878</v>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Art Institute of Chicago</t>
+          <t>Victoria and Albert Museum</t>
         </is>
       </c>
       <c r="G246" s="5" t="n"/>
-      <c r="H246" s="5" t="inlineStr">
-        <is>
-          <t>South Plaza</t>
-        </is>
-      </c>
+      <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="n"/>
       <c r="J246" s="5" t="inlineStr">
         <is>
-          <t>Statues de la Fontaine des Grands Lacs</t>
+          <t>La femme de Loth</t>
         </is>
       </c>
       <c r="K246" s="5" t="n"/>
       <c r="L246" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Lot%27s_Wife_by_Hamo_Thornycroft%2C_Victoria_and_Albert_Museum.jpg/500px-Lot%27s_Wife_by_Hamo_Thornycroft%2C_Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M246" s="5" t="n"/>
@@ -17063,22 +17059,22 @@
       <c r="Q246" s="5" t="n"/>
       <c r="R246" s="5" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S246" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T246" s="6" t="n">
-        <v>670</v>
-      </c>
-      <c r="U246" t="n">
-        <v>500</v>
-      </c>
-      <c r="V246" t="n">
-        <v>500</v>
+        <v>175</v>
+      </c>
+      <c r="U246" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="V246" s="6" t="n">
+        <v>60</v>
       </c>
       <c r="W246" s="6" t="n">
         <v>3</v>
@@ -17087,28 +17083,26 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>Lorado</t>
+          <t>Hamo</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>TAFT</t>
+          <t>THORNYCROFT</t>
         </is>
       </c>
       <c r="C247" s="5" t="n"/>
-      <c r="D247" s="6" t="inlineStr">
-        <is>
-          <t>1911</t>
-        </is>
+      <c r="D247" s="6" t="n">
+        <v>1886</v>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Lowden State Park</t>
+          <t>Kew Garden</t>
         </is>
       </c>
       <c r="G247" s="5" t="n"/>
@@ -17116,13 +17110,13 @@
       <c r="I247" s="5" t="n"/>
       <c r="J247" s="5" t="inlineStr">
         <is>
-          <t>Statue de Black Hawk</t>
+          <t>Un Semeur</t>
         </is>
       </c>
       <c r="K247" s="5" t="n"/>
       <c r="L247" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/Black_Hawk_by_Lorado_Taft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Thornycroft_-_A_sower_40895.JPG/960px-Thornycroft_-_A_sower_40895.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M247" s="5" t="n"/>
@@ -17137,17 +17131,17 @@
       </c>
       <c r="S247" s="5" t="inlineStr">
         <is>
-          <t>Béton</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T247" s="6" t="n">
-        <v>1463</v>
+        <v>195</v>
       </c>
       <c r="U247" s="6" t="n">
-        <v>440</v>
+        <v>90</v>
       </c>
       <c r="V247" s="6" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="W247" s="6" t="n">
         <v>3</v>
@@ -17156,28 +17150,26 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>Lorado</t>
+          <t>Hamo</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>TAFT</t>
+          <t>THORNYCROFT</t>
         </is>
       </c>
       <c r="C248" s="5" t="n"/>
-      <c r="D248" s="6" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
+      <c r="D248" s="6" t="n">
+        <v>1888</v>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Carle Park</t>
+          <t>Victoria Embankment Gardens</t>
         </is>
       </c>
       <c r="G248" s="5" t="n"/>
@@ -17185,13 +17177,13 @@
       <c r="I248" s="5" t="n"/>
       <c r="J248" s="5" t="inlineStr">
         <is>
-          <t>Lincoln l'Avocat</t>
+          <t>Monument au Général Gordon</t>
         </is>
       </c>
       <c r="K248" s="5" t="n"/>
       <c r="L248" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/31/Lincoln_by_Taft.jpg/960px-Lincoln_by_Taft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/General_Charles_George_Gordon_statue%2C_Embankment%2C_London_%282%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="M248" s="5" t="n"/>
@@ -17210,13 +17202,13 @@
         </is>
       </c>
       <c r="T248" s="6" t="n">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="U248" s="6" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="V248" s="6" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="W248" s="6" t="n">
         <v>3</v>
@@ -17225,26 +17217,28 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Hamo</t>
+          <t>Bertel</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>THORNYCROFT</t>
+          <t>THORVALDSEN</t>
         </is>
       </c>
       <c r="C249" s="5" t="n"/>
-      <c r="D249" s="6" t="n">
-        <v>1881</v>
+      <c r="D249" s="6" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Musée Thorvaldsen</t>
         </is>
       </c>
       <c r="G249" s="5" t="n"/>
@@ -17252,13 +17246,13 @@
       <c r="I249" s="5" t="n"/>
       <c r="J249" s="5" t="inlineStr">
         <is>
-          <t>"Teucer"</t>
+          <t>"Jason à la Toison d'or"</t>
         </is>
       </c>
       <c r="K249" s="5" t="n"/>
       <c r="L249" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Hamo_Thornycroft-Teucer-07211.jpg/960px-Hamo_Thornycroft-Teucer-07211.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg/960px-Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M249" s="5" t="n"/>
@@ -17273,45 +17267,47 @@
       </c>
       <c r="S249" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T249" s="6" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U249" s="6" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="V249" s="6" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="W249" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>Hamo</t>
+          <t>Bertel</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>THORNYCROFT</t>
+          <t>THORVALDSEN</t>
         </is>
       </c>
       <c r="C250" s="5" t="n"/>
-      <c r="D250" s="6" t="n">
-        <v>1878</v>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Victoria and Albert Museum</t>
+          <t>Cathédrale Notre-Dame</t>
         </is>
       </c>
       <c r="G250" s="5" t="n"/>
@@ -17319,13 +17315,13 @@
       <c r="I250" s="5" t="n"/>
       <c r="J250" s="5" t="inlineStr">
         <is>
-          <t>La femme de Loth</t>
+          <t>"Le Christ"</t>
         </is>
       </c>
       <c r="K250" s="5" t="n"/>
       <c r="L250" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Lot%27s_Wife_by_Hamo_Thornycroft%2C_Victoria_and_Albert_Museum.jpg/500px-Lot%27s_Wife_by_Hamo_Thornycroft%2C_Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M250" s="5" t="n"/>
@@ -17344,41 +17340,43 @@
         </is>
       </c>
       <c r="T250" s="6" t="n">
-        <v>175</v>
+        <v>345</v>
       </c>
       <c r="U250" s="6" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="V250" s="6" t="n">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="W250" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>Hamo</t>
+          <t>Bertel</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>THORNYCROFT</t>
+          <t>THORVALDSEN</t>
         </is>
       </c>
       <c r="C251" s="5" t="n"/>
-      <c r="D251" s="6" t="n">
-        <v>1886</v>
+      <c r="D251" s="6" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Lucerne</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Kew Garden</t>
+          <t>Monument du Lion</t>
         </is>
       </c>
       <c r="G251" s="5" t="n"/>
@@ -17386,13 +17384,13 @@
       <c r="I251" s="5" t="n"/>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>Un Semeur</t>
+          <t>"Le Lion de Lucerne"</t>
         </is>
       </c>
       <c r="K251" s="5" t="n"/>
       <c r="L251" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Thornycroft_-_A_sower_40895.JPG/960px-Thornycroft_-_A_sower_40895.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Luzern_asv2022-10_L%C3%B6wendenkmal_img2.jpg/1280px-Luzern_asv2022-10_L%C3%B6wendenkmal_img2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M251" s="5" t="n"/>
@@ -17402,50 +17400,52 @@
       <c r="Q251" s="5" t="n"/>
       <c r="R251" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S251" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Roche (grès)</t>
         </is>
       </c>
       <c r="T251" s="6" t="n">
-        <v>195</v>
+        <v>600</v>
       </c>
       <c r="U251" s="6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="V251" s="6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="W251" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>Hamo</t>
+          <t>Bertel</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>THORNYCROFT</t>
+          <t>THORVALDSEN</t>
         </is>
       </c>
       <c r="C252" s="5" t="n"/>
-      <c r="D252" s="6" t="n">
-        <v>1888</v>
+      <c r="D252" s="6" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Victoria Embankment Gardens</t>
+          <t>Musée Thorvaldsen</t>
         </is>
       </c>
       <c r="G252" s="5" t="n"/>
@@ -17453,13 +17453,13 @@
       <c r="I252" s="5" t="n"/>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>Monument au Général Gordon</t>
+          <t>"Ganymède et l'Aigle de Jupiter"</t>
         </is>
       </c>
       <c r="K252" s="5" t="n"/>
       <c r="L252" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/General_Charles_George_Gordon_statue%2C_Embankment%2C_London_%282%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Ganymede_Waters_Zeus_as_an_Eagle_by_Thorvaldsen.jpg/1280px-Ganymede_Waters_Zeus_as_an_Eagle_by_Thorvaldsen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M252" s="5" t="n"/>
@@ -17469,25 +17469,25 @@
       <c r="Q252" s="5" t="n"/>
       <c r="R252" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Ensemble en ronde-bosse</t>
         </is>
       </c>
       <c r="S252" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T252" s="6" t="n">
-        <v>325</v>
+        <v>93</v>
       </c>
       <c r="U252" s="6" t="n">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="V252" s="6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="W252" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1">
@@ -17504,17 +17504,17 @@
       <c r="C253" s="5" t="n"/>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Varsovie</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Musée Thorvaldsen</t>
+          <t>Place des Églises</t>
         </is>
       </c>
       <c r="G253" s="5" t="n"/>
@@ -17522,13 +17522,13 @@
       <c r="I253" s="5" t="n"/>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>"Jason à la Toison d'or"</t>
+          <t>"Monument à Nicolas Copernic"</t>
         </is>
       </c>
       <c r="K253" s="5" t="n"/>
       <c r="L253" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg/960px-Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d3/Copernicus_by_Thorwaldsen_Warsaw_02.jpg/960px-Copernicus_by_Thorwaldsen_Warsaw_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M253" s="5" t="n"/>
@@ -17543,17 +17543,17 @@
       </c>
       <c r="S253" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T253" s="6" t="n">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="U253" s="6" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="V253" s="6" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="W253" s="6" t="n">
         <v>1</v>
@@ -17573,17 +17573,17 @@
       <c r="C254" s="5" t="n"/>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Varsovie</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Cathédrale Notre-Dame</t>
+          <t>Palais Koniecpolski</t>
         </is>
       </c>
       <c r="G254" s="5" t="n"/>
@@ -17591,13 +17591,13 @@
       <c r="I254" s="5" t="n"/>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>"Le Christ"</t>
+          <t>"Monument au prince Józef Poniatowski"</t>
         </is>
       </c>
       <c r="K254" s="5" t="n"/>
       <c r="L254" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M254" s="5" t="n"/>
@@ -17612,17 +17612,17 @@
       </c>
       <c r="S254" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T254" s="6" t="n">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="U254" s="6" t="n">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="V254" s="6" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="W254" s="6" t="n">
         <v>1</v>
@@ -17642,17 +17642,17 @@
       <c r="C255" s="5" t="n"/>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1813-1816</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>Lucerne</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Monument du Lion</t>
+          <t>Musée Thorvaldsen</t>
         </is>
       </c>
       <c r="G255" s="5" t="n"/>
@@ -17660,13 +17660,13 @@
       <c r="I255" s="5" t="n"/>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>"Le Lion de Lucerne"</t>
+          <t>"Vénus à la pomme"</t>
         </is>
       </c>
       <c r="K255" s="5" t="n"/>
       <c r="L255" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Luzern_asv2022-10_L%C3%B6wendenkmal_img2.jpg/1280px-Luzern_asv2022-10_L%C3%B6wendenkmal_img2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Thorvaldsens_Venus.jpg/960px-Thorvaldsens_Venus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M255" s="5" t="n"/>
@@ -17676,121 +17676,117 @@
       <c r="Q255" s="5" t="n"/>
       <c r="R255" s="5" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S255" s="5" t="inlineStr">
         <is>
-          <t>Roche (grès)</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T255" s="6" t="n">
-        <v>600</v>
+        <v>161</v>
       </c>
       <c r="U255" s="6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="V255" s="6" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="W255" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="5" t="inlineStr">
+      <c r="A256" s="27" t="inlineStr">
         <is>
           <t>Bertel</t>
         </is>
       </c>
-      <c r="B256" s="5" t="inlineStr">
+      <c r="B256" s="27" t="inlineStr">
         <is>
           <t>THORVALDSEN</t>
         </is>
       </c>
-      <c r="C256" s="5" t="n"/>
-      <c r="D256" s="6" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="E256" s="5" t="inlineStr">
-        <is>
-          <t>Copenhague</t>
-        </is>
-      </c>
-      <c r="F256" s="5" t="inlineStr">
-        <is>
-          <t>Musée Thorvaldsen</t>
-        </is>
-      </c>
-      <c r="G256" s="5" t="n"/>
-      <c r="H256" s="5" t="n"/>
-      <c r="I256" s="5" t="n"/>
-      <c r="J256" s="5" t="inlineStr">
-        <is>
-          <t>"Ganymède et l'Aigle de Jupiter"</t>
-        </is>
-      </c>
-      <c r="K256" s="5" t="n"/>
-      <c r="L256" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Ganymede_Waters_Zeus_as_an_Eagle_by_Thorvaldsen.jpg/1280px-Ganymede_Waters_Zeus_as_an_Eagle_by_Thorvaldsen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M256" s="5" t="n"/>
-      <c r="N256" s="5" t="n"/>
-      <c r="O256" s="5" t="n"/>
-      <c r="P256" s="5" t="n"/>
-      <c r="Q256" s="5" t="n"/>
-      <c r="R256" s="5" t="inlineStr">
-        <is>
-          <t>Ensemble en ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S256" s="5" t="inlineStr">
+      <c r="C256" s="27" t="n"/>
+      <c r="D256" s="37" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E256" s="27" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F256" s="27" t="inlineStr">
+        <is>
+          <t>Basilique Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="G256" s="27" t="n"/>
+      <c r="H256" s="27" t="n"/>
+      <c r="I256" s="27" t="n"/>
+      <c r="J256" s="27" t="inlineStr">
+        <is>
+          <t>"Monument funéraire du pape Pie VII"</t>
+        </is>
+      </c>
+      <c r="K256" s="27" t="n"/>
+      <c r="L256" s="36" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/99/0_Tombeau_du_pape_Pie_VII_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Tombeau_du_pape_Pie_VII_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M256" s="27" t="n"/>
+      <c r="N256" s="27" t="n"/>
+      <c r="O256" s="27" t="n"/>
+      <c r="P256" s="27" t="n"/>
+      <c r="Q256" s="27" t="n"/>
+      <c r="R256" s="27" t="inlineStr">
+        <is>
+          <t>Monument funéraire avec ensemble en ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S256" s="27" t="inlineStr">
         <is>
           <t>Marbre</t>
         </is>
       </c>
-      <c r="T256" s="6" t="n">
-        <v>93</v>
-      </c>
-      <c r="U256" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="V256" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="W256" s="6" t="n">
+      <c r="T256" s="37" t="n">
+        <v>700</v>
+      </c>
+      <c r="U256" s="37" t="n">
+        <v>450</v>
+      </c>
+      <c r="V256" s="37" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W256" s="37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>Bertel</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>THORVALDSEN</t>
+          <t>TROUBETZKOY</t>
         </is>
       </c>
       <c r="C257" s="5" t="n"/>
-      <c r="D257" s="6" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
+      <c r="D257" s="6" t="n">
+        <v>1900</v>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>Varsovie</t>
+          <t>Saint Petersbourg</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>Place des Églises</t>
+          <t>Musée Russe</t>
         </is>
       </c>
       <c r="G257" s="5" t="n"/>
@@ -17798,13 +17794,13 @@
       <c r="I257" s="5" t="n"/>
       <c r="J257" s="5" t="inlineStr">
         <is>
-          <t>"Monument à Nicolas Copernic"</t>
+          <t>"Les Enfants"</t>
         </is>
       </c>
       <c r="K257" s="5" t="n"/>
       <c r="L257" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d3/Copernicus_by_Thorwaldsen_Warsaw_02.jpg/960px-Copernicus_by_Thorwaldsen_Warsaw_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Trubetzkoy_Children.jpg/960px-Trubetzkoy_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M257" s="5" t="n"/>
@@ -17822,44 +17818,42 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T257" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="U257" s="6" t="n">
+      <c r="T257" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="V257" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="W257" s="6" t="n">
-        <v>1</v>
+      <c r="U257" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="V257" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="W257" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>Bertel</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>THORVALDSEN</t>
+          <t>TROUBETZKOY</t>
         </is>
       </c>
       <c r="C258" s="5" t="n"/>
-      <c r="D258" s="6" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="D258" s="6" t="n">
+        <v>1909</v>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>Varsovie</t>
+          <t>Saint Petersbourg</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Palais Koniecpolski</t>
+          <t>Cour du Palais de Marbre</t>
         </is>
       </c>
       <c r="G258" s="5" t="n"/>
@@ -17867,13 +17861,13 @@
       <c r="I258" s="5" t="n"/>
       <c r="J258" s="5" t="inlineStr">
         <is>
-          <t>"Monument au prince Józef Poniatowski"</t>
+          <t>Monument à Alexandre III</t>
         </is>
       </c>
       <c r="K258" s="5" t="n"/>
       <c r="L258" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="M258" s="5" t="n"/>
@@ -17883,7 +17877,7 @@
       <c r="Q258" s="5" t="n"/>
       <c r="R258" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Statue équestre</t>
         </is>
       </c>
       <c r="S258" s="5" t="inlineStr">
@@ -17891,44 +17885,42 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T258" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="U258" s="6" t="n">
-        <v>350</v>
-      </c>
-      <c r="V258" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="W258" s="6" t="n">
-        <v>1</v>
+      <c r="T258" s="3" t="n">
+        <v>480</v>
+      </c>
+      <c r="U258" s="3" t="n">
+        <v>580</v>
+      </c>
+      <c r="V258" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="W258" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>Bertel</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>THORVALDSEN</t>
+          <t>TROUBETZKOY</t>
         </is>
       </c>
       <c r="C259" s="5" t="n"/>
-      <c r="D259" s="6" t="inlineStr">
-        <is>
-          <t>1813-1816</t>
-        </is>
+      <c r="D259" s="6" t="n">
+        <v>1899</v>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Verbania</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Musée Thorvaldsen</t>
+          <t>Museo del Passaggio</t>
         </is>
       </c>
       <c r="G259" s="5" t="n"/>
@@ -17936,13 +17928,13 @@
       <c r="I259" s="5" t="n"/>
       <c r="J259" s="5" t="inlineStr">
         <is>
-          <t>"Vénus à la pomme"</t>
+          <t>Tolstoï à cheval</t>
         </is>
       </c>
       <c r="K259" s="5" t="n"/>
       <c r="L259" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Thorvaldsens_Venus.jpg/960px-Thorvaldsens_Venus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="M259" s="5" t="n"/>
@@ -17957,179 +17949,179 @@
       </c>
       <c r="S259" s="5" t="inlineStr">
         <is>
+          <t>Plâtre ciré</t>
+        </is>
+      </c>
+      <c r="T259" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="U259" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="V259" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W259" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" ht="15" customHeight="1">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>Paolo</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>TROUBETZKOY</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="6" t="n">
+        <v>1911</v>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>Tate Britain</t>
+        </is>
+      </c>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
+      <c r="J260" s="5" t="inlineStr">
+        <is>
+          <t>Buste de George Bernard Shaw</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n"/>
+      <c r="L260" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e3/7220_-_Paolo_Troubetzkoy_-_George_Bernard_Shaw_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/960px-7220_-_Paolo_Troubetzkoy_-_George_Bernard_Shaw_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+        </is>
+      </c>
+      <c r="M260" s="5" t="n"/>
+      <c r="N260" s="5" t="n"/>
+      <c r="O260" s="5" t="n"/>
+      <c r="P260" s="5" t="n"/>
+      <c r="Q260" s="5" t="n"/>
+      <c r="R260" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S260" s="5" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T260" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="U260" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="V260" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W260" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" ht="15" customHeight="1">
+      <c r="A261" s="29" t="inlineStr">
+        <is>
+          <t>Vincenzo</t>
+        </is>
+      </c>
+      <c r="B261" s="29" t="inlineStr">
+        <is>
+          <t>VELA</t>
+        </is>
+      </c>
+      <c r="C261" s="29" t="n"/>
+      <c r="D261" s="31" t="n">
+        <v>1847</v>
+      </c>
+      <c r="E261" s="29" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F261" s="29" t="inlineStr">
+        <is>
+          <t>Palazzo Civico</t>
+        </is>
+      </c>
+      <c r="G261" s="29" t="n"/>
+      <c r="H261" s="29" t="n"/>
+      <c r="I261" s="29" t="n"/>
+      <c r="J261" s="29" t="inlineStr">
+        <is>
+          <t>Spartacus</t>
+        </is>
+      </c>
+      <c r="K261" s="29" t="n"/>
+      <c r="L261" s="30" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Spartaco_by_Vincenzo_Vela_01.jpg/960px-Spartaco_by_Vincenzo_Vela_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M261" s="29" t="n"/>
+      <c r="N261" s="29" t="n"/>
+      <c r="O261" s="29" t="n"/>
+      <c r="P261" s="29" t="n"/>
+      <c r="Q261" s="29" t="n"/>
+      <c r="R261" s="29" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S261" s="29" t="inlineStr">
+        <is>
           <t>Marbre</t>
         </is>
       </c>
-      <c r="T259" s="6" t="n">
-        <v>161</v>
-      </c>
-      <c r="U259" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="V259" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="W259" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" ht="15" customHeight="1">
-      <c r="A260" s="27" t="inlineStr">
-        <is>
-          <t>Bertel</t>
-        </is>
-      </c>
-      <c r="B260" s="27" t="inlineStr">
-        <is>
-          <t>THORVALDSEN</t>
-        </is>
-      </c>
-      <c r="C260" s="27" t="n"/>
-      <c r="D260" s="37" t="n">
-        <v>1831</v>
-      </c>
-      <c r="E260" s="27" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="F260" s="27" t="inlineStr">
-        <is>
-          <t>Basilique Saint-Pierre</t>
-        </is>
-      </c>
-      <c r="G260" s="27" t="n"/>
-      <c r="H260" s="27" t="n"/>
-      <c r="I260" s="27" t="n"/>
-      <c r="J260" s="27" t="inlineStr">
-        <is>
-          <t>"Monument funéraire du pape Pie VII"</t>
-        </is>
-      </c>
-      <c r="K260" s="27" t="n"/>
-      <c r="L260" s="36" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/99/0_Tombeau_du_pape_Pie_VII_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Tombeau_du_pape_Pie_VII_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M260" s="27" t="n"/>
-      <c r="N260" s="27" t="n"/>
-      <c r="O260" s="27" t="n"/>
-      <c r="P260" s="27" t="n"/>
-      <c r="Q260" s="27" t="n"/>
-      <c r="R260" s="27" t="inlineStr">
-        <is>
-          <t>Monument funéraire avec ensemble en ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S260" s="27" t="inlineStr">
-        <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T260" s="37" t="n">
-        <v>700</v>
-      </c>
-      <c r="U260" s="37" t="n">
-        <v>450</v>
-      </c>
-      <c r="V260" s="37" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W260" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" ht="15" customHeight="1">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>Paolo</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
-        <is>
-          <t>TROUBETZKOY</t>
-        </is>
-      </c>
-      <c r="C261" s="5" t="n"/>
-      <c r="D261" s="6" t="n">
-        <v>1900</v>
-      </c>
-      <c r="E261" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersbourg</t>
-        </is>
-      </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>Musée Russe</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="n"/>
-      <c r="H261" s="5" t="n"/>
-      <c r="I261" s="5" t="n"/>
-      <c r="J261" s="5" t="inlineStr">
-        <is>
-          <t>"Les Enfants"</t>
-        </is>
-      </c>
-      <c r="K261" s="5" t="n"/>
-      <c r="L261" s="8" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Trubetzkoy_Children.jpg/960px-Trubetzkoy_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M261" s="5" t="n"/>
-      <c r="N261" s="5" t="n"/>
-      <c r="O261" s="5" t="n"/>
-      <c r="P261" s="5" t="n"/>
-      <c r="Q261" s="5" t="n"/>
-      <c r="R261" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S261" s="5" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T261" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="U261" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="V261" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="W261" s="3" t="n">
-        <v>3</v>
+      <c r="T261" s="31" t="n">
+        <v>208</v>
+      </c>
+      <c r="U261" s="31" t="n">
+        <v>120</v>
+      </c>
+      <c r="V261" s="31" t="n">
+        <v>126</v>
+      </c>
+      <c r="W261" s="31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Vincenzo</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>TROUBETZKOY</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="C262" s="5" t="n"/>
       <c r="D262" s="6" t="n">
-        <v>1909</v>
+        <v>1868</v>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>Saint Petersbourg</t>
+          <t>Ligornetto</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Cour du Palais de Marbre</t>
+          <t>Museo Vincenzo Vela</t>
         </is>
       </c>
       <c r="G262" s="5" t="n"/>
@@ -18137,13 +18129,13 @@
       <c r="I262" s="5" t="n"/>
       <c r="J262" s="5" t="inlineStr">
         <is>
-          <t>Monument à Alexandre III</t>
+          <t>Ecce Homo</t>
         </is>
       </c>
       <c r="K262" s="5" t="n"/>
       <c r="L262" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b9/Ecce_Homo%2C_Vincenzo_Vela.jpg/960px-Ecce_Homo%2C_Vincenzo_Vela.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M262" s="5" t="n"/>
@@ -18153,50 +18145,50 @@
       <c r="Q262" s="5" t="n"/>
       <c r="R262" s="5" t="inlineStr">
         <is>
-          <t>Statue équestre</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S262" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T262" s="3" t="n">
-        <v>480</v>
-      </c>
-      <c r="U262" s="3" t="n">
-        <v>580</v>
-      </c>
-      <c r="V262" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="W262" s="3" t="n">
-        <v>3</v>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T262" s="6" t="n">
+        <v>162</v>
+      </c>
+      <c r="U262" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="V262" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="W262" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Vincenzo</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>TROUBETZKOY</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="C263" s="5" t="n"/>
       <c r="D263" s="6" t="n">
-        <v>1899</v>
+        <v>1882</v>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>Verbania</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Museo del Passaggio</t>
+          <t>Galleria Nazionale d'Arte Moderna</t>
         </is>
       </c>
       <c r="G263" s="5" t="n"/>
@@ -18204,13 +18196,13 @@
       <c r="I263" s="5" t="n"/>
       <c r="J263" s="5" t="inlineStr">
         <is>
-          <t>Tolstoï à cheval</t>
+          <t>Les Victimes du travail</t>
         </is>
       </c>
       <c r="K263" s="5" t="n"/>
       <c r="L263" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Monumento_alle_vittime_del_lavoro_%28Airolo%29_%28Vincenzo_Vela_1883%29_%281932%29_01.jpg/1280px-Monumento_alle_vittime_del_lavoro_%28Airolo%29_%28Vincenzo_Vela_1883%29_%281932%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M263" s="5" t="n"/>
@@ -18220,50 +18212,50 @@
       <c r="Q263" s="5" t="n"/>
       <c r="R263" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S263" s="5" t="inlineStr">
         <is>
-          <t>Plâtre ciré</t>
-        </is>
-      </c>
-      <c r="T263" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="U263" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="V263" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W263" s="3" t="n">
-        <v>3</v>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T263" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="U263" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="V263" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="W263" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Vincenzo</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>TROUBETZKOY</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="C264" s="5" t="n"/>
       <c r="D264" s="6" t="n">
-        <v>1911</v>
+        <v>1856</v>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Quai Vincenzo Vela</t>
         </is>
       </c>
       <c r="G264" s="5" t="n"/>
@@ -18271,13 +18263,13 @@
       <c r="I264" s="5" t="n"/>
       <c r="J264" s="5" t="inlineStr">
         <is>
-          <t>Buste de George Bernard Shaw</t>
+          <t>Monument à Guillaume Tell</t>
         </is>
       </c>
       <c r="K264" s="5" t="n"/>
       <c r="L264" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e3/7220_-_Paolo_Troubetzkoy_-_George_Bernard_Shaw_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/960px-7220_-_Paolo_Troubetzkoy_-_George_Bernard_Shaw_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Guillermo_Tell_by_Vincenzo_Vela.jpg/960px-Guillermo_Tell_by_Vincenzo_Vela.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M264" s="5" t="n"/>
@@ -18292,86 +18284,86 @@
       </c>
       <c r="S264" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T264" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="U264" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="V264" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W264" s="3" t="n">
-        <v>3</v>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="T264" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="U264" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="V264" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="W264" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
-      <c r="A265" s="29" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
         <is>
           <t>Vincenzo</t>
         </is>
       </c>
-      <c r="B265" s="29" t="inlineStr">
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>VELA</t>
         </is>
       </c>
-      <c r="C265" s="29" t="n"/>
-      <c r="D265" s="31" t="n">
-        <v>1847</v>
-      </c>
-      <c r="E265" s="29" t="inlineStr">
-        <is>
-          <t>Lugano</t>
-        </is>
-      </c>
-      <c r="F265" s="29" t="inlineStr">
-        <is>
-          <t>Palazzo Civico</t>
-        </is>
-      </c>
-      <c r="G265" s="29" t="n"/>
-      <c r="H265" s="29" t="n"/>
-      <c r="I265" s="29" t="n"/>
-      <c r="J265" s="29" t="inlineStr">
-        <is>
-          <t>Spartacus</t>
-        </is>
-      </c>
-      <c r="K265" s="29" t="n"/>
-      <c r="L265" s="30" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Spartaco_by_Vincenzo_Vela_01.jpg/960px-Spartaco_by_Vincenzo_Vela_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M265" s="29" t="n"/>
-      <c r="N265" s="29" t="n"/>
-      <c r="O265" s="29" t="n"/>
-      <c r="P265" s="29" t="n"/>
-      <c r="Q265" s="29" t="n"/>
-      <c r="R265" s="29" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S265" s="29" t="inlineStr">
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="6" t="n">
+        <v>1858</v>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Palazzo Brera</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="5" t="n"/>
+      <c r="I265" s="5" t="n"/>
+      <c r="J265" s="5" t="inlineStr">
+        <is>
+          <t>Monument à Tommaso Grossi</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n"/>
+      <c r="L265" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Vincenzo_Vela%2C_Monumento_a_Tommaso_Grossi_%281858%29_Accademia_di_Brera.jpg/960px-Vincenzo_Vela%2C_Monumento_a_Tommaso_Grossi_%281858%29_Accademia_di_Brera.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M265" s="5" t="n"/>
+      <c r="N265" s="5" t="n"/>
+      <c r="O265" s="5" t="n"/>
+      <c r="P265" s="5" t="n"/>
+      <c r="Q265" s="5" t="n"/>
+      <c r="R265" s="5" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S265" s="5" t="inlineStr">
         <is>
           <t>Marbre</t>
         </is>
       </c>
-      <c r="T265" s="31" t="n">
-        <v>208</v>
-      </c>
-      <c r="U265" s="31" t="n">
-        <v>120</v>
-      </c>
-      <c r="V265" s="31" t="n">
-        <v>126</v>
-      </c>
-      <c r="W265" s="31" t="n">
+      <c r="T265" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="U265" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="V265" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="W265" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18388,16 +18380,16 @@
       </c>
       <c r="C266" s="5" t="n"/>
       <c r="D266" s="6" t="n">
-        <v>1868</v>
+        <v>1862</v>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>Ligornetto</t>
+          <t>Compiègne</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Museo Vincenzo Vela</t>
+          <t>Château de Compiègne</t>
         </is>
       </c>
       <c r="G266" s="5" t="n"/>
@@ -18405,13 +18397,13 @@
       <c r="I266" s="5" t="n"/>
       <c r="J266" s="5" t="inlineStr">
         <is>
-          <t>Ecce Homo</t>
+          <t>L'Italie reconnaissante</t>
         </is>
       </c>
       <c r="K266" s="5" t="n"/>
-      <c r="L266" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b9/Ecce_Homo%2C_Vincenzo_Vela.jpg/960px-Ecce_Homo%2C_Vincenzo_Vela.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L266" s="34" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Ch%C3%A2teau_de_Compi%C3%A8gne-La_France_Imp%C3%A9riale_secourant_l%27Italie-20150303.jpg/960px-Ch%C3%A2teau_de_Compi%C3%A8gne-La_France_Imp%C3%A9riale_secourant_l%27Italie-20150303.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M266" s="5" t="n"/>
@@ -18421,184 +18413,167 @@
       <c r="Q266" s="5" t="n"/>
       <c r="R266" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S266" s="5" t="inlineStr">
+          <t>Groupe en ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
         <is>
           <t>Marbre</t>
         </is>
       </c>
       <c r="T266" s="6" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="U266" s="6" t="n">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="V266" s="6" t="n">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="W266" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Vincenzo</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
-        <is>
-          <t>VELA</t>
-        </is>
-      </c>
-      <c r="C267" s="5" t="n"/>
-      <c r="D267" s="6" t="n">
-        <v>1882</v>
-      </c>
-      <c r="E267" s="5" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>Galleria Nazionale d'Arte Moderna</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="n"/>
-      <c r="H267" s="5" t="n"/>
-      <c r="I267" s="5" t="n"/>
-      <c r="J267" s="5" t="inlineStr">
-        <is>
-          <t>Les Victimes du travail</t>
-        </is>
-      </c>
-      <c r="K267" s="5" t="n"/>
-      <c r="L267" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Monumento_alle_vittime_del_lavoro_%28Airolo%29_%28Vincenzo_Vela_1883%29_%281932%29_01.jpg/1280px-Monumento_alle_vittime_del_lavoro_%28Airolo%29_%28Vincenzo_Vela_1883%29_%281932%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M267" s="5" t="n"/>
-      <c r="N267" s="5" t="n"/>
-      <c r="O267" s="5" t="n"/>
-      <c r="P267" s="5" t="n"/>
-      <c r="Q267" s="5" t="n"/>
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Adolf</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>von HILDEBRAND</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
+        <is>
+          <t>1871-1873</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Alte Nationalgalerie</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>"Jeune pâtre endormi"</t>
+        </is>
+      </c>
+      <c r="L267" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8b/Hirtenknabe.jpg/960px-Hirtenknabe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
       <c r="R267" s="5" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S267" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T267" s="6" t="n">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="U267" s="6" t="n">
-        <v>323</v>
+        <v>68</v>
       </c>
       <c r="V267" s="6" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="W267" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Vincenzo</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
-        <is>
-          <t>VELA</t>
-        </is>
-      </c>
-      <c r="C268" s="5" t="n"/>
-      <c r="D268" s="6" t="n">
-        <v>1856</v>
-      </c>
-      <c r="E268" s="5" t="inlineStr">
-        <is>
-          <t>Lugano</t>
-        </is>
-      </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>Quai Vincenzo Vela</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="n"/>
-      <c r="H268" s="5" t="n"/>
-      <c r="I268" s="5" t="n"/>
-      <c r="J268" s="5" t="inlineStr">
-        <is>
-          <t>Monument à Guillaume Tell</t>
-        </is>
-      </c>
-      <c r="K268" s="5" t="n"/>
-      <c r="L268" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Guillermo_Tell_by_Vincenzo_Vela.jpg/960px-Guillermo_Tell_by_Vincenzo_Vela.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M268" s="5" t="n"/>
-      <c r="N268" s="5" t="n"/>
-      <c r="O268" s="5" t="n"/>
-      <c r="P268" s="5" t="n"/>
-      <c r="Q268" s="5" t="n"/>
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Adolf</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>von HILDEBRAND</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
+        <is>
+          <t>1893-1895</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Lenbachplatz</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>"Fontaine Wittelsbach"</t>
+        </is>
+      </c>
+      <c r="L268" s="10" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=de</t>
+        </is>
+      </c>
       <c r="R268" s="5" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S268" s="5" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Pierre et bronze</t>
         </is>
       </c>
       <c r="T268" s="6" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="U268" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="V268" s="6" t="n">
-        <v>80</v>
+        <v>2500</v>
       </c>
       <c r="W268" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>Vincenzo</t>
+          <t>Adolf</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>von HILDEBRAND</t>
         </is>
       </c>
       <c r="C269" s="5" t="n"/>
-      <c r="D269" s="6" t="n">
-        <v>1858</v>
+      <c r="D269" s="6" t="inlineStr">
+        <is>
+          <t>1881-1884</t>
+        </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Palazzo Brera</t>
+          <t>Alte Nationalgalerie</t>
         </is>
       </c>
       <c r="G269" s="5" t="n"/>
@@ -18606,13 +18581,13 @@
       <c r="I269" s="5" t="n"/>
       <c r="J269" s="5" t="inlineStr">
         <is>
-          <t>Monument à Tommaso Grossi</t>
+          <t>Jeune homme debout</t>
         </is>
       </c>
       <c r="K269" s="5" t="n"/>
       <c r="L269" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Vincenzo_Vela%2C_Monumento_a_Tommaso_Grossi_%281858%29_Accademia_di_Brera.jpg/960px-Vincenzo_Vela%2C_Monumento_a_Tommaso_Grossi_%281858%29_Accademia_di_Brera.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Stehender.jpg/960px-Stehender.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M269" s="5" t="n"/>
@@ -18631,41 +18606,41 @@
         </is>
       </c>
       <c r="T269" s="6" t="n">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="U269" s="6" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="V269" s="6" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="W269" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>Vincenzo</t>
+          <t>Adolf</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>von HILDEBRAND</t>
         </is>
       </c>
       <c r="C270" s="5" t="n"/>
       <c r="D270" s="6" t="n">
-        <v>1862</v>
+        <v>1897</v>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Compiègne</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Château de Compiègne</t>
+          <t>Neue Pinakothek</t>
         </is>
       </c>
       <c r="G270" s="5" t="n"/>
@@ -18673,13 +18648,13 @@
       <c r="I270" s="5" t="n"/>
       <c r="J270" s="5" t="inlineStr">
         <is>
-          <t>L'Italie reconnaissante</t>
+          <t>Buste d'Arnold Böcklin</t>
         </is>
       </c>
       <c r="K270" s="5" t="n"/>
-      <c r="L270" s="34" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Ch%C3%A2teau_de_Compi%C3%A8gne-La_France_Imp%C3%A9riale_secourant_l%27Italie-20150303.jpg/960px-Ch%C3%A2teau_de_Compi%C3%A8gne-La_France_Imp%C3%A9riale_secourant_l%27Italie-20150303.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+      <c r="L270" s="8" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Arnold_B%C3%B6cklin_bust_by_Adolf_von_Hildebrand_1897.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="M270" s="5" t="n"/>
@@ -18689,61 +18664,61 @@
       <c r="Q270" s="5" t="n"/>
       <c r="R270" s="5" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>Marbre</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S270" s="5" t="inlineStr">
+        <is>
+          <t>Plâtre patiné</t>
         </is>
       </c>
       <c r="T270" s="6" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="U270" s="6" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="V270" s="6" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="W270" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Adolf</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>von HILDEBRAND</t>
+          <t>WHITNEY</t>
         </is>
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>1871-1873</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>Alte Nationalgalerie</t>
+          <t>United States Capitol</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>"Jeune pâtre endormi"</t>
+          <t>"Samuel Adams"</t>
         </is>
       </c>
       <c r="L271" s="10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8b/Hirtenknabe.jpg/960px-Hirtenknabe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="R271" s="5" t="inlineStr">
@@ -18757,69 +18732,82 @@
         </is>
       </c>
       <c r="T271" s="6" t="n">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="U271" s="6" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="V271" s="6" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="W271" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>Adolf</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>von HILDEBRAND</t>
-        </is>
-      </c>
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>WHITNEY</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="n"/>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>1893-1895</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="F272" s="2" t="inlineStr">
-        <is>
-          <t>Lenbachplatz</t>
-        </is>
-      </c>
-      <c r="J272" s="2" t="inlineStr">
-        <is>
-          <t>"Fontaine Wittelsbach"</t>
-        </is>
-      </c>
-      <c r="L272" s="10" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=de</t>
-        </is>
-      </c>
+          <t>1863</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Smithsonian American Art Museum</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+      <c r="J272" s="5" t="inlineStr">
+        <is>
+          <t>"Laura Brown"</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n"/>
+      <c r="L272" s="8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Laura_Brown_SAAM-1968.24_1.jpg/960px-Laura_Brown_SAAM-1968.24_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M272" s="5" t="n"/>
+      <c r="N272" s="5" t="n"/>
+      <c r="O272" s="5" t="n"/>
+      <c r="P272" s="5" t="n"/>
+      <c r="Q272" s="5" t="n"/>
       <c r="R272" s="5" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S272" s="5" t="inlineStr">
         <is>
-          <t>Pierre et bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T272" s="6" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="U272" s="6" t="n">
-        <v>2500</v>
+        <v>28</v>
+      </c>
+      <c r="V272" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="W272" s="6" t="n">
         <v>3</v>
@@ -18828,28 +18816,28 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>Adolf</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>von HILDEBRAND</t>
+          <t>WHITNEY</t>
         </is>
       </c>
       <c r="C273" s="5" t="n"/>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>1881-1884</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Alte Nationalgalerie</t>
+          <t>Harvard Square</t>
         </is>
       </c>
       <c r="G273" s="5" t="n"/>
@@ -18857,13 +18845,13 @@
       <c r="I273" s="5" t="n"/>
       <c r="J273" s="5" t="inlineStr">
         <is>
-          <t>Jeune homme debout</t>
+          <t>"Charles Sumner"</t>
         </is>
       </c>
       <c r="K273" s="5" t="n"/>
       <c r="L273" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Stehender.jpg/960px-Stehender.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Charles_Sumner_statue_%28Cambridge%2C_MA%29_-_Anne_Whitney_sculptor.JPG/960px-Charles_Sumner_statue_%28Cambridge%2C_MA%29_-_Anne_Whitney_sculptor.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M273" s="5" t="n"/>
@@ -18878,17 +18866,17 @@
       </c>
       <c r="S273" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T273" s="6" t="n">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="U273" s="6" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="V273" s="6" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="W273" s="6" t="n">
         <v>3</v>
@@ -18897,26 +18885,28 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>Adolf</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>von HILDEBRAND</t>
+          <t>WHITNEY</t>
         </is>
       </c>
       <c r="C274" s="5" t="n"/>
-      <c r="D274" s="6" t="n">
-        <v>1897</v>
+      <c r="D274" s="6" t="inlineStr">
+        <is>
+          <t>1885-1887</t>
+        </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Neue Pinakothek</t>
+          <t>Commonwealth Avenue Mall</t>
         </is>
       </c>
       <c r="G274" s="5" t="n"/>
@@ -18924,13 +18914,13 @@
       <c r="I274" s="5" t="n"/>
       <c r="J274" s="5" t="inlineStr">
         <is>
-          <t>Buste d'Arnold Böcklin</t>
+          <t>Statue de Leif Eriksson</t>
         </is>
       </c>
       <c r="K274" s="5" t="n"/>
       <c r="L274" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Arnold_B%C3%B6cklin_bust_by_Adolf_von_Hildebrand_1897.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/Leif_Eriksson_statue%2C_Boston.jpg/960px-Leif_Eriksson_statue%2C_Boston.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M274" s="5" t="n"/>
@@ -18945,58 +18935,68 @@
       </c>
       <c r="S274" s="5" t="inlineStr">
         <is>
-          <t>Plâtre patiné</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T274" s="6" t="n">
-        <v>58</v>
+        <v>260</v>
       </c>
       <c r="U274" s="6" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="V274" s="6" t="n">
-        <v>26</v>
+        <v>250</v>
       </c>
       <c r="W274" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>Anne</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>WHITNEY</t>
-        </is>
-      </c>
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>William Wetmore</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="n"/>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="F275" s="2" t="inlineStr">
-        <is>
-          <t>United States Capitol</t>
-        </is>
-      </c>
-      <c r="J275" s="2" t="inlineStr">
-        <is>
-          <t>"Samuel Adams"</t>
-        </is>
-      </c>
-      <c r="L275" s="10" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+          <t>1858-1869</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Metropolitan Museum of Art</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
+      <c r="J275" s="5" t="inlineStr">
+        <is>
+          <t>Cléopâtre</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n"/>
+      <c r="L275" s="8" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Cleopatra_by_William_Wetmore_Story_01.jpg/1280px-Cleopatra_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M275" s="5" t="n"/>
+      <c r="N275" s="5" t="n"/>
+      <c r="O275" s="5" t="n"/>
+      <c r="P275" s="5" t="n"/>
+      <c r="Q275" s="5" t="n"/>
       <c r="R275" s="5" t="inlineStr">
         <is>
           <t>Ronde-bosse</t>
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="T275" s="6" t="n">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c r="U275" s="6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="V275" s="6" t="n">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="W275" s="6" t="n">
         <v>3</v>
@@ -19023,28 +19023,28 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>William Wetmore</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>WHITNEY</t>
+          <t>STORY</t>
         </is>
       </c>
       <c r="C276" s="5" t="n"/>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Smithsonian American Art Museum</t>
+          <t>Cimetière protestant</t>
         </is>
       </c>
       <c r="G276" s="5" t="n"/>
@@ -19052,13 +19052,13 @@
       <c r="I276" s="5" t="n"/>
       <c r="J276" s="5" t="inlineStr">
         <is>
-          <t>"Laura Brown"</t>
+          <t>Angel of grief, pierre tombale de l’artiste et de son épouse Emelyn</t>
         </is>
       </c>
       <c r="K276" s="5" t="n"/>
       <c r="L276" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Laura_Brown_SAAM-1968.24_1.jpg/960px-Laura_Brown_SAAM-1968.24_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f2/Emelyn_Story_Tomba_%28Cimitero_Acattolico_Roma%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="M276" s="5" t="n"/>
@@ -19077,13 +19077,13 @@
         </is>
       </c>
       <c r="T276" s="6" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="U276" s="6" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="V276" s="6" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="W276" s="6" t="n">
         <v>3</v>
@@ -19092,28 +19092,28 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>William Wetmore</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>WHITNEY</t>
+          <t>STORY</t>
         </is>
       </c>
       <c r="C277" s="5" t="n"/>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Harvard Square</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="G277" s="5" t="n"/>
@@ -19121,13 +19121,13 @@
       <c r="I277" s="5" t="n"/>
       <c r="J277" s="5" t="inlineStr">
         <is>
-          <t>"Charles Sumner"</t>
+          <t>Medée</t>
         </is>
       </c>
       <c r="K277" s="5" t="n"/>
       <c r="L277" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Charles_Sumner_statue_%28Cambridge%2C_MA%29_-_Anne_Whitney_sculptor.JPG/960px-Charles_Sumner_statue_%28Cambridge%2C_MA%29_-_Anne_Whitney_sculptor.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/Medea_by_William_Wetmore_Story_01.jpg/960px-Medea_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M277" s="5" t="n"/>
@@ -19142,17 +19142,17 @@
       </c>
       <c r="S277" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T277" s="6" t="n">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="U277" s="6" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="V277" s="6" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="W277" s="6" t="n">
         <v>3</v>
@@ -19161,28 +19161,28 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>William Wetmore</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>WHITNEY</t>
+          <t>STORY</t>
         </is>
       </c>
       <c r="C278" s="5" t="n"/>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>1885-1887</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Commonwealth Avenue Mall</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="G278" s="5" t="n"/>
@@ -19190,13 +19190,13 @@
       <c r="I278" s="5" t="n"/>
       <c r="J278" s="5" t="inlineStr">
         <is>
-          <t>Statue de Leif Eriksson</t>
+          <t>Sibylle libyenne</t>
         </is>
       </c>
       <c r="K278" s="5" t="n"/>
       <c r="L278" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/Leif_Eriksson_statue%2C_Boston.jpg/960px-Leif_Eriksson_statue%2C_Boston.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/The_Libyan_Sibyl_by_William_Wetmore_Story_02.jpg/960px-The_Libyan_Sibyl_by_William_Wetmore_Story_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M278" s="5" t="n"/>
@@ -19211,17 +19211,17 @@
       </c>
       <c r="S278" s="5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T278" s="6" t="n">
-        <v>260</v>
+        <v>135</v>
       </c>
       <c r="U278" s="6" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="V278" s="6" t="n">
-        <v>250</v>
+        <v>116</v>
       </c>
       <c r="W278" s="6" t="n">
         <v>3</v>
@@ -19230,28 +19230,26 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>William Wetmore</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>Woolner</t>
         </is>
       </c>
       <c r="C279" s="5" t="n"/>
-      <c r="D279" s="6" t="inlineStr">
-        <is>
-          <t>1858-1869</t>
-        </is>
+      <c r="D279" s="6" t="n">
+        <v>1873</v>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>National Portrait Gallery</t>
         </is>
       </c>
       <c r="G279" s="5" t="n"/>
@@ -19259,13 +19257,13 @@
       <c r="I279" s="5" t="n"/>
       <c r="J279" s="5" t="inlineStr">
         <is>
-          <t>Cléopâtre</t>
+          <t>Buste de Alfred Tennyson</t>
         </is>
       </c>
       <c r="K279" s="5" t="n"/>
       <c r="L279" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Cleopatra_by_William_Wetmore_Story_01.jpg/1280px-Cleopatra_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ea/Bust_of_Alfred%2C_Lord_Tennyson%2C_Westminster_Abbey_01.jpg/960px-Bust_of_Alfred%2C_Lord_Tennyson%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M279" s="5" t="n"/>
@@ -19280,17 +19278,17 @@
       </c>
       <c r="S279" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Plâtre</t>
         </is>
       </c>
       <c r="T279" s="6" t="n">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="U279" s="6" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="V279" s="6" t="n">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="W279" s="6" t="n">
         <v>3</v>
@@ -19299,28 +19297,28 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>William Wetmore</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>Woolner</t>
         </is>
       </c>
       <c r="C280" s="5" t="n"/>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Cimetière protestant</t>
+          <t>Palais de Westminster</t>
         </is>
       </c>
       <c r="G280" s="5" t="n"/>
@@ -19328,13 +19326,13 @@
       <c r="I280" s="5" t="n"/>
       <c r="J280" s="5" t="inlineStr">
         <is>
-          <t>Angel of grief, pierre tombale de l’artiste et de son épouse Emelyn</t>
+          <t>Statue de Lord Palmerston</t>
         </is>
       </c>
       <c r="K280" s="5" t="n"/>
       <c r="L280" s="8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f2/Emelyn_Story_Tomba_%28Cimitero_Acattolico_Roma%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Palmerston_statue_Parliament_Square.jpg/960px-Palmerston_statue_Parliament_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M280" s="5" t="n"/>
@@ -19349,17 +19347,17 @@
       </c>
       <c r="S280" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T280" s="6" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="U280" s="6" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="V280" s="6" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="W280" s="6" t="n">
         <v>3</v>
@@ -19368,28 +19366,28 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>William Wetmore</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>Woolner</t>
         </is>
       </c>
       <c r="C281" s="5" t="n"/>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Hyde Park</t>
         </is>
       </c>
       <c r="G281" s="5" t="n"/>
@@ -19397,13 +19395,13 @@
       <c r="I281" s="5" t="n"/>
       <c r="J281" s="5" t="inlineStr">
         <is>
-          <t>Medée</t>
+          <t>Statue du Capitaine James Cook</t>
         </is>
       </c>
       <c r="K281" s="5" t="n"/>
       <c r="L281" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/Medea_by_William_Wetmore_Story_01.jpg/960px-Medea_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Hyde_Park_Captain_Cook.JPG/960px-Hyde_Park_Captain_Cook.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M281" s="5" t="n"/>
@@ -19418,17 +19416,17 @@
       </c>
       <c r="S281" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T281" s="6" t="n">
-        <v>209</v>
+        <v>470</v>
       </c>
       <c r="U281" s="6" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="V281" s="6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="W281" s="6" t="n">
         <v>3</v>
@@ -19437,28 +19435,26 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>William Wetmore</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>Woolner</t>
         </is>
       </c>
       <c r="C282" s="5" t="n"/>
-      <c r="D282" s="6" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
+      <c r="D282" s="6" t="n">
+        <v>1878</v>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Embankment</t>
         </is>
       </c>
       <c r="G282" s="5" t="n"/>
@@ -19466,13 +19462,13 @@
       <c r="I282" s="5" t="n"/>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>Sibylle libyenne</t>
+          <t>Statue de John Stuart Mill</t>
         </is>
       </c>
       <c r="K282" s="5" t="n"/>
       <c r="L282" s="8" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/The_Libyan_Sibyl_by_William_Wetmore_Story_02.jpg/960px-The_Libyan_Sibyl_by_William_Wetmore_Story_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/John_Stuart_Mill_%2831925382120%29.jpg/960px-John_Stuart_Mill_%2831925382120%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M282" s="5" t="n"/>
@@ -19487,294 +19483,26 @@
       </c>
       <c r="S282" s="5" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T282" s="6" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="U282" s="6" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="V282" s="6" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="W282" s="6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="283" ht="15" customHeight="1">
-      <c r="A283" s="5" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="B283" s="5" t="inlineStr">
-        <is>
-          <t>Woolner</t>
-        </is>
-      </c>
-      <c r="C283" s="5" t="n"/>
-      <c r="D283" s="6" t="n">
-        <v>1873</v>
-      </c>
-      <c r="E283" s="5" t="inlineStr">
-        <is>
-          <t>Londres</t>
-        </is>
-      </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>National Portrait Gallery</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="n"/>
-      <c r="H283" s="5" t="n"/>
-      <c r="I283" s="5" t="n"/>
-      <c r="J283" s="5" t="inlineStr">
-        <is>
-          <t>Buste de Alfred Tennyson</t>
-        </is>
-      </c>
-      <c r="K283" s="5" t="n"/>
-      <c r="L283" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ea/Bust_of_Alfred%2C_Lord_Tennyson%2C_Westminster_Abbey_01.jpg/960px-Bust_of_Alfred%2C_Lord_Tennyson%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M283" s="5" t="n"/>
-      <c r="N283" s="5" t="n"/>
-      <c r="O283" s="5" t="n"/>
-      <c r="P283" s="5" t="n"/>
-      <c r="Q283" s="5" t="n"/>
-      <c r="R283" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S283" s="5" t="inlineStr">
-        <is>
-          <t>Plâtre</t>
-        </is>
-      </c>
-      <c r="T283" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="U283" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="V283" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="W283" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="284" ht="15" customHeight="1">
-      <c r="A284" s="5" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="B284" s="5" t="inlineStr">
-        <is>
-          <t>Woolner</t>
-        </is>
-      </c>
-      <c r="C284" s="5" t="n"/>
-      <c r="D284" s="6" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="E284" s="5" t="inlineStr">
-        <is>
-          <t>Londres</t>
-        </is>
-      </c>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>Palais de Westminster</t>
-        </is>
-      </c>
-      <c r="G284" s="5" t="n"/>
-      <c r="H284" s="5" t="n"/>
-      <c r="I284" s="5" t="n"/>
-      <c r="J284" s="5" t="inlineStr">
-        <is>
-          <t>Statue de Lord Palmerston</t>
-        </is>
-      </c>
-      <c r="K284" s="5" t="n"/>
-      <c r="L284" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Palmerston_statue_Parliament_Square.jpg/960px-Palmerston_statue_Parliament_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M284" s="5" t="n"/>
-      <c r="N284" s="5" t="n"/>
-      <c r="O284" s="5" t="n"/>
-      <c r="P284" s="5" t="n"/>
-      <c r="Q284" s="5" t="n"/>
-      <c r="R284" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S284" s="5" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T284" s="6" t="n">
-        <v>260</v>
-      </c>
-      <c r="U284" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="V284" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="W284" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="285" ht="15" customHeight="1">
-      <c r="A285" s="5" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="inlineStr">
-        <is>
-          <t>Woolner</t>
-        </is>
-      </c>
-      <c r="C285" s="5" t="n"/>
-      <c r="D285" s="6" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="E285" s="5" t="inlineStr">
-        <is>
-          <t>Sydney</t>
-        </is>
-      </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>Hyde Park</t>
-        </is>
-      </c>
-      <c r="G285" s="5" t="n"/>
-      <c r="H285" s="5" t="n"/>
-      <c r="I285" s="5" t="n"/>
-      <c r="J285" s="5" t="inlineStr">
-        <is>
-          <t>Statue du Capitaine James Cook</t>
-        </is>
-      </c>
-      <c r="K285" s="5" t="n"/>
-      <c r="L285" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Hyde_Park_Captain_Cook.JPG/960px-Hyde_Park_Captain_Cook.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M285" s="5" t="n"/>
-      <c r="N285" s="5" t="n"/>
-      <c r="O285" s="5" t="n"/>
-      <c r="P285" s="5" t="n"/>
-      <c r="Q285" s="5" t="n"/>
-      <c r="R285" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S285" s="5" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T285" s="6" t="n">
-        <v>470</v>
-      </c>
-      <c r="U285" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="V285" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="W285" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="286" ht="15" customHeight="1">
-      <c r="A286" s="5" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="B286" s="5" t="inlineStr">
-        <is>
-          <t>Woolner</t>
-        </is>
-      </c>
-      <c r="C286" s="5" t="n"/>
-      <c r="D286" s="6" t="n">
-        <v>1878</v>
-      </c>
-      <c r="E286" s="5" t="inlineStr">
-        <is>
-          <t>Londres</t>
-        </is>
-      </c>
-      <c r="F286" s="5" t="inlineStr">
-        <is>
-          <t>Embankment</t>
-        </is>
-      </c>
-      <c r="G286" s="5" t="n"/>
-      <c r="H286" s="5" t="n"/>
-      <c r="I286" s="5" t="n"/>
-      <c r="J286" s="5" t="inlineStr">
-        <is>
-          <t>Statue de John Stuart Mill</t>
-        </is>
-      </c>
-      <c r="K286" s="5" t="n"/>
-      <c r="L286" s="8" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/John_Stuart_Mill_%2831925382120%29.jpg/960px-John_Stuart_Mill_%2831925382120%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M286" s="5" t="n"/>
-      <c r="N286" s="5" t="n"/>
-      <c r="O286" s="5" t="n"/>
-      <c r="P286" s="5" t="n"/>
-      <c r="Q286" s="5" t="n"/>
-      <c r="R286" s="5" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S286" s="5" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T286" s="6" t="n">
-        <v>175</v>
-      </c>
-      <c r="U286" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="V286" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="W286" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="283" ht="15" customHeight="1"/>
+    <row r="284" ht="15" customHeight="1"/>
+    <row r="285" ht="15" customHeight="1"/>
+    <row r="286" ht="15" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
@@ -20002,13 +19730,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N230" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N231" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N226" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N227" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId233"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId235"/>
@@ -20060,10 +19788,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="rId287"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/quizzes/sculpture-19e_20e.xlsx
+++ b/quizzes/sculpture-19e_20e.xlsx
@@ -1450,7 +1450,7 @@
     <t>Daumier</t>
   </si>
   <si>
-    <t>vers 1851</t>
+    <t>1851 environ</t>
   </si>
   <si>
     <t>Ratapoil</t>
@@ -1462,7 +1462,7 @@
     <t>bronze patiné</t>
   </si>
   <si>
-    <t>vers 1848</t>
+    <t>1848 environ</t>
   </si>
   <si>
     <t>Fugitifs (Les Émigrants)</t>

--- a/quizzes/sculpture-19e_20e.xlsx
+++ b/quizzes/sculpture-19e_20e.xlsx
@@ -4885,7 +4885,7 @@
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronze (statue), pierre (socle)</t>
+          <t xml:space="preserve">Bronze pour la statue, pierre pour le socle</t>
         </is>
       </c>
       <c r="T17" s="6" t="s">
@@ -5449,8 +5449,10 @@
           <t xml:space="preserve">Monument avec groupe en ronde-bosse. L'artiste n'a créé que la statue équestre. Le socle est dû à Eugène Viollet-le-Duc.</t>
         </is>
       </c>
-      <c r="S28" s="5" t="s">
-        <v>1179</v>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour les statues, granit pour le socle</t>
+        </is>
       </c>
       <c r="T28" s="6" t="s">
         <v>1180</v>

--- a/quizzes/sculpture-19e_20e.xlsx
+++ b/quizzes/sculpture-19e_20e.xlsx
@@ -4880,8 +4880,10 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="R17" s="5" t="s">
-        <v>1181</v>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument équestre avec ronde-bosse en bronze et haut-relief, sur un socle en pierre.</t>
+        </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -5291,8 +5293,10 @@
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
-      <c r="R25" s="5" t="s">
-        <v>1186</v>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statuette de bronze en ronde-bosse.</t>
+        </is>
       </c>
       <c r="S25" s="5" t="s">
         <v>31</v>
@@ -5446,7 +5450,7 @@
       <c r="Q28" s="5"/>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monument avec groupe en ronde-bosse. L'artiste n'a créé que la statue équestre. Le socle est dû à Eugène Viollet-le-Duc.</t>
+          <t xml:space="preserve">Monument avec groupe en ronde-bosse, statues en bronze et socle en granit. L'artiste n'a créé que la statue équestre. Le socle est dû à Eugène Viollet-le-Duc.</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -11066,7 +11070,7 @@
       <c r="Q142" s="5"/>
       <c r="R142" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuette équestre en ronde-bosse </t>
+          <t xml:space="preserve">Statuette équestre de bronze doré en ronde-bosse.</t>
         </is>
       </c>
       <c r="S142" s="5" t="s">
@@ -11745,8 +11749,10 @@
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
-      <c r="R156" t="s">
-        <v>1176</v>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument en bronze avec groupe en ronde-bosse, bas et haut-relief. L'artiste a créé la statue équestre et deux bas-reliefs.</t>
+        </is>
       </c>
       <c r="S156" s="5" t="s">
         <v>31</v>
@@ -14469,7 +14475,7 @@
       </c>
       <c r="R210" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monument équestre avec groupe en ronde-bosse intégralement conçu par l'artiste. </t>
+          <t xml:space="preserve">Monument équestre en bronze avec groupe en ronde-bosse, intégralement conçu par l'artiste.</t>
         </is>
       </c>
       <c r="S210" s="5" t="s">
@@ -17117,8 +17123,10 @@
       <c r="O265" s="5"/>
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
-      <c r="R265" s="5" t="s">
-        <v>1187</v>
+      <c r="R265" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statue équestre en bronze créée par l'artiste, le socle est récent et plus bas que l'original.</t>
+        </is>
       </c>
       <c r="S265" s="5" t="s">
         <v>31</v>

--- a/quizzes/sculpture-19e_20e.xlsx
+++ b/quizzes/sculpture-19e_20e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C57E7C2-9897-420C-985F-24617DDB525D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4926F01-5516-447B-BB1C-ECF0AD167382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2609" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="1223">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1273,9 +1273,6 @@
     <t>Capitol Square</t>
   </si>
   <si>
-    <t>Monument à George Washington</t>
-  </si>
-  <si>
     <t>Virginia Washington Monument</t>
   </si>
   <si>
@@ -2977,9 +2974,6 @@
     <t>Grand Army Plaza</t>
   </si>
   <si>
-    <t>"Monument au général Sherman"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -3208,9 +3202,6 @@
     <t>Palais Koniecpolski</t>
   </si>
   <si>
-    <t>"Monument au prince Józef Poniatowski"</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -3644,6 +3635,60 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>"Statue équestre du prince Józef Poniatowski"</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument équestre avec ronde-bosse. Resté sur ordre du tsar en Biélorussie jusqu'en 1922. Il réintégre Varsovie, la cour du Château Royal, mais il est dynamité en 1945 par les nazis. En 1951, le Danemark offre une nouvelle statue moulée sur le plâtre conservé au musée Thordvalsen à Copenhague.</t>
+  </si>
+  <si>
+    <t>Mémorial à George Washington</t>
+  </si>
+  <si>
+    <t>Monument équestre avec groupe en ronde-bosse. Le projet a été conçu intégralement par l'artiste qui est mort après avoir achevé trois statues, dont celle de Washington. Radolph Rogers a achevé les autres rondes-bosses.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>"Statue équestre du général Sherman"</t>
+  </si>
+  <si>
+    <t>Monument avec groupe en ronde-bosse.  L'artiste a créé la statue du général Sherman et celle de de la Victoire. AlaxanderPhimister Proctor a sculpté le cheval. Le socle a été réalisé par l'architecte Charles Follen MacKim.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Sherman_gilded_jeh.JPG/960px-Sherman_gilded_jeh.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue équestre en ronde-bosse</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500 pour la statue, 1400 pour le socle. </t>
+  </si>
+  <si>
+    <t>Statue équestrevet groupe en ronde-bosse. L'ensemble du projet a été conçu par l'artiste.</t>
   </si>
 </sst>
 </file>
@@ -4265,7 +4310,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4801,10 +4846,10 @@
         <v>88</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>89</v>
@@ -4815,7 +4860,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="R14" s="5" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="S14" s="5" t="s">
         <v>91</v>
@@ -4944,13 +4989,13 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="R17" s="5" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="U17" s="6">
         <v>450</v>
@@ -5341,7 +5386,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="8" t="s">
@@ -5353,7 +5398,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="S25" s="5" t="s">
         <v>31</v>
@@ -5506,13 +5551,13 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="U28" s="6">
         <v>235</v>
@@ -5637,14 +5682,14 @@
         <v>156</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>165</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="34" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>163</v>
@@ -5653,7 +5698,7 @@
         <v>164</v>
       </c>
       <c r="L31" s="34" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -5661,7 +5706,7 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="S31" s="5" t="s">
         <v>167</v>
@@ -6567,9 +6612,13 @@
       <c r="F49" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G49" s="5"/>
+      <c r="G49" s="34" t="s">
+        <v>1220</v>
+      </c>
       <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="I49" s="34" t="s">
+        <v>1219</v>
+      </c>
       <c r="J49" s="5" t="s">
         <v>249</v>
       </c>
@@ -6583,13 +6632,13 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="5" t="s">
-        <v>30</v>
+        <v>1222</v>
       </c>
       <c r="S49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T49" s="6">
-        <v>500</v>
+      <c r="T49" s="6" t="s">
+        <v>1221</v>
       </c>
       <c r="U49">
         <v>450</v>
@@ -6905,14 +6954,14 @@
         <v>276</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="34" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="8" t="s">
@@ -6924,7 +6973,7 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
       <c r="R56" s="5" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="S56" s="5" t="s">
         <v>31</v>
@@ -8682,17 +8731,20 @@
       <c r="F92" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
+      <c r="G92" s="34" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>418</v>
+      </c>
       <c r="J92" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="K92" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="K92" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="L92" s="8" t="s">
-        <v>419</v>
+      <c r="L92" s="34" t="s">
+        <v>1210</v>
       </c>
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
@@ -8700,7 +8752,7 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
       <c r="R92" s="5" t="s">
-        <v>63</v>
+        <v>1209</v>
       </c>
       <c r="S92" s="5" t="s">
         <v>31</v>
@@ -8736,13 +8788,13 @@
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="K93" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="K93" s="5" t="s">
+      <c r="L93" s="8" t="s">
         <v>421</v>
-      </c>
-      <c r="L93" s="8" t="s">
-        <v>422</v>
       </c>
       <c r="M93" s="5"/>
       <c r="N93" s="5"/>
@@ -8770,30 +8822,34 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>322</v>
       </c>
       <c r="F94" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="G94" s="34" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="34" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J94" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="K94" s="5"/>
       <c r="L94" s="32" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M94" s="5"/>
       <c r="N94" s="5"/>
@@ -8801,7 +8857,7 @@
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
       <c r="R94" s="5" t="s">
-        <v>30</v>
+        <v>1216</v>
       </c>
       <c r="S94" s="5" t="s">
         <v>31</v>
@@ -8821,30 +8877,30 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="F95" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K95" s="5"/>
       <c r="L95" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M95" s="5"/>
       <c r="N95" s="5"/>
@@ -8872,30 +8928,30 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E96" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F96" s="5" t="s">
         <v>434</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>435</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K96" s="5"/>
       <c r="L96" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M96" s="5"/>
       <c r="N96" s="5"/>
@@ -8923,30 +8979,30 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="F97" s="5" t="s">
         <v>439</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>440</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K97" s="5"/>
       <c r="L97" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M97" s="5"/>
       <c r="N97" s="5"/>
@@ -8974,14 +9030,14 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>45</v>
@@ -8993,11 +9049,11 @@
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K98" s="5"/>
       <c r="L98" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M98" s="5"/>
       <c r="N98" s="5"/>
@@ -9025,10 +9081,10 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="6" t="s">
@@ -9038,17 +9094,17 @@
         <v>45</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K99" s="5"/>
       <c r="L99" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
@@ -9076,10 +9132,10 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C100" s="5"/>
       <c r="D100" s="6" t="s">
@@ -9089,17 +9145,17 @@
         <v>45</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K100" s="5"/>
       <c r="L100" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
@@ -9124,10 +9180,10 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C101" s="5"/>
       <c r="D101" s="6" t="s">
@@ -9137,17 +9193,17 @@
         <v>45</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K101" s="5"/>
       <c r="L101" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
@@ -9172,10 +9228,10 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C102" s="5"/>
       <c r="D102" s="6" t="s">
@@ -9191,11 +9247,11 @@
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K102" s="5"/>
       <c r="L102" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
@@ -9223,10 +9279,10 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="6" t="s">
@@ -9236,17 +9292,17 @@
         <v>45</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K103" s="5"/>
       <c r="L103" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
@@ -9254,7 +9310,7 @@
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
       <c r="R103" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="S103" s="5" t="s">
         <v>31</v>
@@ -9271,10 +9327,10 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C104" s="5"/>
       <c r="D104" s="6" t="s">
@@ -9284,17 +9340,17 @@
         <v>45</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K104" s="5"/>
       <c r="L104" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
@@ -9322,10 +9378,10 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>443</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>444</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="6" t="s">
@@ -9335,17 +9391,17 @@
         <v>45</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K105" s="5"/>
       <c r="L105" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
@@ -9353,7 +9409,7 @@
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
       <c r="R105" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="S105" s="5" t="s">
         <v>233</v>
@@ -9373,16 +9429,16 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B106" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="C106" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="D106" s="12" t="s">
         <v>471</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>472</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>45</v>
@@ -9394,10 +9450,10 @@
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
       <c r="J106" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="L106" s="13" t="s">
         <v>473</v>
-      </c>
-      <c r="L106" s="13" t="s">
-        <v>474</v>
       </c>
       <c r="M106" s="11"/>
       <c r="N106" s="11"/>
@@ -9408,7 +9464,7 @@
         <v>30</v>
       </c>
       <c r="S106" s="14" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="T106" s="12">
         <v>43</v>
@@ -9425,16 +9481,16 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B107" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="C107" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>471</v>
-      </c>
       <c r="D107" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>45</v>
@@ -9446,10 +9502,10 @@
       <c r="H107" s="11"/>
       <c r="I107" s="11"/>
       <c r="J107" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="L107" s="13" t="s">
         <v>477</v>
-      </c>
-      <c r="L107" s="13" t="s">
-        <v>478</v>
       </c>
       <c r="M107" s="11"/>
       <c r="N107" s="11"/>
@@ -9460,7 +9516,7 @@
         <v>146</v>
       </c>
       <c r="S107" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="T107" s="12">
         <v>54</v>
@@ -9477,16 +9533,16 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B108" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="C108" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="C108" s="11" t="s">
-        <v>471</v>
-      </c>
       <c r="D108" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E108" s="11" t="s">
         <v>45</v>
@@ -9498,10 +9554,10 @@
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
       <c r="J108" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="L108" s="13" t="s">
         <v>481</v>
-      </c>
-      <c r="L108" s="13" t="s">
-        <v>482</v>
       </c>
       <c r="M108" s="11"/>
       <c r="N108" s="11"/>
@@ -9512,7 +9568,7 @@
         <v>30</v>
       </c>
       <c r="S108" s="14" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T108" s="12">
         <v>11</v>
@@ -9529,16 +9585,16 @@
     </row>
     <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B109" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="C109" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="C109" s="11" t="s">
-        <v>471</v>
-      </c>
       <c r="D109" s="12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>45</v>
@@ -9550,10 +9606,10 @@
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
       <c r="J109" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="L109" s="13" t="s">
         <v>485</v>
-      </c>
-      <c r="L109" s="13" t="s">
-        <v>486</v>
       </c>
       <c r="M109" s="11"/>
       <c r="N109" s="11"/>
@@ -9564,7 +9620,7 @@
         <v>30</v>
       </c>
       <c r="S109" s="14" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T109" s="12">
         <v>13</v>
@@ -9581,28 +9637,28 @@
     </row>
     <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="D110" s="6" t="s">
         <v>489</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>490</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F110" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J110" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="J110" s="2" t="s">
+      <c r="L110" s="10" t="s">
         <v>492</v>
-      </c>
-      <c r="L110" s="10" t="s">
-        <v>493</v>
       </c>
       <c r="R110" s="5" t="s">
         <v>182</v>
@@ -9625,16 +9681,16 @@
     </row>
     <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="D111" s="6" t="s">
         <v>489</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>490</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>45</v>
@@ -9643,10 +9699,10 @@
         <v>109</v>
       </c>
       <c r="J111" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="L111" s="10" t="s">
         <v>494</v>
-      </c>
-      <c r="L111" s="10" t="s">
-        <v>495</v>
       </c>
       <c r="R111" s="5" t="s">
         <v>30</v>
@@ -9669,28 +9725,28 @@
     </row>
     <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>489</v>
-      </c>
       <c r="D112" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="F112" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="J112" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="J112" s="2" t="s">
+      <c r="L112" s="10" t="s">
         <v>499</v>
-      </c>
-      <c r="L112" s="10" t="s">
-        <v>500</v>
       </c>
       <c r="R112" s="5" t="s">
         <v>30</v>
@@ -9713,32 +9769,32 @@
     </row>
     <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="C113" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>489</v>
-      </c>
       <c r="D113" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="E113" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="F113" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K113" s="5"/>
       <c r="L113" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="M113" s="5"/>
       <c r="N113" s="5"/>
@@ -9766,14 +9822,14 @@
     </row>
     <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C114" s="5"/>
       <c r="D114" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>136</v>
@@ -9785,11 +9841,11 @@
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K114" s="5"/>
       <c r="L114" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M114" s="5"/>
       <c r="N114" s="5"/>
@@ -9800,7 +9856,7 @@
         <v>30</v>
       </c>
       <c r="S114" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T114" s="6">
         <v>99</v>
@@ -9817,10 +9873,10 @@
     </row>
     <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="6" t="s">
@@ -9836,11 +9892,11 @@
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K115" s="5"/>
       <c r="L115" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M115" s="5"/>
       <c r="N115" s="5"/>
@@ -9851,7 +9907,7 @@
         <v>30</v>
       </c>
       <c r="S115" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T115" s="6">
         <v>42</v>
@@ -9868,14 +9924,14 @@
     </row>
     <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C116" s="5"/>
       <c r="D116" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>73</v>
@@ -9887,11 +9943,11 @@
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K116" s="5"/>
       <c r="L116" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M116" s="5"/>
       <c r="N116" s="5"/>
@@ -9902,7 +9958,7 @@
         <v>30</v>
       </c>
       <c r="S116" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T116" s="6">
         <v>20</v>
@@ -9919,30 +9975,30 @@
     </row>
     <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C117" s="5"/>
       <c r="D117" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E117" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="F117" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K117" s="5"/>
       <c r="L117" s="34" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M117" s="5"/>
       <c r="N117" s="5"/>
@@ -9953,7 +10009,7 @@
         <v>182</v>
       </c>
       <c r="S117" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T117" s="6">
         <v>22</v>
@@ -9970,10 +10026,10 @@
     </row>
     <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C118" s="5"/>
       <c r="D118" s="6">
@@ -9989,11 +10045,11 @@
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K118" s="5"/>
       <c r="L118" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M118" s="5"/>
       <c r="N118" s="5"/>
@@ -10004,7 +10060,7 @@
         <v>30</v>
       </c>
       <c r="S118" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T118" s="6">
         <v>31</v>
@@ -10021,10 +10077,10 @@
     </row>
     <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="6" t="s">
@@ -10040,11 +10096,11 @@
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K119" s="5"/>
       <c r="L119" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M119" s="5"/>
       <c r="N119" s="5"/>
@@ -10055,7 +10111,7 @@
         <v>30</v>
       </c>
       <c r="S119" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T119" s="6">
         <v>40</v>
@@ -10072,10 +10128,10 @@
     </row>
     <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="6" t="s">
@@ -10091,11 +10147,11 @@
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K120" s="5"/>
       <c r="L120" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M120" s="5"/>
       <c r="N120" s="5"/>
@@ -10106,7 +10162,7 @@
         <v>30</v>
       </c>
       <c r="S120" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T120" s="6">
         <v>23</v>
@@ -10123,10 +10179,10 @@
     </row>
     <row r="121" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="6" t="s">
@@ -10142,11 +10198,11 @@
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K121" s="5"/>
       <c r="L121" s="34" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M121" s="5"/>
       <c r="N121" s="5"/>
@@ -10157,7 +10213,7 @@
         <v>30</v>
       </c>
       <c r="S121" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="T121" s="6">
         <v>20</v>
@@ -10174,30 +10230,30 @@
     </row>
     <row r="122" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>118</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K122" s="5"/>
       <c r="L122" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M122" s="5"/>
       <c r="N122" s="5"/>
@@ -10225,30 +10281,30 @@
     </row>
     <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>118</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K123" s="5"/>
       <c r="L123" s="8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M123" s="5"/>
       <c r="N123" s="5"/>
@@ -10276,30 +10332,30 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>118</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K124" s="5"/>
       <c r="L124" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
@@ -10327,30 +10383,30 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="C125" s="5"/>
       <c r="D125" s="6" t="s">
         <v>372</v>
       </c>
       <c r="E125" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="F125" s="5" t="s">
         <v>545</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>546</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K125" s="5"/>
       <c r="L125" s="8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M125" s="5"/>
       <c r="N125" s="5"/>
@@ -10378,13 +10434,13 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="D126" s="6" t="s">
         <v>550</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>551</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>45</v>
@@ -10393,10 +10449,10 @@
         <v>51</v>
       </c>
       <c r="J126" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="L126" s="10" t="s">
         <v>552</v>
-      </c>
-      <c r="L126" s="10" t="s">
-        <v>553</v>
       </c>
       <c r="R126" s="5" t="s">
         <v>30</v>
@@ -10419,13 +10475,13 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="D127" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>45</v>
@@ -10434,10 +10490,10 @@
         <v>51</v>
       </c>
       <c r="J127" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="L127" s="10" t="s">
         <v>555</v>
-      </c>
-      <c r="L127" s="10" t="s">
-        <v>556</v>
       </c>
       <c r="R127" s="5" t="s">
         <v>30</v>
@@ -10460,13 +10516,13 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="D128" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>45</v>
@@ -10475,10 +10531,10 @@
         <v>51</v>
       </c>
       <c r="J128" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="L128" s="10" t="s">
         <v>558</v>
-      </c>
-      <c r="L128" s="10" t="s">
-        <v>559</v>
       </c>
       <c r="R128" s="5" t="s">
         <v>30</v>
@@ -10501,30 +10557,30 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>550</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="6">
         <v>1882</v>
       </c>
       <c r="E129" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>560</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>561</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K129" s="5"/>
       <c r="L129" s="8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M129" s="5"/>
       <c r="N129" s="5"/>
@@ -10532,7 +10588,7 @@
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
       <c r="R129" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="S129" s="5" t="s">
         <v>282</v>
@@ -10552,25 +10608,25 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="D130" s="6">
         <v>1817</v>
       </c>
       <c r="E130" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="J130" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="J130" s="2" t="s">
+      <c r="L130" s="7" t="s">
         <v>569</v>
-      </c>
-      <c r="L130" s="7" t="s">
-        <v>570</v>
       </c>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
@@ -10595,25 +10651,25 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="D131" s="6">
         <v>1826</v>
       </c>
       <c r="E131" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="F131" s="2" t="s">
+      <c r="J131" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="L131" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="J131" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="L131" s="7" t="s">
-        <v>573</v>
       </c>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -10638,10 +10694,10 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>275</v>
@@ -10650,13 +10706,13 @@
         <v>45</v>
       </c>
       <c r="F132" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="J132" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="J132" s="2" t="s">
+      <c r="L132" s="10" t="s">
         <v>577</v>
-      </c>
-      <c r="L132" s="10" t="s">
-        <v>578</v>
       </c>
       <c r="R132" s="5" t="s">
         <v>30</v>
@@ -10679,25 +10735,25 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="D133" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>208</v>
       </c>
       <c r="J133" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L133" s="10" t="s">
         <v>581</v>
-      </c>
-      <c r="L133" s="10" t="s">
-        <v>582</v>
       </c>
       <c r="R133" s="5" t="s">
         <v>30</v>
@@ -10720,31 +10776,31 @@
     </row>
     <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>339</v>
       </c>
       <c r="E134" t="s">
+        <v>582</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="J134" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="J134" s="2" t="s">
+      <c r="L134" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="L134" s="10" t="s">
+      <c r="R134" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S134" s="5" t="s">
         <v>586</v>
-      </c>
-      <c r="R134" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S134" s="5" t="s">
-        <v>587</v>
       </c>
       <c r="T134" s="6">
         <v>450</v>
@@ -10761,25 +10817,25 @@
     </row>
     <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="D135" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F135" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="J135" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="L135" s="10" t="s">
         <v>590</v>
-      </c>
-      <c r="L135" s="10" t="s">
-        <v>591</v>
       </c>
       <c r="R135" s="5" t="s">
         <v>30</v>
@@ -10802,10 +10858,10 @@
     </row>
     <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>592</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>593</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="6">
@@ -10815,17 +10871,17 @@
         <v>73</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K136" s="5"/>
       <c r="L136" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="M136" s="5"/>
       <c r="N136" s="5"/>
@@ -10836,7 +10892,7 @@
         <v>30</v>
       </c>
       <c r="S136" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="T136" s="6">
         <v>68</v>
@@ -10853,28 +10909,28 @@
     </row>
     <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="F137" s="35" t="s">
         <v>598</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="F137" s="35" t="s">
-        <v>599</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
       <c r="J137" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="L137" s="34" t="s">
         <v>600</v>
-      </c>
-      <c r="L137" s="34" t="s">
-        <v>601</v>
       </c>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
@@ -10902,10 +10958,10 @@
     </row>
     <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>592</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>593</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="6">
@@ -10921,11 +10977,11 @@
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K138" s="5"/>
       <c r="L138" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M138" s="5"/>
       <c r="N138" s="5"/>
@@ -10953,25 +11009,25 @@
     </row>
     <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>592</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>593</v>
       </c>
       <c r="D139" s="6">
         <v>1912</v>
       </c>
       <c r="E139" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="J139" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="J139" s="2" t="s">
+      <c r="L139" s="34" t="s">
         <v>606</v>
-      </c>
-      <c r="L139" s="34" t="s">
-        <v>607</v>
       </c>
       <c r="R139" s="5" t="s">
         <v>30</v>
@@ -10994,10 +11050,10 @@
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="6">
@@ -11013,11 +11069,11 @@
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K140" s="5"/>
       <c r="L140" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="M140" s="5"/>
       <c r="N140" s="5"/>
@@ -11028,7 +11084,7 @@
         <v>30</v>
       </c>
       <c r="S140" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="T140" s="6">
         <v>155</v>
@@ -11045,30 +11101,30 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C141" s="5"/>
       <c r="D141" s="6">
         <v>1887</v>
       </c>
       <c r="E141" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="F141" s="5" t="s">
         <v>613</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>614</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K141" s="5"/>
       <c r="L141" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M141" s="5"/>
       <c r="N141" s="5"/>
@@ -11096,17 +11152,17 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="6">
         <v>1897</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>208</v>
@@ -11115,11 +11171,11 @@
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K142" s="5"/>
       <c r="L142" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="M142" s="5"/>
       <c r="N142" s="5"/>
@@ -11127,7 +11183,7 @@
       <c r="P142" s="5"/>
       <c r="Q142" s="5"/>
       <c r="R142" s="5" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="S142" s="5" t="s">
         <v>301</v>
@@ -11147,30 +11203,30 @@
     </row>
     <row r="143" spans="1:23" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C143" s="5"/>
       <c r="D143" s="6">
         <v>1891</v>
       </c>
       <c r="E143" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="F143" s="5" t="s">
         <v>613</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>614</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K143" s="5"/>
       <c r="L143" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M143" s="5"/>
       <c r="N143" s="5"/>
@@ -11201,34 +11257,34 @@
         <v>200</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>336</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F144" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="G144" s="34" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J144" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="G144" s="34" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I144" s="10" t="s">
+      <c r="L144" s="34" t="s">
+        <v>1194</v>
+      </c>
+      <c r="R144" s="5" t="s">
+        <v>1193</v>
+      </c>
+      <c r="S144" s="5" t="s">
         <v>625</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="L144" s="34" t="s">
-        <v>1197</v>
-      </c>
-      <c r="R144" s="5" t="s">
-        <v>1196</v>
-      </c>
-      <c r="S144" s="5" t="s">
-        <v>626</v>
       </c>
       <c r="T144" s="6">
         <v>243</v>
@@ -11248,27 +11304,27 @@
         <v>200</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C145" s="5"/>
       <c r="D145" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K145" s="5"/>
       <c r="L145" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M145" s="5"/>
       <c r="N145" s="5"/>
@@ -11299,27 +11355,27 @@
         <v>200</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C146" s="5"/>
       <c r="D146" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K146" s="5"/>
       <c r="L146" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M146" s="5"/>
       <c r="N146" s="5"/>
@@ -11350,27 +11406,27 @@
         <v>200</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C147" s="5"/>
       <c r="D147" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E147" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>604</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>605</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K147" s="5"/>
       <c r="L147" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M147" s="5"/>
       <c r="N147" s="5"/>
@@ -11401,27 +11457,27 @@
         <v>200</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C148" s="5"/>
       <c r="D148" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="F148" s="5" t="s">
         <v>635</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>636</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K148" s="5"/>
       <c r="L148" s="25" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="M148" s="5"/>
       <c r="N148" s="5"/>
@@ -11452,27 +11508,27 @@
         <v>200</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C149" s="5"/>
       <c r="D149" s="6">
         <v>1894</v>
       </c>
       <c r="E149" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>639</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>640</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K149" s="5"/>
       <c r="L149" s="34" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="M149" s="5"/>
       <c r="N149" s="5"/>
@@ -11483,7 +11539,7 @@
         <v>30</v>
       </c>
       <c r="S149" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="T149" s="6">
         <v>53</v>
@@ -11497,25 +11553,25 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="D150" s="6" t="s">
         <v>645</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="E150" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="F150" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="J150" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="J150" s="2" t="s">
+      <c r="L150" s="10" t="s">
         <v>649</v>
-      </c>
-      <c r="L150" s="10" t="s">
-        <v>650</v>
       </c>
       <c r="R150" s="5" t="s">
         <v>30</v>
@@ -11538,30 +11594,30 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>644</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>645</v>
       </c>
       <c r="C151" s="5"/>
       <c r="D151" s="6">
         <v>1854</v>
       </c>
       <c r="E151" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="F151" s="5" t="s">
         <v>651</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>652</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K151" s="5"/>
       <c r="L151" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M151" s="5"/>
       <c r="N151" s="5"/>
@@ -11589,30 +11645,30 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>644</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>645</v>
       </c>
       <c r="C152" s="5"/>
       <c r="D152" s="6">
         <v>1857</v>
       </c>
       <c r="E152" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="F152" s="5" t="s">
         <v>655</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>656</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K152" s="5"/>
       <c r="L152" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M152" s="5"/>
       <c r="N152" s="5"/>
@@ -11640,10 +11696,10 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B153" s="5" t="s">
         <v>644</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>645</v>
       </c>
       <c r="C153" s="5"/>
       <c r="D153" s="6">
@@ -11659,11 +11715,11 @@
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K153" s="5"/>
       <c r="L153" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="M153" s="5"/>
       <c r="N153" s="5"/>
@@ -11691,30 +11747,30 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>661</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>662</v>
       </c>
       <c r="C154" s="5"/>
       <c r="D154" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K154" s="5"/>
       <c r="L154" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="M154" s="5"/>
       <c r="N154" s="5"/>
@@ -11728,38 +11784,38 @@
         <v>31</v>
       </c>
       <c r="T154" s="6" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="W154" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>661</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>662</v>
       </c>
       <c r="C155" s="5"/>
       <c r="D155" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K155" s="5"/>
       <c r="L155" s="34" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="M155" s="5"/>
       <c r="N155" s="5"/>
@@ -11773,38 +11829,38 @@
         <v>31</v>
       </c>
       <c r="T155" s="6" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="W155" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>661</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>662</v>
       </c>
       <c r="C156" s="5"/>
       <c r="D156" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E156" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="K156" s="5"/>
       <c r="L156" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="M156" s="5"/>
       <c r="N156" s="5"/>
@@ -11812,44 +11868,44 @@
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
       <c r="R156" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="S156" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T156" s="6" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="W156" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>661</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>662</v>
       </c>
       <c r="C157" s="5"/>
       <c r="D157" s="6" t="s">
         <v>278</v>
       </c>
       <c r="E157" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="F157" s="5" t="s">
         <v>675</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>676</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="K157" s="5"/>
       <c r="L157" s="34" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="M157" s="5"/>
       <c r="N157" s="5"/>
@@ -11872,30 +11928,30 @@
         <v>500</v>
       </c>
       <c r="W157" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="D158" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="E158" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="J158" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="E158" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="J158" s="2" t="s">
+      <c r="L158" s="15" t="s">
         <v>681</v>
-      </c>
-      <c r="L158" s="15" t="s">
-        <v>682</v>
       </c>
       <c r="R158" s="5" t="s">
         <v>30</v>
@@ -11918,25 +11974,25 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E159" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="J159" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="J159" s="2" t="s">
+      <c r="L159" s="10" t="s">
         <v>685</v>
-      </c>
-      <c r="L159" s="10" t="s">
-        <v>686</v>
       </c>
       <c r="R159" s="5" t="s">
         <v>30</v>
@@ -11959,30 +12015,30 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>678</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>679</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="6">
         <v>1886</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
       <c r="J160" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K160" s="5"/>
       <c r="L160" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M160" s="5"/>
       <c r="N160" s="5"/>
@@ -12010,30 +12066,30 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>678</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>679</v>
       </c>
       <c r="C161" s="5"/>
       <c r="D161" s="6">
         <v>1890</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
       <c r="J161" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K161" s="5"/>
       <c r="L161" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M161" s="5"/>
       <c r="N161" s="5"/>
@@ -12061,30 +12117,30 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>692</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>693</v>
       </c>
       <c r="C162" s="5"/>
       <c r="D162" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="E162" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="F162" s="5" t="s">
         <v>695</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>696</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
       <c r="J162" s="5" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K162" s="5"/>
       <c r="L162" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M162" s="5"/>
       <c r="N162" s="5"/>
@@ -12095,7 +12151,7 @@
         <v>30</v>
       </c>
       <c r="S162" s="5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="T162" s="6">
         <v>78</v>
@@ -12112,30 +12168,30 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>692</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>693</v>
       </c>
       <c r="C163" s="5"/>
       <c r="D163" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E163" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>695</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>696</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
       <c r="J163" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="K163" s="5"/>
       <c r="L163" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M163" s="5"/>
       <c r="N163" s="5"/>
@@ -12163,30 +12219,30 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>692</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>693</v>
       </c>
       <c r="C164" s="5"/>
       <c r="D164" s="6" t="s">
         <v>189</v>
       </c>
       <c r="E164" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="F164" s="5" t="s">
         <v>695</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>696</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="K164" s="5"/>
       <c r="L164" s="8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="M164" s="5"/>
       <c r="N164" s="5"/>
@@ -12214,30 +12270,30 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="27" t="s">
+        <v>691</v>
+      </c>
+      <c r="B165" s="27" t="s">
         <v>692</v>
-      </c>
-      <c r="B165" s="27" t="s">
-        <v>693</v>
       </c>
       <c r="C165" s="27"/>
       <c r="D165" s="37" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E165" s="27" t="s">
+        <v>694</v>
+      </c>
+      <c r="F165" s="27" t="s">
         <v>695</v>
-      </c>
-      <c r="F165" s="27" t="s">
-        <v>696</v>
       </c>
       <c r="G165" s="27"/>
       <c r="H165" s="27"/>
       <c r="I165" s="27"/>
       <c r="J165" s="27" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K165" s="27"/>
       <c r="L165" s="36" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="M165" s="27"/>
       <c r="N165" s="27"/>
@@ -12265,32 +12321,32 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="27" t="s">
+        <v>691</v>
+      </c>
+      <c r="B166" s="27" t="s">
         <v>692</v>
-      </c>
-      <c r="B166" s="27" t="s">
-        <v>693</v>
       </c>
       <c r="C166" s="27"/>
       <c r="D166" s="37" t="s">
+        <v>707</v>
+      </c>
+      <c r="E166" s="27" t="s">
         <v>708</v>
       </c>
-      <c r="E166" s="27" t="s">
+      <c r="F166" s="27" t="s">
         <v>709</v>
-      </c>
-      <c r="F166" s="27" t="s">
-        <v>710</v>
       </c>
       <c r="G166" s="27"/>
       <c r="H166" s="27"/>
       <c r="I166" s="27"/>
       <c r="J166" s="27" t="s">
+        <v>710</v>
+      </c>
+      <c r="K166" s="27" t="s">
         <v>711</v>
       </c>
-      <c r="K166" s="27" t="s">
+      <c r="L166" s="34" t="s">
         <v>712</v>
-      </c>
-      <c r="L166" s="34" t="s">
-        <v>713</v>
       </c>
       <c r="M166" s="27"/>
       <c r="N166" s="27"/>
@@ -12301,7 +12357,7 @@
         <v>30</v>
       </c>
       <c r="S166" s="27" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="T166" s="37">
         <v>104</v>
@@ -12318,32 +12374,32 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="27" t="s">
+        <v>691</v>
+      </c>
+      <c r="B167" s="27" t="s">
         <v>692</v>
-      </c>
-      <c r="B167" s="27" t="s">
-        <v>693</v>
       </c>
       <c r="C167" s="27"/>
       <c r="D167" s="37" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E167" s="27" t="s">
         <v>156</v>
       </c>
       <c r="F167" s="27" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G167" s="27"/>
       <c r="H167" s="27"/>
       <c r="I167" s="27"/>
       <c r="J167" s="27" t="s">
+        <v>715</v>
+      </c>
+      <c r="K167" s="27" t="s">
         <v>716</v>
       </c>
-      <c r="K167" s="27" t="s">
+      <c r="L167" s="34" t="s">
         <v>717</v>
-      </c>
-      <c r="L167" s="34" t="s">
-        <v>718</v>
       </c>
       <c r="M167" s="27"/>
       <c r="N167" s="27"/>
@@ -12354,7 +12410,7 @@
         <v>30</v>
       </c>
       <c r="S167" s="27" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="T167" s="37">
         <v>64</v>
@@ -12371,14 +12427,14 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B168" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C168" s="5"/>
       <c r="D168" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>45</v>
@@ -12390,11 +12446,11 @@
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K168" s="5"/>
       <c r="L168" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="M168" s="5"/>
       <c r="N168" s="5"/>
@@ -12422,10 +12478,10 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C169" s="5"/>
       <c r="D169" s="6" t="s">
@@ -12441,11 +12497,11 @@
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
       <c r="J169" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="K169" s="5"/>
       <c r="L169" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="M169" s="5"/>
       <c r="N169" s="5"/>
@@ -12473,10 +12529,10 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C170" s="5"/>
       <c r="D170" s="6" t="s">
@@ -12492,11 +12548,11 @@
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="K170" s="5"/>
       <c r="L170" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M170" s="5"/>
       <c r="N170" s="5"/>
@@ -12524,10 +12580,10 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="6" t="s">
@@ -12543,11 +12599,11 @@
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="K171" s="5"/>
       <c r="L171" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M171" s="5"/>
       <c r="N171" s="5"/>
@@ -12575,14 +12631,14 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C172" s="5"/>
       <c r="D172" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E172" s="5" t="s">
         <v>45</v>
@@ -12594,11 +12650,11 @@
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K172" s="5"/>
       <c r="L172" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M172" s="5"/>
       <c r="N172" s="5"/>
@@ -12609,7 +12665,7 @@
         <v>30</v>
       </c>
       <c r="S172" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="T172" s="6">
         <v>130</v>
@@ -12626,14 +12682,14 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>45</v>
@@ -12645,11 +12701,11 @@
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K173" s="5"/>
       <c r="L173" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M173" s="5"/>
       <c r="N173" s="5"/>
@@ -12660,7 +12716,7 @@
         <v>30</v>
       </c>
       <c r="S173" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="T173" s="6">
         <v>136</v>
@@ -12677,30 +12733,30 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="29" t="s">
+        <v>736</v>
+      </c>
+      <c r="B174" s="29" t="s">
         <v>737</v>
-      </c>
-      <c r="B174" s="29" t="s">
-        <v>738</v>
       </c>
       <c r="C174" s="29"/>
       <c r="D174" s="31" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E174" s="29" t="s">
         <v>136</v>
       </c>
       <c r="F174" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G174" s="29"/>
       <c r="H174" s="29"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="K174" s="29"/>
       <c r="L174" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="M174" s="29"/>
       <c r="N174" s="29"/>
@@ -12728,10 +12784,10 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>737</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>738</v>
       </c>
       <c r="C175" s="5"/>
       <c r="D175" s="6" t="s">
@@ -12741,17 +12797,17 @@
         <v>136</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K175" s="5"/>
       <c r="L175" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M175" s="5"/>
       <c r="N175" s="5"/>
@@ -12779,30 +12835,30 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B176" s="5" t="s">
         <v>737</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>738</v>
       </c>
       <c r="C176" s="5"/>
       <c r="D176" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>136</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G176" s="5"/>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
       <c r="J176" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="K176" s="5"/>
       <c r="L176" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="M176" s="5"/>
       <c r="N176" s="5"/>
@@ -12830,30 +12886,30 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>737</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>738</v>
       </c>
       <c r="C177" s="5"/>
       <c r="D177" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="E177" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="F177" s="5" t="s">
         <v>750</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>751</v>
       </c>
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
       <c r="J177" s="5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="K177" s="5"/>
       <c r="L177" s="8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="M177" s="5"/>
       <c r="N177" s="5"/>
@@ -12881,10 +12937,10 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="C178" s="5"/>
       <c r="D178" s="6" t="s">
@@ -12900,11 +12956,11 @@
       <c r="H178" s="5"/>
       <c r="I178" s="5"/>
       <c r="J178" s="5" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="K178" s="5"/>
       <c r="L178" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M178" s="5"/>
       <c r="N178" s="5"/>
@@ -12932,10 +12988,10 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="C179" s="5"/>
       <c r="D179" s="6" t="s">
@@ -12945,17 +13001,17 @@
         <v>45</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G179" s="5"/>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
       <c r="J179" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K179" s="5"/>
       <c r="L179" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="M179" s="5"/>
       <c r="N179" s="5"/>
@@ -12983,14 +13039,14 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B180" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="C180" s="5"/>
       <c r="D180" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>45</v>
@@ -13002,11 +13058,11 @@
       <c r="H180" s="5"/>
       <c r="I180" s="5"/>
       <c r="J180" s="5" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="K180" s="5"/>
       <c r="L180" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="M180" s="5"/>
       <c r="N180" s="5"/>
@@ -13034,14 +13090,14 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="C181" s="5"/>
       <c r="D181" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>45</v>
@@ -13053,11 +13109,11 @@
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
       <c r="J181" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="K181" s="5"/>
       <c r="L181" s="8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="M181" s="5"/>
       <c r="N181" s="5"/>
@@ -13085,30 +13141,30 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C182" s="5"/>
       <c r="D182" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="E182" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="F182" s="5" t="s">
         <v>769</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>770</v>
       </c>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
       <c r="J182" s="5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K182" s="5"/>
       <c r="L182" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M182" s="5"/>
       <c r="N182" s="5"/>
@@ -13136,30 +13192,30 @@
     </row>
     <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C183" s="5"/>
       <c r="D183" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
       <c r="J183" s="5" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K183" s="5"/>
       <c r="L183" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="M183" s="5"/>
       <c r="N183" s="5"/>
@@ -13187,30 +13243,30 @@
     </row>
     <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B184" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C184" s="5"/>
       <c r="D184" s="6" t="s">
         <v>206</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G184" s="5"/>
       <c r="H184" s="5"/>
       <c r="I184" s="5"/>
       <c r="J184" s="5" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K184" s="5"/>
       <c r="L184" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="M184" s="5"/>
       <c r="N184" s="5"/>
@@ -13238,30 +13294,30 @@
     </row>
     <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C185" s="5"/>
       <c r="D185" s="6" t="s">
         <v>336</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G185" s="5"/>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
       <c r="J185" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K185" s="5"/>
       <c r="L185" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="M185" s="5"/>
       <c r="N185" s="5"/>
@@ -13289,30 +13345,30 @@
     </row>
     <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C186" s="5"/>
       <c r="D186" s="6">
         <v>1896</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G186" s="5"/>
       <c r="H186" s="5"/>
       <c r="I186" s="5"/>
       <c r="J186" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K186" s="5"/>
       <c r="L186" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="M186" s="5"/>
       <c r="N186" s="5"/>
@@ -13340,17 +13396,17 @@
     </row>
     <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C187" s="5"/>
       <c r="D187" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>208</v>
@@ -13359,11 +13415,11 @@
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
       <c r="J187" s="5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K187" s="5"/>
       <c r="L187" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="M187" s="5"/>
       <c r="N187" s="5"/>
@@ -13391,30 +13447,30 @@
     </row>
     <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B188" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C188" s="5"/>
       <c r="D188" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G188" s="5"/>
       <c r="H188" s="5"/>
       <c r="I188" s="5"/>
       <c r="J188" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K188" s="5"/>
       <c r="L188" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M188" s="5"/>
       <c r="N188" s="5"/>
@@ -13442,30 +13498,30 @@
     </row>
     <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B189" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="C189" s="5"/>
       <c r="D189" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G189" s="5"/>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
       <c r="J189" s="5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K189" s="5"/>
       <c r="L189" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="M189" s="5"/>
       <c r="N189" s="5"/>
@@ -13493,30 +13549,30 @@
     </row>
     <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B190" s="5" t="s">
         <v>790</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>791</v>
       </c>
       <c r="C190" s="5"/>
       <c r="D190" s="6">
         <v>1886</v>
       </c>
       <c r="E190" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="F190" s="5" t="s">
         <v>792</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>793</v>
       </c>
       <c r="G190" s="5"/>
       <c r="H190" s="5"/>
       <c r="I190" s="5"/>
       <c r="J190" s="5" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="K190" s="5"/>
       <c r="L190" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="M190" s="5"/>
       <c r="N190" s="5"/>
@@ -13544,17 +13600,17 @@
     </row>
     <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B191" s="5" t="s">
         <v>790</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>791</v>
       </c>
       <c r="C191" s="5"/>
       <c r="D191" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>208</v>
@@ -13563,11 +13619,11 @@
       <c r="H191" s="5"/>
       <c r="I191" s="5"/>
       <c r="J191" s="5" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="K191" s="5"/>
       <c r="L191" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M191" s="5"/>
       <c r="N191" s="5"/>
@@ -13595,30 +13651,30 @@
     </row>
     <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B192" s="5" t="s">
         <v>790</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>791</v>
       </c>
       <c r="C192" s="5"/>
       <c r="D192" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
       <c r="I192" s="5"/>
       <c r="J192" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K192" s="5"/>
       <c r="L192" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="M192" s="5"/>
       <c r="N192" s="5"/>
@@ -13629,7 +13685,7 @@
         <v>30</v>
       </c>
       <c r="S192" s="5" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="T192" s="6">
         <v>62</v>
@@ -13646,30 +13702,30 @@
     </row>
     <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B193" s="5" t="s">
         <v>790</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>791</v>
       </c>
       <c r="C193" s="5"/>
       <c r="D193" s="6" t="s">
         <v>339</v>
       </c>
       <c r="E193" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="F193" s="5" t="s">
         <v>802</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>803</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
       <c r="I193" s="5"/>
       <c r="J193" s="5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K193" s="5"/>
       <c r="L193" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M193" s="5"/>
       <c r="N193" s="5"/>
@@ -13697,14 +13753,14 @@
     </row>
     <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B194" s="5" t="s">
         <v>806</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="C194" s="5"/>
       <c r="D194" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E194" s="5" t="s">
         <v>45</v>
@@ -13716,11 +13772,11 @@
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
       <c r="J194" s="5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K194" s="5"/>
       <c r="L194" s="25" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M194" s="5"/>
       <c r="N194" s="5"/>
@@ -13748,30 +13804,30 @@
     </row>
     <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="B195" s="16" t="s">
         <v>806</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>807</v>
       </c>
       <c r="C195" s="16"/>
       <c r="D195" s="17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E195" s="17" t="s">
         <v>45</v>
       </c>
       <c r="F195" s="16" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G195" s="16"/>
       <c r="H195" s="16"/>
       <c r="I195" s="16"/>
       <c r="J195" s="16" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K195" s="16"/>
       <c r="L195" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M195" s="16"/>
       <c r="N195" s="16"/>
@@ -13799,17 +13855,17 @@
     </row>
     <row r="196" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B196" s="5" t="s">
         <v>806</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="C196" s="5"/>
       <c r="D196" s="6">
         <v>1908</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>208</v>
@@ -13818,11 +13874,11 @@
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
       <c r="J196" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K196" s="5"/>
       <c r="L196" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="M196" s="5"/>
       <c r="N196" s="5"/>
@@ -13850,17 +13906,17 @@
     </row>
     <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B197" s="5" t="s">
         <v>806</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="C197" s="5"/>
       <c r="D197" s="6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>208</v>
@@ -13869,11 +13925,11 @@
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
       <c r="J197" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K197" s="5"/>
       <c r="L197" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M197" s="5"/>
       <c r="N197" s="5"/>
@@ -13901,17 +13957,17 @@
     </row>
     <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B198" s="5" t="s">
         <v>806</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="C198" s="5"/>
       <c r="D198" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>208</v>
@@ -13920,11 +13976,11 @@
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
       <c r="J198" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K198" s="5"/>
       <c r="L198" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="M198" s="5"/>
       <c r="N198" s="5"/>
@@ -13952,30 +14008,30 @@
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B199" s="5" t="s">
         <v>806</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="C199" s="5"/>
       <c r="D199" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="E199" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="E199" s="5" t="s">
+      <c r="F199" s="5" t="s">
         <v>824</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>825</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
       <c r="J199" s="5" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K199" s="5"/>
       <c r="L199" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M199" s="5"/>
       <c r="N199" s="5"/>
@@ -14003,10 +14059,10 @@
     </row>
     <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="B200" s="5" t="s">
         <v>828</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>829</v>
       </c>
       <c r="C200" s="5"/>
       <c r="D200" s="6">
@@ -14022,11 +14078,11 @@
       <c r="H200" s="5"/>
       <c r="I200" s="5"/>
       <c r="J200" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K200" s="5"/>
       <c r="L200" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M200" s="5"/>
       <c r="N200" s="5"/>
@@ -14054,14 +14110,14 @@
     </row>
     <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="B201" s="5" t="s">
         <v>828</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>829</v>
       </c>
       <c r="C201" s="5"/>
       <c r="D201" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>73</v>
@@ -14073,11 +14129,11 @@
       <c r="H201" s="5"/>
       <c r="I201" s="5"/>
       <c r="J201" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K201" s="5"/>
       <c r="L201" s="8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M201" s="5"/>
       <c r="N201" s="5"/>
@@ -14105,30 +14161,30 @@
     </row>
     <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="B202" s="5" t="s">
         <v>828</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>829</v>
       </c>
       <c r="C202" s="5"/>
       <c r="D202" s="6">
         <v>1844</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
       <c r="I202" s="5"/>
       <c r="J202" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="K202" s="5"/>
       <c r="L202" s="8" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M202" s="5"/>
       <c r="N202" s="5"/>
@@ -14156,10 +14212,10 @@
     </row>
     <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="B203" s="5" t="s">
         <v>828</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>829</v>
       </c>
       <c r="C203" s="5"/>
       <c r="D203" s="6">
@@ -14169,17 +14225,17 @@
         <v>136</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
       <c r="I203" s="5"/>
       <c r="J203" s="5" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K203" s="5"/>
       <c r="L203" s="8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M203" s="5"/>
       <c r="N203" s="5"/>
@@ -14207,10 +14263,10 @@
     </row>
     <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B204" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C204" s="5"/>
       <c r="D204" s="6">
@@ -14226,11 +14282,11 @@
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
       <c r="J204" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K204" s="5"/>
       <c r="L204" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M204" s="5"/>
       <c r="N204" s="5"/>
@@ -14258,10 +14314,10 @@
     </row>
     <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C205" s="5"/>
       <c r="D205" s="6">
@@ -14277,11 +14333,11 @@
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
       <c r="J205" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="K205" s="5"/>
       <c r="L205" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M205" s="5"/>
       <c r="N205" s="5"/>
@@ -14309,10 +14365,10 @@
     </row>
     <row r="206" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B206" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C206" s="5"/>
       <c r="D206" s="6">
@@ -14328,11 +14384,11 @@
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
       <c r="J206" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K206" s="5"/>
       <c r="L206" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M206" s="5"/>
       <c r="N206" s="5"/>
@@ -14360,10 +14416,10 @@
     </row>
     <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B207" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C207" s="5"/>
       <c r="D207" s="6">
@@ -14379,11 +14435,11 @@
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
       <c r="J207" s="5" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="K207" s="5"/>
       <c r="L207" s="8" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="M207" s="5"/>
       <c r="N207" s="5"/>
@@ -14411,30 +14467,30 @@
     </row>
     <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B208" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C208" s="5"/>
       <c r="D208" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E208" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
       <c r="J208" s="5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K208" s="5"/>
       <c r="L208" s="34" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M208" s="5"/>
       <c r="N208" s="5"/>
@@ -14442,7 +14498,7 @@
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
       <c r="R208" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="S208" s="5" t="s">
         <v>233</v>
@@ -14462,10 +14518,10 @@
     </row>
     <row r="209" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B209" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C209" s="5"/>
       <c r="D209" s="6" t="s">
@@ -14481,11 +14537,11 @@
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
       <c r="J209" s="5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K209" s="5"/>
       <c r="L209" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M209" s="5"/>
       <c r="N209" s="5"/>
@@ -14513,34 +14569,34 @@
     </row>
     <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B210" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B210" s="2" t="s">
+      <c r="D210" s="6" t="s">
         <v>857</v>
-      </c>
-      <c r="D210" s="6" t="s">
-        <v>858</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F210" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="J210" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="J210" s="2" t="s">
+      <c r="L210" s="10" t="s">
         <v>860</v>
       </c>
-      <c r="L210" s="10" t="s">
-        <v>861</v>
-      </c>
       <c r="R210" s="5" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="S210" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T210" s="6" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="U210" s="6">
         <v>900</v>
@@ -14554,31 +14610,31 @@
     </row>
     <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>857</v>
-      </c>
       <c r="D211" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F211" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="J211" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="J211" s="2" t="s">
+      <c r="L211" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="L211" s="10" t="s">
+      <c r="R211" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="R211" s="5" t="s">
+      <c r="S211" s="5" t="s">
         <v>866</v>
-      </c>
-      <c r="S211" s="5" t="s">
-        <v>867</v>
       </c>
       <c r="T211" s="6">
         <v>166</v>
@@ -14595,28 +14651,28 @@
     </row>
     <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B212" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B212" s="2" t="s">
-        <v>857</v>
-      </c>
       <c r="D212" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="E212" s="2" t="s">
+      <c r="F212" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="F212" s="2" t="s">
+      <c r="J212" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="J212" s="2" t="s">
+      <c r="L212" s="10" t="s">
         <v>871</v>
       </c>
-      <c r="L212" s="10" t="s">
+      <c r="R212" s="5" t="s">
         <v>872</v>
-      </c>
-      <c r="R212" s="5" t="s">
-        <v>873</v>
       </c>
       <c r="S212" s="5" t="s">
         <v>31</v>
@@ -14636,28 +14692,28 @@
     </row>
     <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>857</v>
-      </c>
       <c r="D213" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E213" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="F213" s="2" t="s">
+      <c r="J213" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="J213" s="2" t="s">
+      <c r="L213" s="10" t="s">
         <v>876</v>
       </c>
-      <c r="L213" s="10" t="s">
+      <c r="R213" s="5" t="s">
         <v>877</v>
-      </c>
-      <c r="R213" s="5" t="s">
-        <v>878</v>
       </c>
       <c r="S213" s="5" t="s">
         <v>31</v>
@@ -14677,28 +14733,28 @@
     </row>
     <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>857</v>
-      </c>
       <c r="D214" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F214" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="J214" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="J214" s="2" t="s">
+      <c r="K214" t="s">
         <v>881</v>
       </c>
-      <c r="K214" t="s">
+      <c r="L214" s="34" t="s">
         <v>882</v>
-      </c>
-      <c r="L214" s="34" t="s">
-        <v>883</v>
       </c>
       <c r="R214" s="5" t="s">
         <v>166</v>
@@ -14707,7 +14763,7 @@
         <v>31</v>
       </c>
       <c r="T214" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="U214" s="6">
         <v>150</v>
@@ -14721,28 +14777,28 @@
     </row>
     <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>857</v>
-      </c>
       <c r="D215" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="E215" s="2" t="s">
+      <c r="F215" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="F215" s="2" t="s">
+      <c r="J215" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="J215" s="2" t="s">
+      <c r="K215" t="s">
         <v>888</v>
       </c>
-      <c r="K215" t="s">
+      <c r="L215" s="34" t="s">
         <v>889</v>
-      </c>
-      <c r="L215" s="34" t="s">
-        <v>890</v>
       </c>
       <c r="R215" s="5" t="s">
         <v>166</v>
@@ -14751,7 +14807,7 @@
         <v>31</v>
       </c>
       <c r="T215" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="U215" s="6">
         <v>450</v>
@@ -14768,10 +14824,10 @@
         <v>64</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>156</v>
@@ -14780,10 +14836,10 @@
         <v>168</v>
       </c>
       <c r="J216" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="L216" s="10" t="s">
         <v>893</v>
-      </c>
-      <c r="L216" s="10" t="s">
-        <v>894</v>
       </c>
       <c r="R216" s="5" t="s">
         <v>30</v>
@@ -14809,10 +14865,10 @@
         <v>64</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>45</v>
@@ -14821,10 +14877,10 @@
         <v>239</v>
       </c>
       <c r="J217" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="L217" s="10" t="s">
         <v>896</v>
-      </c>
-      <c r="L217" s="10" t="s">
-        <v>897</v>
       </c>
       <c r="R217" s="5" t="s">
         <v>30</v>
@@ -14850,22 +14906,22 @@
         <v>64</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D218" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="E218" s="2" t="s">
+      <c r="F218" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="J218" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="J218" s="2" t="s">
+      <c r="L218" s="10" t="s">
         <v>901</v>
-      </c>
-      <c r="L218" s="10" t="s">
-        <v>902</v>
       </c>
       <c r="R218" s="5" t="s">
         <v>30</v>
@@ -14891,10 +14947,10 @@
         <v>64</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>45</v>
@@ -14903,10 +14959,10 @@
         <v>239</v>
       </c>
       <c r="J219" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="L219" s="10" t="s">
         <v>903</v>
-      </c>
-      <c r="L219" s="10" t="s">
-        <v>904</v>
       </c>
       <c r="R219" s="5" t="s">
         <v>30</v>
@@ -14932,11 +14988,11 @@
         <v>64</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C220" s="5"/>
       <c r="D220" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>45</v>
@@ -14948,11 +15004,11 @@
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="K220" s="5"/>
       <c r="L220" s="25" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="M220" s="5"/>
       <c r="N220" s="5"/>
@@ -14983,7 +15039,7 @@
         <v>64</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C221" s="5"/>
       <c r="D221" s="6" t="s">
@@ -14999,11 +15055,11 @@
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K221" s="5"/>
       <c r="L221" s="25" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="M221" s="5"/>
       <c r="N221" s="5"/>
@@ -15034,7 +15090,7 @@
         <v>64</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C222" s="5"/>
       <c r="D222" s="6" t="s">
@@ -15050,11 +15106,11 @@
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="K222" s="5"/>
       <c r="L222" s="25" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M222" s="5"/>
       <c r="N222" s="5"/>
@@ -15085,7 +15141,7 @@
         <v>64</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C223" s="5"/>
       <c r="D223" s="6" t="s">
@@ -15101,11 +15157,11 @@
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="K223" s="5"/>
       <c r="L223" s="25" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="M223" s="5"/>
       <c r="N223" s="5"/>
@@ -15133,30 +15189,30 @@
     </row>
     <row r="224" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B224" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="B224" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="C224" s="5"/>
       <c r="D224" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E224" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="F224" s="5" t="s">
         <v>916</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>917</v>
       </c>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K224" s="5"/>
       <c r="L224" s="8" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="M224" s="5"/>
       <c r="N224" s="5"/>
@@ -15184,30 +15240,30 @@
     </row>
     <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B225" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="C225" s="5"/>
       <c r="D225" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E225" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="F225" s="5" t="s">
         <v>920</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>921</v>
       </c>
       <c r="G225" s="5"/>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K225" s="5"/>
       <c r="L225" s="8" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="M225" s="5"/>
       <c r="N225" s="5"/>
@@ -15218,7 +15274,7 @@
         <v>30</v>
       </c>
       <c r="S225" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T225" s="6">
         <v>23</v>
@@ -15235,10 +15291,10 @@
     </row>
     <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B226" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="C226" s="5"/>
       <c r="D226" s="6" t="s">
@@ -15248,17 +15304,17 @@
         <v>45</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="K226" s="5"/>
       <c r="L226" s="8" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="M226" s="5"/>
       <c r="N226" s="5"/>
@@ -15269,7 +15325,7 @@
         <v>182</v>
       </c>
       <c r="S226" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T226" s="6">
         <v>48</v>
@@ -15286,10 +15342,10 @@
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B227" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="C227" s="5"/>
       <c r="D227" s="6" t="s">
@@ -15305,11 +15361,11 @@
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="K227" s="5"/>
       <c r="L227" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M227" s="5"/>
       <c r="N227" s="5"/>
@@ -15320,7 +15376,7 @@
         <v>30</v>
       </c>
       <c r="S227" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T227" s="6">
         <v>23</v>
@@ -15337,32 +15393,32 @@
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B228" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="B228" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="C228" s="5"/>
       <c r="D228" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E228" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="F228" s="5" t="s">
         <v>929</v>
-      </c>
-      <c r="F228" s="5" t="s">
-        <v>930</v>
       </c>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="K228" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="K228" s="5" t="s">
+      <c r="L228" s="34" t="s">
         <v>932</v>
-      </c>
-      <c r="L228" s="34" t="s">
-        <v>933</v>
       </c>
       <c r="M228" s="5"/>
       <c r="N228" s="5"/>
@@ -15373,7 +15429,7 @@
         <v>30</v>
       </c>
       <c r="S228" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T228" s="6">
         <v>36</v>
@@ -15390,32 +15446,32 @@
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B229" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="C229" s="5"/>
       <c r="D229" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E229" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="F229" s="5" t="s">
         <v>929</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>930</v>
       </c>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="K229" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="K229" s="5" t="s">
+      <c r="L229" s="34" t="s">
         <v>936</v>
-      </c>
-      <c r="L229" s="34" t="s">
-        <v>937</v>
       </c>
       <c r="M229" s="5"/>
       <c r="N229" s="5"/>
@@ -15426,7 +15482,7 @@
         <v>30</v>
       </c>
       <c r="S229" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T229" s="6">
         <v>35</v>
@@ -15443,13 +15499,13 @@
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="D230" s="6" t="s">
         <v>938</v>
-      </c>
-      <c r="D230" s="6" t="s">
-        <v>939</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>45</v>
@@ -15458,10 +15514,10 @@
         <v>109</v>
       </c>
       <c r="J230" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="L230" s="10" t="s">
         <v>940</v>
-      </c>
-      <c r="L230" s="10" t="s">
-        <v>941</v>
       </c>
       <c r="R230" s="5" t="s">
         <v>30</v>
@@ -15484,30 +15540,30 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="19" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B231" s="19" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C231" s="19"/>
       <c r="D231" s="23" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E231" s="19" t="s">
+        <v>941</v>
+      </c>
+      <c r="F231" s="19" t="s">
         <v>942</v>
-      </c>
-      <c r="F231" s="19" t="s">
-        <v>943</v>
       </c>
       <c r="G231" s="19"/>
       <c r="H231" s="19"/>
       <c r="I231" s="19"/>
       <c r="J231" s="19" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="K231" s="19"/>
       <c r="L231" s="20" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="M231" s="21"/>
       <c r="N231" s="21"/>
@@ -15518,7 +15574,7 @@
         <v>30</v>
       </c>
       <c r="S231" s="22" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="T231" s="23">
         <v>82</v>
@@ -15535,13 +15591,13 @@
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>73</v>
@@ -15550,16 +15606,16 @@
         <v>271</v>
       </c>
       <c r="J232" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="L232" s="10" t="s">
         <v>948</v>
       </c>
-      <c r="L232" s="10" t="s">
+      <c r="M232" s="4" t="s">
         <v>949</v>
       </c>
-      <c r="M232" s="4" t="s">
+      <c r="N232" s="10" t="s">
         <v>950</v>
-      </c>
-      <c r="N232" s="10" t="s">
-        <v>951</v>
       </c>
       <c r="R232" s="5" t="s">
         <v>30</v>
@@ -15582,31 +15638,31 @@
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F233" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="J233" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="J233" s="2" t="s">
+      <c r="L233" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="M233" s="4" t="s">
         <v>953</v>
       </c>
-      <c r="L233" s="10" t="s">
-        <v>951</v>
-      </c>
-      <c r="M233" s="4" t="s">
+      <c r="N233" s="10" t="s">
         <v>954</v>
-      </c>
-      <c r="N233" s="10" t="s">
-        <v>955</v>
       </c>
       <c r="R233" s="5" t="s">
         <v>182</v>
@@ -15629,25 +15685,25 @@
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F234" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="J234" s="2" t="s">
         <v>957</v>
       </c>
-      <c r="J234" s="2" t="s">
+      <c r="L234" s="10" t="s">
         <v>958</v>
-      </c>
-      <c r="L234" s="10" t="s">
-        <v>959</v>
       </c>
       <c r="R234" s="5" t="s">
         <v>30</v>
@@ -15670,25 +15726,25 @@
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E235" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="F235" s="2" t="s">
+      <c r="J235" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="J235" s="2" t="s">
+      <c r="L235" s="10" t="s">
         <v>962</v>
-      </c>
-      <c r="L235" s="10" t="s">
-        <v>963</v>
       </c>
       <c r="R235" s="5" t="s">
         <v>30</v>
@@ -15711,10 +15767,10 @@
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C236" s="5"/>
       <c r="D236" s="6">
@@ -15724,17 +15780,17 @@
         <v>45</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="K236" s="5"/>
       <c r="L236" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="M236" s="5"/>
       <c r="N236" s="5"/>
@@ -15762,17 +15818,17 @@
     </row>
     <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C237" s="5"/>
       <c r="D237" s="6">
         <v>1848</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>208</v>
@@ -15781,11 +15837,11 @@
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K237" s="5"/>
       <c r="L237" s="8" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="M237" s="5"/>
       <c r="N237" s="5"/>
@@ -15813,10 +15869,10 @@
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>970</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>339</v>
@@ -15825,13 +15881,13 @@
         <v>322</v>
       </c>
       <c r="F238" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="J238" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="J238" s="2" t="s">
+      <c r="L238" s="10" t="s">
         <v>972</v>
-      </c>
-      <c r="L238" s="10" t="s">
-        <v>973</v>
       </c>
       <c r="R238" s="5" t="s">
         <v>182</v>
@@ -15851,10 +15907,10 @@
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>970</v>
       </c>
       <c r="D239" s="6" t="s">
         <v>336</v>
@@ -15866,10 +15922,10 @@
         <v>271</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L239" s="10" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="R239" s="5" t="s">
         <v>30</v>
@@ -15892,25 +15948,25 @@
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>970</v>
-      </c>
       <c r="D240" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E240" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="F240" s="2" t="s">
+      <c r="J240" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="J240" s="2" t="s">
+      <c r="L240" s="10" t="s">
         <v>977</v>
-      </c>
-      <c r="L240" s="10" t="s">
-        <v>978</v>
       </c>
       <c r="R240" s="5" t="s">
         <v>30</v>
@@ -15933,25 +15989,25 @@
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B241" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>970</v>
-      </c>
       <c r="D241" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E241" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="F241" s="2" t="s">
+      <c r="J241" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="J241" s="2" t="s">
+      <c r="L241" s="10" t="s">
         <v>981</v>
-      </c>
-      <c r="L241" s="10" t="s">
-        <v>982</v>
       </c>
       <c r="R241" s="5" t="s">
         <v>30</v>
@@ -15974,30 +16030,34 @@
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="B242" s="5" t="s">
         <v>969</v>
-      </c>
-      <c r="B242" s="5" t="s">
-        <v>970</v>
       </c>
       <c r="C242" s="5"/>
       <c r="D242" s="6" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>984</v>
-      </c>
-      <c r="G242" s="5"/>
+        <v>983</v>
+      </c>
+      <c r="G242" s="34" t="s">
+        <v>1215</v>
+      </c>
       <c r="H242" s="5"/>
-      <c r="I242" s="5"/>
+      <c r="I242" s="34" t="s">
+        <v>1214</v>
+      </c>
       <c r="J242" s="5" t="s">
-        <v>985</v>
+        <v>1212</v>
       </c>
       <c r="K242" s="5"/>
       <c r="L242" s="25" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="M242" s="5"/>
       <c r="N242" s="5"/>
@@ -16005,7 +16065,7 @@
       <c r="P242" s="5"/>
       <c r="Q242" s="5"/>
       <c r="R242" s="5" t="s">
-        <v>30</v>
+        <v>1213</v>
       </c>
       <c r="S242" s="5" t="s">
         <v>301</v>
@@ -16025,10 +16085,10 @@
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="B243" s="5" t="s">
         <v>969</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>970</v>
       </c>
       <c r="C243" s="5"/>
       <c r="D243" s="6" t="s">
@@ -16038,19 +16098,19 @@
         <v>136</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G243" s="5"/>
       <c r="H243" s="5"/>
       <c r="I243" s="5"/>
       <c r="J243" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="K243" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="L243" s="34" t="s">
         <v>988</v>
-      </c>
-      <c r="K243" s="5" t="s">
-        <v>989</v>
-      </c>
-      <c r="L243" s="34" t="s">
-        <v>990</v>
       </c>
       <c r="M243" s="5"/>
       <c r="N243" s="5"/>
@@ -16061,7 +16121,7 @@
         <v>63</v>
       </c>
       <c r="S243" s="5" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="T243" s="6">
         <v>180</v>
@@ -16078,30 +16138,30 @@
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C244" s="5"/>
       <c r="D244" s="6">
         <v>1888</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G244" s="5"/>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
       <c r="J244" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="K244" s="5"/>
       <c r="L244" s="8" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="M244" s="5"/>
       <c r="N244" s="5"/>
@@ -16129,30 +16189,30 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C245" s="5"/>
       <c r="D245" s="6">
         <v>1878</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G245" s="5"/>
       <c r="H245" s="5"/>
       <c r="I245" s="5"/>
       <c r="J245" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="K245" s="5"/>
       <c r="L245" s="8" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="M245" s="5"/>
       <c r="N245" s="5"/>
@@ -16180,30 +16240,30 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C246" s="5"/>
       <c r="D246" s="6">
         <v>1899</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G246" s="5"/>
       <c r="H246" s="5"/>
       <c r="I246" s="5"/>
       <c r="J246" s="5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="K246" s="5"/>
       <c r="L246" s="8" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="M246" s="5"/>
       <c r="N246" s="5"/>
@@ -16231,30 +16291,30 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C247" s="5"/>
       <c r="D247" s="6">
         <v>1891</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G247" s="5"/>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="K247" s="5"/>
       <c r="L247" s="8" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="M247" s="5"/>
       <c r="N247" s="5"/>
@@ -16282,34 +16342,34 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C248" s="5"/>
       <c r="D248" s="6" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F248" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G248" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="G248" s="25" t="s">
-        <v>1011</v>
       </c>
       <c r="H248" s="5"/>
       <c r="I248" s="34" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="J248" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="K248" s="5"/>
       <c r="L248" s="34" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="M248" s="5"/>
       <c r="N248" s="5"/>
@@ -16317,10 +16377,10 @@
       <c r="P248" s="5"/>
       <c r="Q248" s="5"/>
       <c r="R248" s="5" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="S248" s="5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="T248" s="6">
         <v>730</v>
@@ -16337,34 +16397,34 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C249" s="5"/>
       <c r="D249" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="G249" s="34" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="H249" s="5"/>
       <c r="I249" s="34" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="K249" s="5"/>
       <c r="L249" s="8" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="M249" s="5"/>
       <c r="N249" s="5"/>
@@ -16372,7 +16432,7 @@
       <c r="P249" s="5"/>
       <c r="Q249" s="5"/>
       <c r="R249" s="5" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="S249" s="5" t="s">
         <v>31</v>
@@ -16392,30 +16452,30 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C250" s="5"/>
       <c r="D250" s="6" t="s">
         <v>189</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G250" s="5"/>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="K250" s="5"/>
       <c r="L250" s="8" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="M250" s="5"/>
       <c r="N250" s="5"/>
@@ -16426,7 +16486,7 @@
         <v>30</v>
       </c>
       <c r="S250" s="5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="T250" s="6">
         <v>1463</v>
@@ -16443,30 +16503,30 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C251" s="5"/>
       <c r="D251" s="6" t="s">
         <v>195</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G251" s="5"/>
       <c r="H251" s="5"/>
       <c r="I251" s="5"/>
       <c r="J251" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="K251" s="5"/>
       <c r="L251" s="8" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M251" s="5"/>
       <c r="N251" s="5"/>
@@ -16494,30 +16554,30 @@
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C252" s="5"/>
       <c r="D252" s="6">
         <v>1881</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G252" s="5"/>
       <c r="H252" s="5"/>
       <c r="I252" s="5"/>
       <c r="J252" s="5" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="K252" s="5"/>
       <c r="L252" s="8" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="M252" s="5"/>
       <c r="N252" s="5"/>
@@ -16545,30 +16605,30 @@
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C253" s="5"/>
       <c r="D253" s="6">
         <v>1878</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="G253" s="5"/>
       <c r="H253" s="5"/>
       <c r="I253" s="5"/>
       <c r="J253" s="5" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="K253" s="5"/>
       <c r="L253" s="8" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="M253" s="5"/>
       <c r="N253" s="5"/>
@@ -16596,30 +16656,30 @@
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C254" s="5"/>
       <c r="D254" s="6">
         <v>1886</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G254" s="5"/>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
       <c r="J254" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="K254" s="5"/>
       <c r="L254" s="8" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="M254" s="5"/>
       <c r="N254" s="5"/>
@@ -16647,30 +16707,30 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C255" s="5"/>
       <c r="D255" s="6">
         <v>1888</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
       <c r="I255" s="5"/>
       <c r="J255" s="5" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="K255" s="5"/>
       <c r="L255" s="8" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="M255" s="5"/>
       <c r="N255" s="5"/>
@@ -16698,30 +16758,30 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C256" s="5"/>
       <c r="D256" s="6" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G256" s="5"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
       <c r="J256" s="5" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="K256" s="5"/>
       <c r="L256" s="8" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="M256" s="5"/>
       <c r="N256" s="5"/>
@@ -16749,30 +16809,30 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C257" s="5"/>
       <c r="D257" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
       <c r="J257" s="5" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="K257" s="5"/>
       <c r="L257" s="8" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="M257" s="5"/>
       <c r="N257" s="5"/>
@@ -16800,30 +16860,30 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C258" s="5"/>
       <c r="D258" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E258" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F258" s="5" t="s">
         <v>1047</v>
-      </c>
-      <c r="E258" s="5" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F258" s="5" t="s">
-        <v>1049</v>
       </c>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
       <c r="J258" s="5" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="K258" s="5"/>
       <c r="L258" s="8" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="M258" s="5"/>
       <c r="N258" s="5"/>
@@ -16834,7 +16894,7 @@
         <v>182</v>
       </c>
       <c r="S258" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="T258" s="6">
         <v>600</v>
@@ -16851,30 +16911,30 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C259" s="5"/>
       <c r="D259" s="6" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
       <c r="J259" s="5" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="K259" s="5"/>
       <c r="L259" s="8" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="M259" s="5"/>
       <c r="N259" s="5"/>
@@ -16882,7 +16942,7 @@
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
       <c r="R259" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="S259" s="5" t="s">
         <v>35</v>
@@ -16902,30 +16962,30 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C260" s="5"/>
       <c r="D260" s="6" t="s">
         <v>258</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
       <c r="J260" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="K260" s="5"/>
       <c r="L260" s="8" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="M260" s="5"/>
       <c r="N260" s="5"/>
@@ -16953,30 +17013,32 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C261" s="5"/>
       <c r="D261" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
-      <c r="I261" s="5"/>
+      <c r="I261" s="34" t="s">
+        <v>1206</v>
+      </c>
       <c r="J261" s="5" t="s">
-        <v>1062</v>
+        <v>1205</v>
       </c>
       <c r="K261" s="5"/>
       <c r="L261" s="8" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="M261" s="5"/>
       <c r="N261" s="5"/>
@@ -16984,7 +17046,7 @@
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
       <c r="R261" s="5" t="s">
-        <v>30</v>
+        <v>1207</v>
       </c>
       <c r="S261" s="5" t="s">
         <v>31</v>
@@ -17004,30 +17066,30 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C262" s="5"/>
       <c r="D262" s="6" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
       <c r="J262" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="K262" s="5"/>
       <c r="L262" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="M262" s="5"/>
       <c r="N262" s="5"/>
@@ -17055,30 +17117,30 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="27" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B263" s="27" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C263" s="27"/>
       <c r="D263" s="37">
         <v>1831</v>
       </c>
       <c r="E263" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F263" s="27" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="G263" s="27"/>
       <c r="H263" s="27"/>
       <c r="I263" s="27"/>
       <c r="J263" s="27" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="K263" s="27"/>
       <c r="L263" s="36" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="M263" s="27"/>
       <c r="N263" s="27"/>
@@ -17086,7 +17148,7 @@
       <c r="P263" s="27"/>
       <c r="Q263" s="27"/>
       <c r="R263" s="27" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="S263" s="27" t="s">
         <v>35</v>
@@ -17106,10 +17168,10 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C264" s="5"/>
       <c r="D264" s="6">
@@ -17125,11 +17187,11 @@
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
       <c r="J264" s="5" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="K264" s="5"/>
       <c r="L264" s="8" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="M264" s="5"/>
       <c r="N264" s="5"/>
@@ -17157,10 +17219,10 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C265" s="5"/>
       <c r="D265" s="6">
@@ -17170,17 +17232,17 @@
         <v>26</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
       <c r="J265" s="5" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="K265" s="5"/>
       <c r="L265" s="8" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="M265" s="5"/>
       <c r="N265" s="5"/>
@@ -17188,13 +17250,13 @@
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
       <c r="R265" s="5" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="S265" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T265" s="3" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="U265" s="3">
         <v>580</v>
@@ -17208,30 +17270,30 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C266" s="5"/>
       <c r="D266" s="6">
         <v>1899</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
       <c r="J266" s="5" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="K266" s="5"/>
       <c r="L266" s="8" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="M266" s="5"/>
       <c r="N266" s="5"/>
@@ -17242,7 +17304,7 @@
         <v>30</v>
       </c>
       <c r="S266" s="5" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="T266" s="3">
         <v>49</v>
@@ -17259,30 +17321,30 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C267" s="5"/>
       <c r="D267" s="6">
         <v>1911</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
       <c r="I267" s="5"/>
       <c r="J267" s="5" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="K267" s="5"/>
       <c r="L267" s="8" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="M267" s="5"/>
       <c r="N267" s="5"/>
@@ -17310,30 +17372,30 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="29" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B268" s="29" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C268" s="29"/>
       <c r="D268" s="31">
         <v>1847</v>
       </c>
       <c r="E268" s="29" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="F268" s="29" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="G268" s="29"/>
       <c r="H268" s="29"/>
       <c r="I268" s="29"/>
       <c r="J268" s="29" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="K268" s="29"/>
       <c r="L268" s="30" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="M268" s="29"/>
       <c r="N268" s="29"/>
@@ -17361,30 +17423,30 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C269" s="5"/>
       <c r="D269" s="6">
         <v>1868</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
       <c r="J269" s="5" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="K269" s="5"/>
       <c r="L269" s="8" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="M269" s="5"/>
       <c r="N269" s="5"/>
@@ -17412,30 +17474,30 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C270" s="5"/>
       <c r="D270" s="6">
         <v>1882</v>
       </c>
       <c r="E270" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="F270" s="5" t="s">
         <v>545</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>546</v>
       </c>
       <c r="G270" s="5"/>
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
       <c r="J270" s="5" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="K270" s="5"/>
       <c r="L270" s="8" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="M270" s="5"/>
       <c r="N270" s="5"/>
@@ -17463,30 +17525,30 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C271" s="5"/>
       <c r="D271" s="6">
         <v>1856</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="G271" s="5"/>
       <c r="H271" s="5"/>
       <c r="I271" s="5"/>
       <c r="J271" s="5" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="K271" s="5"/>
       <c r="L271" s="8" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="M271" s="5"/>
       <c r="N271" s="5"/>
@@ -17514,30 +17576,30 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C272" s="5"/>
       <c r="D272" s="6">
         <v>1858</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="G272" s="5"/>
       <c r="H272" s="5"/>
       <c r="I272" s="5"/>
       <c r="J272" s="5" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="K272" s="5"/>
       <c r="L272" s="8" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="M272" s="5"/>
       <c r="N272" s="5"/>
@@ -17565,30 +17627,30 @@
     </row>
     <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C273" s="5"/>
       <c r="D273" s="6">
         <v>1862</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="G273" s="5"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5"/>
       <c r="J273" s="5" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="K273" s="5"/>
       <c r="L273" s="34" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="M273" s="5"/>
       <c r="N273" s="5"/>
@@ -17616,13 +17678,13 @@
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>156</v>
@@ -17631,10 +17693,10 @@
         <v>168</v>
       </c>
       <c r="J274" s="2" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="L274" s="10" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="R274" s="5" t="s">
         <v>30</v>
@@ -17657,37 +17719,37 @@
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="D275" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G275" s="34" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I275" s="34" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L275" s="10" t="s">
         <v>1112</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="F275" s="2" t="s">
+      <c r="R275" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="S275" s="5" t="s">
         <v>1113</v>
-      </c>
-      <c r="G275" s="34" t="s">
-        <v>1201</v>
-      </c>
-      <c r="I275" s="34" t="s">
-        <v>1200</v>
-      </c>
-      <c r="J275" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="L275" s="10" t="s">
-        <v>1115</v>
-      </c>
-      <c r="R275" s="5" t="s">
-        <v>1199</v>
-      </c>
-      <c r="S275" s="5" t="s">
-        <v>1116</v>
       </c>
       <c r="T275" s="6">
         <v>900</v>
@@ -17701,14 +17763,14 @@
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C276" s="5"/>
       <c r="D276" s="6" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="E276" s="5" t="s">
         <v>156</v>
@@ -17720,11 +17782,11 @@
       <c r="H276" s="5"/>
       <c r="I276" s="5"/>
       <c r="J276" s="5" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="K276" s="5"/>
       <c r="L276" s="8" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="M276" s="5"/>
       <c r="N276" s="5"/>
@@ -17752,30 +17814,30 @@
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C277" s="5"/>
       <c r="D277" s="6">
         <v>1897</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="G277" s="5"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
       <c r="J277" s="5" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="K277" s="5"/>
       <c r="L277" s="8" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="M277" s="5"/>
       <c r="N277" s="5"/>
@@ -17803,25 +17865,25 @@
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>136</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="L278" s="10" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="R278" s="5" t="s">
         <v>30</v>
@@ -17844,10 +17906,10 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C279" s="5"/>
       <c r="D279" s="6" t="s">
@@ -17857,17 +17919,17 @@
         <v>136</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G279" s="5"/>
       <c r="H279" s="5"/>
       <c r="I279" s="5"/>
       <c r="J279" s="5" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="K279" s="5"/>
       <c r="L279" s="8" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="M279" s="5"/>
       <c r="N279" s="5"/>
@@ -17895,30 +17957,30 @@
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C280" s="5"/>
       <c r="D280" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="G280" s="5"/>
       <c r="H280" s="5"/>
       <c r="I280" s="5"/>
       <c r="J280" s="5" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="K280" s="5"/>
       <c r="L280" s="8" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="M280" s="5"/>
       <c r="N280" s="5"/>
@@ -17946,30 +18008,30 @@
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C281" s="5"/>
       <c r="D281" s="6" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>322</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="G281" s="5"/>
       <c r="H281" s="5"/>
       <c r="I281" s="5"/>
       <c r="J281" s="5" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K281" s="5"/>
       <c r="L281" s="8" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="M281" s="5"/>
       <c r="N281" s="5"/>
@@ -17997,14 +18059,14 @@
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C282" s="5"/>
       <c r="D282" s="6" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>73</v>
@@ -18016,11 +18078,11 @@
       <c r="H282" s="5"/>
       <c r="I282" s="5"/>
       <c r="J282" s="5" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="K282" s="5"/>
       <c r="L282" s="8" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="M282" s="5"/>
       <c r="N282" s="5"/>
@@ -18048,30 +18110,30 @@
     </row>
     <row r="283" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C283" s="5"/>
       <c r="D283" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="G283" s="5"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
       <c r="J283" s="5" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="K283" s="5"/>
       <c r="L283" s="8" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M283" s="5"/>
       <c r="N283" s="5"/>
@@ -18099,14 +18161,14 @@
     </row>
     <row r="284" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C284" s="5"/>
       <c r="D284" s="6" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E284" s="5" t="s">
         <v>73</v>
@@ -18118,11 +18180,11 @@
       <c r="H284" s="5"/>
       <c r="I284" s="5"/>
       <c r="J284" s="5" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="K284" s="5"/>
       <c r="L284" s="8" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="M284" s="5"/>
       <c r="N284" s="5"/>
@@ -18150,10 +18212,10 @@
     </row>
     <row r="285" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C285" s="5"/>
       <c r="D285" s="6" t="s">
@@ -18169,11 +18231,11 @@
       <c r="H285" s="5"/>
       <c r="I285" s="5"/>
       <c r="J285" s="5" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="K285" s="5"/>
       <c r="L285" s="8" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="M285" s="5"/>
       <c r="N285" s="5"/>
@@ -18204,27 +18266,27 @@
         <v>404</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C286" s="5"/>
       <c r="D286" s="6">
         <v>1873</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="G286" s="5"/>
       <c r="H286" s="5"/>
       <c r="I286" s="5"/>
       <c r="J286" s="5" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="K286" s="5"/>
       <c r="L286" s="8" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="M286" s="5"/>
       <c r="N286" s="5"/>
@@ -18255,27 +18317,27 @@
         <v>404</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C287" s="5"/>
       <c r="D287" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
       <c r="I287" s="5"/>
       <c r="J287" s="5" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="K287" s="5"/>
       <c r="L287" s="8" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="M287" s="5"/>
       <c r="N287" s="5"/>
@@ -18306,27 +18368,27 @@
         <v>404</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C288" s="5"/>
       <c r="D288" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E288" s="5" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="G288" s="5"/>
       <c r="H288" s="5"/>
       <c r="I288" s="5"/>
       <c r="J288" s="5" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="K288" s="5"/>
       <c r="L288" s="8" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="M288" s="5"/>
       <c r="N288" s="5"/>
@@ -18357,27 +18419,27 @@
         <v>404</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C289" s="5"/>
       <c r="D289" s="6">
         <v>1878</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5"/>
       <c r="J289" s="5" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="K289" s="5"/>
       <c r="L289" s="8" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="M289" s="5"/>
       <c r="N289" s="5"/>
@@ -18496,7 +18558,7 @@
     <hyperlink ref="L89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
     <hyperlink ref="L90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
     <hyperlink ref="L91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="L92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
     <hyperlink ref="L93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
     <hyperlink ref="L94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
     <hyperlink ref="L95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
@@ -18710,6 +18772,15 @@
     <hyperlink ref="G249" r:id="rId302" xr:uid="{EEC2A50D-A275-496F-B1BA-33D9BEC8533F}"/>
     <hyperlink ref="L248" r:id="rId303" xr:uid="{02EEC5EC-4771-4F6C-8F1D-C4865393B0DA}"/>
     <hyperlink ref="I248" r:id="rId304" xr:uid="{6FB10617-44F6-4117-989F-986B637C80BA}"/>
+    <hyperlink ref="I261" r:id="rId305" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D838E2C-8FA1-4CD1-A8B9-FFFB38369124}"/>
+    <hyperlink ref="L92" r:id="rId306" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE04F37C-DA8D-4C44-8629-531DA028EFF3}"/>
+    <hyperlink ref="G92" r:id="rId307" xr:uid="{478F4210-B1A9-479A-88CB-34CA65A7DB24}"/>
+    <hyperlink ref="I242" r:id="rId308" xr:uid="{E2F907B4-2490-4105-8839-192C0B00A8BC}"/>
+    <hyperlink ref="G242" r:id="rId309" xr:uid="{8C6D563F-3B0B-4952-A62D-DD8F82458E4F}"/>
+    <hyperlink ref="I94" r:id="rId310" xr:uid="{85DE5E63-4AFC-4E51-AF27-A337B1571742}"/>
+    <hyperlink ref="G94" r:id="rId311" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DF7BF212-7779-47A4-83B7-AF2917EECFFC}"/>
+    <hyperlink ref="I49" r:id="rId312" xr:uid="{C89E209D-9483-4F74-AAF2-ED4B186D5B23}"/>
+    <hyperlink ref="G49" r:id="rId313" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{537B7F22-4511-405B-B10F-9A6222040DED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/quizzes/sculpture-19e_20e.xlsx
+++ b/quizzes/sculpture-19e_20e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FE1628-7CA2-451C-A4ED-3F77101E76EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D8F063-88DE-4CF1-B5F7-19677243166C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="1227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2623" uniqueCount="1229">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1777,9 +1777,6 @@
     <t>Henri</t>
   </si>
   <si>
-    <t>Gaudier-Brzeska</t>
-  </si>
-  <si>
     <t>Museum of Modern Art</t>
   </si>
   <si>
@@ -2368,9 +2365,6 @@
     <t>George</t>
   </si>
   <si>
-    <t>Minne</t>
-  </si>
-  <si>
     <t>Darmstadt</t>
   </si>
   <si>
@@ -2725,9 +2719,6 @@
     <t>Medardo</t>
   </si>
   <si>
-    <t>Rosso</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -3406,9 +3397,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/The_Libyan_Sibyl_by_William_Wetmore_Story_02.jpg/960px-The_Libyan_Sibyl_by_William_Wetmore_Story_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Woolner</t>
-  </si>
-  <si>
     <t>National Portrait Gallery</t>
   </si>
   <si>
@@ -3701,6 +3689,24 @@
   </si>
   <si>
     <t>Mémorial à Guillaume Tell</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg/1280px-Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>WOOLNER</t>
+  </si>
+  <si>
+    <t>ROSSO</t>
+  </si>
+  <si>
+    <t>MINNE</t>
+  </si>
+  <si>
+    <t>GAUDIER-BRZESKA</t>
+  </si>
+  <si>
+    <t>472 pour la statue, 400 pour le socle</t>
   </si>
 </sst>
 </file>
@@ -3766,7 +3772,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3815,6 +3821,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3823,7 +3864,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3919,6 +3960,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4245,7 +4310,8 @@
     <col min="17" max="17" width="7" style="2" customWidth="1"/>
     <col min="18" max="18" width="12.85546875" style="5" customWidth="1"/>
     <col min="19" max="19" width="14.85546875" style="5" customWidth="1"/>
-    <col min="20" max="21" width="9.140625" style="6" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="6" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" style="39" customWidth="1"/>
     <col min="22" max="22" width="8" style="6" customWidth="1"/>
     <col min="23" max="23" width="6.5703125" style="6" customWidth="1"/>
     <col min="24" max="24" width="24" customWidth="1"/>
@@ -4312,7 +4378,7 @@
       <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="39" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="6" t="s">
@@ -4322,7 +4388,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4358,7 +4424,7 @@
       <c r="T2" s="6">
         <v>147</v>
       </c>
-      <c r="U2" s="6">
+      <c r="U2" s="39">
         <v>100</v>
       </c>
       <c r="V2" s="6">
@@ -4401,7 +4467,7 @@
       <c r="T3" s="6">
         <v>132</v>
       </c>
-      <c r="U3" s="6">
+      <c r="U3" s="39">
         <v>100</v>
       </c>
       <c r="V3" s="6">
@@ -4444,7 +4510,7 @@
       <c r="T4" s="6">
         <v>173</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="39">
         <v>71</v>
       </c>
       <c r="V4" s="6">
@@ -4487,7 +4553,7 @@
       <c r="T5" s="6">
         <v>145</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="39">
         <v>85</v>
       </c>
       <c r="V5" s="6">
@@ -4530,7 +4596,7 @@
       <c r="T6" s="6">
         <v>252</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="39">
         <v>120</v>
       </c>
       <c r="V6" s="6">
@@ -4573,7 +4639,7 @@
       <c r="T7" s="6">
         <v>200</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U7" s="39">
         <v>85</v>
       </c>
       <c r="V7" s="6">
@@ -4616,7 +4682,7 @@
       <c r="T8" s="6">
         <v>210</v>
       </c>
-      <c r="U8" s="6">
+      <c r="U8" s="39">
         <v>85</v>
       </c>
       <c r="V8" s="6">
@@ -4662,7 +4728,7 @@
       <c r="T9" s="6">
         <v>180</v>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="39">
         <v>100</v>
       </c>
       <c r="V9" s="6">
@@ -4705,7 +4771,7 @@
       <c r="T10" s="6">
         <v>1056</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="39">
         <v>1906</v>
       </c>
       <c r="W10" s="6">
@@ -4745,10 +4811,10 @@
       <c r="T11" s="6">
         <v>4600</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="33">
         <v>1000</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="3">
         <v>1000</v>
       </c>
       <c r="W11" s="6">
@@ -4788,7 +4854,7 @@
       <c r="T12" s="6">
         <v>350</v>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="39">
         <v>300</v>
       </c>
       <c r="V12" s="6">
@@ -4815,7 +4881,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>84</v>
@@ -4831,7 +4897,7 @@
       <c r="T13" s="6">
         <v>240</v>
       </c>
-      <c r="U13" s="6">
+      <c r="U13" s="39">
         <v>80</v>
       </c>
       <c r="V13" s="6">
@@ -4858,10 +4924,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>88</v>
@@ -4872,7 +4938,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="R14" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="S14" s="5" t="s">
         <v>90</v>
@@ -4880,7 +4946,7 @@
       <c r="T14" s="6">
         <v>485</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U14" s="39">
         <v>1500</v>
       </c>
       <c r="V14" s="6">
@@ -4907,7 +4973,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>93</v>
@@ -4923,7 +4989,7 @@
       <c r="T15" s="6">
         <v>614</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U15" s="39">
         <v>547</v>
       </c>
       <c r="V15" s="6">
@@ -4966,7 +5032,7 @@
       <c r="T16" s="6">
         <v>240</v>
       </c>
-      <c r="U16" s="6">
+      <c r="U16" s="39">
         <v>90</v>
       </c>
       <c r="V16" s="6">
@@ -5001,15 +5067,15 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="R17" s="5" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>1147</v>
-      </c>
-      <c r="U17" s="6">
+        <v>1143</v>
+      </c>
+      <c r="U17" s="39">
         <v>450</v>
       </c>
       <c r="V17" s="6">
@@ -5060,7 +5126,7 @@
       <c r="T18" s="6">
         <v>86</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U18" s="39">
         <v>125</v>
       </c>
       <c r="V18" s="6">
@@ -5111,7 +5177,7 @@
       <c r="T19" s="6">
         <v>64</v>
       </c>
-      <c r="U19" s="6">
+      <c r="U19" s="39">
         <v>123</v>
       </c>
       <c r="V19" s="6">
@@ -5164,7 +5230,7 @@
       <c r="T20" s="6">
         <v>345</v>
       </c>
-      <c r="U20" s="6">
+      <c r="U20" s="39">
         <v>150</v>
       </c>
       <c r="V20" s="6">
@@ -5217,7 +5283,7 @@
       <c r="T21" s="6">
         <v>113</v>
       </c>
-      <c r="U21" s="6">
+      <c r="U21" s="39">
         <v>39</v>
       </c>
       <c r="W21" s="6">
@@ -5265,7 +5331,7 @@
       <c r="T22" s="6">
         <v>135</v>
       </c>
-      <c r="U22" s="6">
+      <c r="U22" s="39">
         <v>178</v>
       </c>
       <c r="V22" s="6">
@@ -5316,7 +5382,7 @@
       <c r="T23" s="6">
         <v>45</v>
       </c>
-      <c r="U23" s="6">
+      <c r="U23" s="39">
         <v>29</v>
       </c>
       <c r="V23" s="6">
@@ -5367,7 +5433,7 @@
       <c r="T24" s="6">
         <v>18</v>
       </c>
-      <c r="U24" s="6">
+      <c r="U24" s="39">
         <v>49</v>
       </c>
       <c r="V24" s="6">
@@ -5398,7 +5464,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="8" t="s">
@@ -5410,7 +5476,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="S25" s="5" t="s">
         <v>31</v>
@@ -5418,7 +5484,7 @@
       <c r="T25" s="6">
         <v>30</v>
       </c>
-      <c r="U25" s="6">
+      <c r="U25" s="39">
         <v>26</v>
       </c>
       <c r="V25" s="6">
@@ -5469,7 +5535,7 @@
       <c r="T26" s="6">
         <v>200</v>
       </c>
-      <c r="U26" s="6">
+      <c r="U26" s="39">
         <v>128</v>
       </c>
       <c r="V26" s="6">
@@ -5520,7 +5586,7 @@
       <c r="T27" s="6">
         <v>100</v>
       </c>
-      <c r="U27" s="6">
+      <c r="U27" s="39">
         <v>200</v>
       </c>
       <c r="V27" s="6">
@@ -5563,15 +5629,15 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>1146</v>
-      </c>
-      <c r="U28" s="6">
+        <v>1142</v>
+      </c>
+      <c r="U28" s="39">
         <v>235</v>
       </c>
       <c r="W28" s="6">
@@ -5619,7 +5685,7 @@
       <c r="T29" s="6">
         <v>51</v>
       </c>
-      <c r="U29" s="6">
+      <c r="U29" s="39">
         <v>69</v>
       </c>
       <c r="V29" s="6">
@@ -5672,7 +5738,7 @@
       <c r="T30" s="6">
         <v>295</v>
       </c>
-      <c r="U30" s="6">
+      <c r="U30" s="39">
         <v>200</v>
       </c>
       <c r="W30" s="6">
@@ -5694,14 +5760,14 @@
         <v>154</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="34" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>161</v>
@@ -5710,7 +5776,7 @@
         <v>162</v>
       </c>
       <c r="L31" s="34" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -5718,7 +5784,7 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="S31" s="5" t="s">
         <v>165</v>
@@ -5726,7 +5792,7 @@
       <c r="T31" s="6">
         <v>1000</v>
       </c>
-      <c r="U31" s="6">
+      <c r="U31" s="39">
         <v>1800</v>
       </c>
       <c r="W31" s="6">
@@ -5776,7 +5842,7 @@
       <c r="T32" s="6">
         <v>180</v>
       </c>
-      <c r="U32" s="6">
+      <c r="U32" s="39">
         <v>65</v>
       </c>
       <c r="V32" s="6">
@@ -5829,7 +5895,7 @@
       <c r="T33" s="6">
         <v>132</v>
       </c>
-      <c r="U33" s="6">
+      <c r="U33" s="39">
         <v>101</v>
       </c>
       <c r="V33" s="6">
@@ -5880,10 +5946,10 @@
       <c r="T34" s="37">
         <v>1800</v>
       </c>
-      <c r="U34" s="37">
+      <c r="U34" s="40">
         <v>6200</v>
       </c>
-      <c r="V34" s="37">
+      <c r="V34" s="6">
         <v>1200</v>
       </c>
       <c r="W34" s="37">
@@ -5933,7 +5999,7 @@
       <c r="T35" s="6">
         <v>102</v>
       </c>
-      <c r="U35" s="6">
+      <c r="U35" s="39">
         <v>25</v>
       </c>
       <c r="V35" s="6">
@@ -5986,7 +6052,7 @@
       <c r="T36" s="6">
         <v>305</v>
       </c>
-      <c r="U36" s="6">
+      <c r="U36" s="39">
         <v>1760</v>
       </c>
       <c r="V36" s="6">
@@ -6017,7 +6083,7 @@
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="K37" s="5" t="s">
         <v>195</v>
@@ -6039,7 +6105,7 @@
       <c r="T37" s="6">
         <v>2700</v>
       </c>
-      <c r="U37" s="6">
+      <c r="U37" s="39">
         <v>5800</v>
       </c>
       <c r="V37" s="6">
@@ -6090,10 +6156,10 @@
       <c r="T38" s="31">
         <v>68</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="41">
         <v>101</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="6">
         <v>53</v>
       </c>
       <c r="W38" s="31">
@@ -6141,7 +6207,7 @@
       <c r="T39" s="6">
         <v>67</v>
       </c>
-      <c r="U39" s="6">
+      <c r="U39" s="39">
         <v>47</v>
       </c>
       <c r="V39" s="6">
@@ -6192,7 +6258,7 @@
       <c r="T40" s="6">
         <v>86</v>
       </c>
-      <c r="U40" s="6">
+      <c r="U40" s="39">
         <v>51</v>
       </c>
       <c r="V40" s="6">
@@ -6243,7 +6309,7 @@
       <c r="T41" s="6">
         <v>63</v>
       </c>
-      <c r="U41" s="6">
+      <c r="U41" s="39">
         <v>183</v>
       </c>
       <c r="V41" s="6">
@@ -6294,7 +6360,7 @@
       <c r="T42" s="6">
         <v>67</v>
       </c>
-      <c r="U42" s="6">
+      <c r="U42" s="39">
         <v>27</v>
       </c>
       <c r="V42" s="6">
@@ -6345,7 +6411,7 @@
       <c r="T43" s="6">
         <v>68</v>
       </c>
-      <c r="U43" s="6">
+      <c r="U43" s="39">
         <v>34</v>
       </c>
       <c r="W43" s="6">
@@ -6393,7 +6459,7 @@
       <c r="T44" s="6">
         <v>248</v>
       </c>
-      <c r="U44" s="6">
+      <c r="U44" s="39">
         <v>247</v>
       </c>
       <c r="V44" s="6">
@@ -6444,7 +6510,7 @@
       <c r="T45" s="6">
         <v>177</v>
       </c>
-      <c r="U45" s="6">
+      <c r="U45" s="39">
         <v>150</v>
       </c>
       <c r="V45" s="6">
@@ -6495,7 +6561,7 @@
       <c r="T46" s="6">
         <v>240</v>
       </c>
-      <c r="U46" s="6">
+      <c r="U46" s="39">
         <v>84</v>
       </c>
       <c r="V46" s="6">
@@ -6546,7 +6612,7 @@
       <c r="T47" s="6">
         <v>89</v>
       </c>
-      <c r="U47" s="6">
+      <c r="U47" s="39">
         <v>65</v>
       </c>
       <c r="V47" s="6">
@@ -6597,7 +6663,7 @@
       <c r="T48" s="6">
         <v>276</v>
       </c>
-      <c r="U48" s="6">
+      <c r="U48" s="39">
         <v>185</v>
       </c>
       <c r="V48" s="6">
@@ -6625,11 +6691,11 @@
         <v>245</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="34" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>246</v>
@@ -6644,18 +6710,18 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="5" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="S49" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T49" s="6" t="s">
-        <v>1198</v>
-      </c>
-      <c r="U49">
+        <v>1194</v>
+      </c>
+      <c r="U49" s="33">
         <v>450</v>
       </c>
-      <c r="V49">
+      <c r="V49" s="3">
         <v>200</v>
       </c>
       <c r="W49" s="6">
@@ -6693,7 +6759,7 @@
       <c r="T50" s="6">
         <v>340</v>
       </c>
-      <c r="U50" s="6">
+      <c r="U50" s="39">
         <v>370</v>
       </c>
       <c r="V50" s="6">
@@ -6734,7 +6800,7 @@
       <c r="T51" s="6">
         <v>93</v>
       </c>
-      <c r="U51" s="6">
+      <c r="U51" s="39">
         <v>185</v>
       </c>
       <c r="V51" s="6">
@@ -6785,7 +6851,7 @@
       <c r="T52" s="6">
         <v>195</v>
       </c>
-      <c r="U52" s="6">
+      <c r="U52" s="39">
         <v>150</v>
       </c>
       <c r="V52" s="6">
@@ -6836,7 +6902,7 @@
       <c r="T53" s="6">
         <v>194</v>
       </c>
-      <c r="U53" s="6">
+      <c r="U53" s="39">
         <v>148</v>
       </c>
       <c r="V53" s="6">
@@ -6887,7 +6953,7 @@
       <c r="T54" s="6">
         <v>198</v>
       </c>
-      <c r="U54" s="6">
+      <c r="U54" s="39">
         <v>150</v>
       </c>
       <c r="V54" s="6">
@@ -6938,7 +7004,7 @@
       <c r="T55" s="6">
         <v>194</v>
       </c>
-      <c r="U55" s="6">
+      <c r="U55" s="39">
         <v>148</v>
       </c>
       <c r="V55" s="6">
@@ -6966,14 +7032,14 @@
         <v>273</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="34" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="8" t="s">
@@ -6985,7 +7051,7 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
       <c r="R56" s="5" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="S56" s="5" t="s">
         <v>31</v>
@@ -6993,10 +7059,10 @@
       <c r="T56">
         <v>580</v>
       </c>
-      <c r="U56">
+      <c r="U56" s="33">
         <v>400</v>
       </c>
-      <c r="V56">
+      <c r="V56" s="3">
         <v>400</v>
       </c>
       <c r="W56" s="6">
@@ -7046,7 +7112,7 @@
       <c r="T57" s="6">
         <v>92</v>
       </c>
-      <c r="U57" s="6">
+      <c r="U57" s="39">
         <v>47</v>
       </c>
       <c r="V57" s="6">
@@ -7099,7 +7165,7 @@
       <c r="T58" s="6">
         <v>140</v>
       </c>
-      <c r="U58" s="6">
+      <c r="U58" s="39">
         <v>190</v>
       </c>
       <c r="V58" s="6">
@@ -7150,7 +7216,7 @@
       <c r="T59" s="6">
         <v>94</v>
       </c>
-      <c r="U59" s="6">
+      <c r="U59" s="39">
         <v>65</v>
       </c>
       <c r="V59" s="6">
@@ -7191,7 +7257,7 @@
       <c r="T60" s="6">
         <v>180</v>
       </c>
-      <c r="U60" s="6">
+      <c r="U60" s="39">
         <v>66</v>
       </c>
       <c r="V60" s="6">
@@ -7232,7 +7298,7 @@
       <c r="T61" s="6">
         <v>55</v>
       </c>
-      <c r="U61" s="6">
+      <c r="U61" s="39">
         <v>40</v>
       </c>
       <c r="V61" s="6">
@@ -7273,7 +7339,7 @@
       <c r="T62" s="6">
         <v>260</v>
       </c>
-      <c r="U62" s="6">
+      <c r="U62" s="39">
         <v>140</v>
       </c>
       <c r="V62" s="6">
@@ -7324,7 +7390,7 @@
       <c r="T63" s="6">
         <v>200</v>
       </c>
-      <c r="U63" s="6">
+      <c r="U63" s="39">
         <v>65</v>
       </c>
       <c r="V63" s="6">
@@ -7375,7 +7441,7 @@
       <c r="T64" s="6">
         <v>300</v>
       </c>
-      <c r="U64" s="6">
+      <c r="U64" s="39">
         <v>130</v>
       </c>
       <c r="V64" s="6">
@@ -7426,10 +7492,10 @@
       <c r="T65" s="6">
         <v>135</v>
       </c>
-      <c r="U65">
+      <c r="U65" s="33">
         <v>100</v>
       </c>
-      <c r="V65">
+      <c r="V65" s="3">
         <v>25</v>
       </c>
       <c r="W65" s="6">
@@ -7479,7 +7545,7 @@
       <c r="T66" s="6">
         <v>213</v>
       </c>
-      <c r="U66" s="6">
+      <c r="U66" s="39">
         <v>137</v>
       </c>
       <c r="V66" s="6">
@@ -7532,7 +7598,7 @@
       <c r="T67" s="6">
         <v>180</v>
       </c>
-      <c r="U67" s="6">
+      <c r="U67" s="39">
         <v>98</v>
       </c>
       <c r="V67" s="6">
@@ -7583,7 +7649,7 @@
       <c r="T68" s="6">
         <v>260</v>
       </c>
-      <c r="U68" s="6">
+      <c r="U68" s="39">
         <v>180</v>
       </c>
       <c r="V68" s="6">
@@ -7634,7 +7700,7 @@
       <c r="T69" s="6">
         <v>580</v>
       </c>
-      <c r="U69" s="6">
+      <c r="U69" s="39">
         <v>580</v>
       </c>
       <c r="V69" s="6">
@@ -7675,7 +7741,7 @@
       <c r="T70" s="6">
         <v>43</v>
       </c>
-      <c r="U70" s="6">
+      <c r="U70" s="39">
         <v>23</v>
       </c>
       <c r="V70" s="6">
@@ -7716,7 +7782,7 @@
       <c r="T71" s="6">
         <v>62</v>
       </c>
-      <c r="U71" s="6">
+      <c r="U71" s="39">
         <v>56</v>
       </c>
       <c r="V71" s="6">
@@ -7757,7 +7823,7 @@
       <c r="T72" s="6">
         <v>121</v>
       </c>
-      <c r="U72" s="6">
+      <c r="U72" s="39">
         <v>181</v>
       </c>
       <c r="V72" s="6">
@@ -7808,7 +7874,7 @@
       <c r="T73" s="6">
         <v>196</v>
       </c>
-      <c r="U73" s="6">
+      <c r="U73" s="39">
         <v>111</v>
       </c>
       <c r="V73" s="6">
@@ -7859,7 +7925,7 @@
       <c r="T74" s="6">
         <v>53</v>
       </c>
-      <c r="U74" s="6">
+      <c r="U74" s="39">
         <v>27</v>
       </c>
       <c r="V74" s="6">
@@ -7910,7 +7976,7 @@
       <c r="T75" s="6">
         <v>91</v>
       </c>
-      <c r="U75" s="6">
+      <c r="U75" s="39">
         <v>80</v>
       </c>
       <c r="V75" s="6">
@@ -7961,7 +8027,7 @@
       <c r="T76" s="6">
         <v>42</v>
       </c>
-      <c r="U76" s="6">
+      <c r="U76" s="39">
         <v>39</v>
       </c>
       <c r="V76" s="6">
@@ -8012,7 +8078,7 @@
       <c r="T77" s="38">
         <v>32</v>
       </c>
-      <c r="U77" s="38">
+      <c r="U77" s="42">
         <v>29</v>
       </c>
       <c r="V77" s="38">
@@ -8063,7 +8129,7 @@
       <c r="T78" s="6">
         <v>56</v>
       </c>
-      <c r="U78" s="6">
+      <c r="U78" s="39">
         <v>180</v>
       </c>
       <c r="V78" s="6">
@@ -8114,7 +8180,7 @@
       <c r="T79" s="6">
         <v>56</v>
       </c>
-      <c r="U79" s="6">
+      <c r="U79" s="39">
         <v>200</v>
       </c>
       <c r="V79" s="6">
@@ -8164,7 +8230,7 @@
       <c r="T80" s="6">
         <v>32</v>
       </c>
-      <c r="U80" s="6">
+      <c r="U80" s="39">
         <v>61</v>
       </c>
       <c r="V80" s="6">
@@ -8215,7 +8281,7 @@
       <c r="T81" s="6">
         <v>145</v>
       </c>
-      <c r="U81" s="6">
+      <c r="U81" s="39">
         <v>75</v>
       </c>
       <c r="V81" s="6">
@@ -8266,10 +8332,10 @@
       <c r="T82" s="6">
         <v>250</v>
       </c>
-      <c r="U82">
+      <c r="U82" s="33">
         <v>160</v>
       </c>
-      <c r="V82">
+      <c r="V82" s="3">
         <v>100</v>
       </c>
       <c r="W82" s="6">
@@ -8307,7 +8373,7 @@
       <c r="T83" s="6">
         <v>160</v>
       </c>
-      <c r="U83" s="6">
+      <c r="U83" s="39">
         <v>90</v>
       </c>
       <c r="W83" s="6">
@@ -8355,7 +8421,7 @@
       <c r="T84" s="6">
         <v>96</v>
       </c>
-      <c r="U84" s="6">
+      <c r="U84" s="39">
         <v>66</v>
       </c>
       <c r="V84" s="6">
@@ -8406,7 +8472,7 @@
       <c r="T85" s="6">
         <v>96</v>
       </c>
-      <c r="U85" s="6">
+      <c r="U85" s="39">
         <v>66</v>
       </c>
       <c r="V85" s="6">
@@ -8457,7 +8523,7 @@
       <c r="T86" s="6">
         <v>95</v>
       </c>
-      <c r="U86" s="6">
+      <c r="U86" s="39">
         <v>62</v>
       </c>
       <c r="V86" s="6">
@@ -8508,7 +8574,7 @@
       <c r="T87" s="6">
         <v>88</v>
       </c>
-      <c r="U87" s="6">
+      <c r="U87" s="39">
         <v>55</v>
       </c>
       <c r="V87" s="6">
@@ -8559,7 +8625,7 @@
       <c r="T88" s="6">
         <v>39</v>
       </c>
-      <c r="U88" s="6">
+      <c r="U88" s="39">
         <v>20</v>
       </c>
       <c r="V88" s="6">
@@ -8610,7 +8676,7 @@
       <c r="T89" s="6">
         <v>84</v>
       </c>
-      <c r="U89" s="6">
+      <c r="U89" s="39">
         <v>49</v>
       </c>
       <c r="V89" s="6">
@@ -8663,7 +8729,7 @@
       <c r="T90" s="6">
         <v>114</v>
       </c>
-      <c r="U90" s="6">
+      <c r="U90" s="39">
         <v>45</v>
       </c>
       <c r="V90" s="6">
@@ -8716,7 +8782,7 @@
       <c r="T91" s="6">
         <v>366</v>
       </c>
-      <c r="U91" s="6">
+      <c r="U91" s="39">
         <v>1829</v>
       </c>
       <c r="V91" s="6">
@@ -8744,19 +8810,19 @@
         <v>413</v>
       </c>
       <c r="G92" s="34" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>415</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>414</v>
       </c>
       <c r="L92" s="34" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
@@ -8764,7 +8830,7 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
       <c r="R92" s="5" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="S92" s="5" t="s">
         <v>31</v>
@@ -8772,7 +8838,7 @@
       <c r="T92" s="6">
         <v>1828</v>
       </c>
-      <c r="U92" s="6">
+      <c r="U92" s="39">
         <v>2621</v>
       </c>
       <c r="W92" s="6">
@@ -8822,10 +8888,10 @@
       <c r="T93" s="6">
         <v>594</v>
       </c>
-      <c r="U93">
+      <c r="U93" s="33">
         <v>250</v>
       </c>
-      <c r="V93">
+      <c r="V93" s="3">
         <v>250</v>
       </c>
       <c r="W93" s="6">
@@ -8850,11 +8916,11 @@
         <v>422</v>
       </c>
       <c r="G94" s="34" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="34" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>423</v>
@@ -8869,7 +8935,7 @@
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
       <c r="R94" s="5" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="S94" s="5" t="s">
         <v>31</v>
@@ -8877,7 +8943,7 @@
       <c r="T94" s="6">
         <v>310</v>
       </c>
-      <c r="U94" s="6">
+      <c r="U94" s="39">
         <v>111</v>
       </c>
       <c r="V94" s="6">
@@ -8928,7 +8994,7 @@
       <c r="T95" s="6">
         <v>240</v>
       </c>
-      <c r="U95" s="6">
+      <c r="U95" s="39">
         <v>224</v>
       </c>
       <c r="V95" s="6">
@@ -8979,7 +9045,7 @@
       <c r="T96" s="6">
         <v>380</v>
       </c>
-      <c r="U96" s="6">
+      <c r="U96" s="39">
         <v>95</v>
       </c>
       <c r="V96" s="6">
@@ -9030,7 +9096,7 @@
       <c r="T97" s="6">
         <v>280</v>
       </c>
-      <c r="U97" s="6">
+      <c r="U97" s="39">
         <v>67</v>
       </c>
       <c r="V97" s="6">
@@ -9081,7 +9147,7 @@
       <c r="T98" s="6">
         <v>197</v>
       </c>
-      <c r="U98" s="6">
+      <c r="U98" s="39">
         <v>70</v>
       </c>
       <c r="V98" s="6">
@@ -9132,7 +9198,7 @@
       <c r="T99" s="6">
         <v>1200</v>
       </c>
-      <c r="U99" s="6">
+      <c r="U99" s="39">
         <v>2200</v>
       </c>
       <c r="V99" s="6">
@@ -9183,7 +9249,7 @@
       <c r="T100" s="6">
         <v>236</v>
       </c>
-      <c r="U100" s="6">
+      <c r="U100" s="39">
         <v>654</v>
       </c>
       <c r="W100" s="6">
@@ -9211,7 +9277,7 @@
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="K101" s="5"/>
       <c r="L101" s="8" t="s">
@@ -9231,7 +9297,7 @@
       <c r="T101" s="6">
         <v>600</v>
       </c>
-      <c r="U101" s="6">
+      <c r="U101" s="39">
         <v>400</v>
       </c>
       <c r="W101" s="6">
@@ -9259,7 +9325,7 @@
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="K102" s="5"/>
       <c r="L102" s="8" t="s">
@@ -9279,10 +9345,10 @@
       <c r="T102" s="6">
         <v>175</v>
       </c>
-      <c r="U102">
+      <c r="U102" s="33">
         <v>250</v>
       </c>
-      <c r="V102">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
       <c r="W102" s="6">
@@ -9330,7 +9396,7 @@
       <c r="T103" s="6">
         <v>280</v>
       </c>
-      <c r="U103" s="6">
+      <c r="U103" s="39">
         <v>250</v>
       </c>
       <c r="W103" s="6">
@@ -9378,7 +9444,7 @@
       <c r="T104" s="6">
         <v>380</v>
       </c>
-      <c r="U104" s="6">
+      <c r="U104" s="39">
         <v>250</v>
       </c>
       <c r="V104" s="6">
@@ -9409,7 +9475,7 @@
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="K105" s="5"/>
       <c r="L105" s="8" t="s">
@@ -9429,7 +9495,7 @@
       <c r="T105" s="6">
         <v>350</v>
       </c>
-      <c r="U105" s="6">
+      <c r="U105" s="39">
         <v>600</v>
       </c>
       <c r="V105" s="6">
@@ -9481,7 +9547,7 @@
       <c r="T106" s="12">
         <v>43</v>
       </c>
-      <c r="U106" s="12">
+      <c r="U106" s="43">
         <v>16</v>
       </c>
       <c r="V106" s="12">
@@ -9533,7 +9599,7 @@
       <c r="T107" s="12">
         <v>54</v>
       </c>
-      <c r="U107" s="12">
+      <c r="U107" s="43">
         <v>93</v>
       </c>
       <c r="V107" s="12">
@@ -9585,7 +9651,7 @@
       <c r="T108" s="12">
         <v>11</v>
       </c>
-      <c r="U108" s="12">
+      <c r="U108" s="43">
         <v>12</v>
       </c>
       <c r="V108" s="12">
@@ -9637,7 +9703,7 @@
       <c r="T109" s="12">
         <v>13</v>
       </c>
-      <c r="U109" s="12">
+      <c r="U109" s="43">
         <v>11</v>
       </c>
       <c r="V109" s="12">
@@ -9681,7 +9747,7 @@
       <c r="T110" s="6">
         <v>600</v>
       </c>
-      <c r="U110" s="6">
+      <c r="U110" s="39">
         <v>3080</v>
       </c>
       <c r="V110" s="6">
@@ -9725,7 +9791,7 @@
       <c r="T111" s="6">
         <v>230</v>
       </c>
-      <c r="U111" s="6">
+      <c r="U111" s="39">
         <v>91</v>
       </c>
       <c r="V111" s="6">
@@ -9769,7 +9835,7 @@
       <c r="T112" s="6">
         <v>46</v>
       </c>
-      <c r="U112" s="6">
+      <c r="U112" s="39">
         <v>140</v>
       </c>
       <c r="V112" s="6">
@@ -9822,7 +9888,7 @@
       <c r="T113" s="6">
         <v>82</v>
       </c>
-      <c r="U113" s="6">
+      <c r="U113" s="39">
         <v>58</v>
       </c>
       <c r="V113" s="6">
@@ -9873,7 +9939,7 @@
       <c r="T114" s="6">
         <v>99</v>
       </c>
-      <c r="U114" s="6">
+      <c r="U114" s="39">
         <v>35</v>
       </c>
       <c r="V114" s="6">
@@ -9924,7 +9990,7 @@
       <c r="T115" s="6">
         <v>42</v>
       </c>
-      <c r="U115" s="6">
+      <c r="U115" s="39">
         <v>32</v>
       </c>
       <c r="V115" s="6">
@@ -9975,7 +10041,7 @@
       <c r="T116" s="6">
         <v>20</v>
       </c>
-      <c r="U116" s="6">
+      <c r="U116" s="39">
         <v>14</v>
       </c>
       <c r="V116" s="6">
@@ -10026,7 +10092,7 @@
       <c r="T117" s="6">
         <v>22</v>
       </c>
-      <c r="U117" s="6">
+      <c r="U117" s="39">
         <v>42</v>
       </c>
       <c r="V117" s="6">
@@ -10077,7 +10143,7 @@
       <c r="T118" s="6">
         <v>31</v>
       </c>
-      <c r="U118" s="6">
+      <c r="U118" s="39">
         <v>20</v>
       </c>
       <c r="V118" s="6">
@@ -10128,7 +10194,7 @@
       <c r="T119" s="6">
         <v>40</v>
       </c>
-      <c r="U119" s="6">
+      <c r="U119" s="39">
         <v>38</v>
       </c>
       <c r="V119" s="6">
@@ -10179,7 +10245,7 @@
       <c r="T120" s="6">
         <v>23</v>
       </c>
-      <c r="U120" s="6">
+      <c r="U120" s="39">
         <v>22</v>
       </c>
       <c r="V120" s="6">
@@ -10230,7 +10296,7 @@
       <c r="T121" s="6">
         <v>20</v>
       </c>
-      <c r="U121" s="6">
+      <c r="U121" s="39">
         <v>16</v>
       </c>
       <c r="V121" s="6">
@@ -10281,7 +10347,7 @@
       <c r="T122" s="6">
         <v>185</v>
       </c>
-      <c r="U122" s="6">
+      <c r="U122" s="39">
         <v>100</v>
       </c>
       <c r="V122" s="6">
@@ -10332,7 +10398,7 @@
       <c r="T123" s="6">
         <v>73</v>
       </c>
-      <c r="U123" s="6">
+      <c r="U123" s="39">
         <v>226</v>
       </c>
       <c r="V123" s="6">
@@ -10383,7 +10449,7 @@
       <c r="T124" s="6">
         <v>192</v>
       </c>
-      <c r="U124" s="6">
+      <c r="U124" s="39">
         <v>90</v>
       </c>
       <c r="V124" s="6">
@@ -10434,7 +10500,7 @@
       <c r="T125" s="6">
         <v>141</v>
       </c>
-      <c r="U125" s="6">
+      <c r="U125" s="39">
         <v>122</v>
       </c>
       <c r="V125" s="6">
@@ -10475,7 +10541,7 @@
       <c r="T126" s="6">
         <v>174</v>
       </c>
-      <c r="U126" s="6">
+      <c r="U126" s="39">
         <v>100</v>
       </c>
       <c r="V126" s="6">
@@ -10516,7 +10582,7 @@
       <c r="T127" s="6">
         <v>64</v>
       </c>
-      <c r="U127" s="6">
+      <c r="U127" s="39">
         <v>141</v>
       </c>
       <c r="V127" s="6">
@@ -10557,7 +10623,7 @@
       <c r="T128" s="6">
         <v>235</v>
       </c>
-      <c r="U128" s="6">
+      <c r="U128" s="39">
         <v>160</v>
       </c>
       <c r="V128" s="6">
@@ -10608,7 +10674,7 @@
       <c r="T129" s="6">
         <v>175</v>
       </c>
-      <c r="U129" s="6">
+      <c r="U129" s="39">
         <v>91</v>
       </c>
       <c r="V129" s="6">
@@ -10651,7 +10717,7 @@
       <c r="T130" s="6">
         <v>335</v>
       </c>
-      <c r="U130" s="6">
+      <c r="U130" s="39">
         <v>146</v>
       </c>
       <c r="V130" s="6">
@@ -10694,7 +10760,7 @@
       <c r="T131" s="6">
         <v>344</v>
       </c>
-      <c r="U131" s="6">
+      <c r="U131" s="39">
         <v>150</v>
       </c>
       <c r="V131" s="6">
@@ -10721,7 +10787,7 @@
         <v>569</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="L132" s="10" t="s">
         <v>570</v>
@@ -10733,9 +10799,9 @@
         <v>31</v>
       </c>
       <c r="T132" s="6" t="s">
-        <v>1203</v>
-      </c>
-      <c r="U132" s="6">
+        <v>1199</v>
+      </c>
+      <c r="U132" s="39">
         <v>190</v>
       </c>
       <c r="V132" s="6">
@@ -10768,7 +10834,7 @@
         <v>574</v>
       </c>
       <c r="R133" s="5" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="S133" s="5" t="s">
         <v>31</v>
@@ -10776,7 +10842,7 @@
       <c r="T133" s="6">
         <v>195</v>
       </c>
-      <c r="U133" s="6">
+      <c r="U133" s="39">
         <v>133</v>
       </c>
       <c r="V133" s="6">
@@ -10817,7 +10883,7 @@
       <c r="T134" s="6">
         <v>450</v>
       </c>
-      <c r="U134" s="6">
+      <c r="U134" s="39">
         <v>260</v>
       </c>
       <c r="V134" s="6">
@@ -10850,15 +10916,15 @@
         <v>583</v>
       </c>
       <c r="R135" s="5" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="S135" s="5" t="s">
         <v>298</v>
       </c>
       <c r="T135" s="6" t="s">
-        <v>1202</v>
-      </c>
-      <c r="U135" s="6">
+        <v>1198</v>
+      </c>
+      <c r="U135" s="39">
         <v>320</v>
       </c>
       <c r="V135" s="6">
@@ -10873,7 +10939,7 @@
         <v>584</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>585</v>
+        <v>1227</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="6">
@@ -10883,17 +10949,17 @@
         <v>73</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K136" s="5"/>
       <c r="L136" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M136" s="5"/>
       <c r="N136" s="5"/>
@@ -10904,12 +10970,12 @@
         <v>30</v>
       </c>
       <c r="S136" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T136" s="6">
         <v>68</v>
       </c>
-      <c r="U136" s="6">
+      <c r="U136" s="39">
         <v>26</v>
       </c>
       <c r="V136" s="6">
@@ -10923,26 +10989,26 @@
       <c r="A137" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>585</v>
+      <c r="B137" s="5" t="s">
+        <v>1227</v>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F137" s="35" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
       <c r="J137" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="L137" s="34" t="s">
         <v>592</v>
-      </c>
-      <c r="L137" s="34" t="s">
-        <v>593</v>
       </c>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
@@ -10958,7 +11024,7 @@
       <c r="T137" s="6">
         <v>69</v>
       </c>
-      <c r="U137" s="6">
+      <c r="U137" s="39">
         <v>51</v>
       </c>
       <c r="V137" s="6">
@@ -10973,7 +11039,7 @@
         <v>584</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>585</v>
+        <v>1227</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="6">
@@ -10989,11 +11055,11 @@
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="K138" s="5"/>
       <c r="L138" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M138" s="5"/>
       <c r="N138" s="5"/>
@@ -11009,7 +11075,7 @@
       <c r="T138" s="6">
         <v>90</v>
       </c>
-      <c r="U138" s="6">
+      <c r="U138" s="39">
         <v>46</v>
       </c>
       <c r="V138" s="6">
@@ -11024,22 +11090,22 @@
         <v>584</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>585</v>
+        <v>1227</v>
       </c>
       <c r="D139" s="6">
         <v>1912</v>
       </c>
       <c r="E139" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="J139" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="J139" s="2" t="s">
+      <c r="L139" s="34" t="s">
         <v>598</v>
-      </c>
-      <c r="L139" s="34" t="s">
-        <v>599</v>
       </c>
       <c r="R139" s="5" t="s">
         <v>30</v>
@@ -11050,7 +11116,7 @@
       <c r="T139" s="6">
         <v>64</v>
       </c>
-      <c r="U139" s="6">
+      <c r="U139" s="39">
         <v>33</v>
       </c>
       <c r="V139" s="6">
@@ -11062,10 +11128,10 @@
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>600</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>601</v>
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="6">
@@ -11081,11 +11147,11 @@
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K140" s="5"/>
       <c r="L140" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M140" s="5"/>
       <c r="N140" s="5"/>
@@ -11096,12 +11162,12 @@
         <v>30</v>
       </c>
       <c r="S140" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="T140" s="6">
         <v>155</v>
       </c>
-      <c r="U140" s="6">
+      <c r="U140" s="39">
         <v>56</v>
       </c>
       <c r="V140" s="6">
@@ -11113,30 +11179,30 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>600</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>601</v>
       </c>
       <c r="C141" s="5"/>
       <c r="D141" s="6">
         <v>1887</v>
       </c>
       <c r="E141" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="F141" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K141" s="5"/>
       <c r="L141" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M141" s="5"/>
       <c r="N141" s="5"/>
@@ -11152,7 +11218,7 @@
       <c r="T141" s="6">
         <v>132</v>
       </c>
-      <c r="U141" s="6">
+      <c r="U141" s="39">
         <v>50</v>
       </c>
       <c r="V141" s="6">
@@ -11164,17 +11230,17 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>600</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>601</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="6">
         <v>1897</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>205</v>
@@ -11183,11 +11249,11 @@
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K142" s="5"/>
       <c r="L142" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="M142" s="5"/>
       <c r="N142" s="5"/>
@@ -11195,7 +11261,7 @@
       <c r="P142" s="5"/>
       <c r="Q142" s="5"/>
       <c r="R142" s="5" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="S142" s="5" t="s">
         <v>298</v>
@@ -11203,7 +11269,7 @@
       <c r="T142" s="6">
         <v>84</v>
       </c>
-      <c r="U142" s="6">
+      <c r="U142" s="39">
         <v>73</v>
       </c>
       <c r="V142" s="6">
@@ -11215,30 +11281,30 @@
     </row>
     <row r="143" spans="1:23" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>600</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>601</v>
       </c>
       <c r="C143" s="5"/>
       <c r="D143" s="6">
         <v>1891</v>
       </c>
       <c r="E143" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="F143" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K143" s="5"/>
       <c r="L143" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M143" s="5"/>
       <c r="N143" s="5"/>
@@ -11254,7 +11320,7 @@
       <c r="T143" s="6">
         <v>100</v>
       </c>
-      <c r="U143" s="6">
+      <c r="U143" s="39">
         <v>53</v>
       </c>
       <c r="V143" s="6">
@@ -11269,7 +11335,7 @@
         <v>197</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>333</v>
@@ -11278,30 +11344,30 @@
         <v>560</v>
       </c>
       <c r="F144" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="G144" s="34" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="J144" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="G144" s="34" t="s">
-        <v>1172</v>
-      </c>
-      <c r="I144" s="10" t="s">
+      <c r="L144" s="34" t="s">
+        <v>1167</v>
+      </c>
+      <c r="R144" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="S144" s="5" t="s">
         <v>617</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="L144" s="34" t="s">
-        <v>1171</v>
-      </c>
-      <c r="R144" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="S144" s="5" t="s">
-        <v>618</v>
       </c>
       <c r="T144" s="6">
         <v>243</v>
       </c>
-      <c r="U144" s="6">
+      <c r="U144" s="39">
         <v>518</v>
       </c>
       <c r="V144" s="6">
@@ -11316,27 +11382,27 @@
         <v>197</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C145" s="5"/>
       <c r="D145" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>560</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K145" s="5"/>
       <c r="L145" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M145" s="5"/>
       <c r="N145" s="5"/>
@@ -11352,7 +11418,7 @@
       <c r="T145" s="6">
         <v>103</v>
       </c>
-      <c r="U145" s="6">
+      <c r="U145" s="39">
         <v>67</v>
       </c>
       <c r="V145" s="6">
@@ -11367,27 +11433,27 @@
         <v>197</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C146" s="5"/>
       <c r="D146" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E146" s="5" t="s">
         <v>560</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K146" s="5"/>
       <c r="L146" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M146" s="5"/>
       <c r="N146" s="5"/>
@@ -11403,7 +11469,7 @@
       <c r="T146" s="6">
         <v>37</v>
       </c>
-      <c r="U146" s="6">
+      <c r="U146" s="39">
         <v>14</v>
       </c>
       <c r="V146" s="6">
@@ -11418,27 +11484,27 @@
         <v>197</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C147" s="5"/>
       <c r="D147" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E147" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>596</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>597</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K147" s="5"/>
       <c r="L147" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M147" s="5"/>
       <c r="N147" s="5"/>
@@ -11454,7 +11520,7 @@
       <c r="T147" s="6">
         <v>49</v>
       </c>
-      <c r="U147" s="6">
+      <c r="U147" s="39">
         <v>21</v>
       </c>
       <c r="V147" s="6">
@@ -11469,27 +11535,27 @@
         <v>197</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C148" s="5"/>
       <c r="D148" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>560</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K148" s="5"/>
       <c r="L148" s="25" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M148" s="5"/>
       <c r="N148" s="5"/>
@@ -11505,7 +11571,7 @@
       <c r="T148" s="6">
         <v>510</v>
       </c>
-      <c r="U148" s="6">
+      <c r="U148" s="39">
         <v>540</v>
       </c>
       <c r="V148" s="6">
@@ -11520,27 +11586,27 @@
         <v>197</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C149" s="5"/>
       <c r="D149" s="6">
         <v>1894</v>
       </c>
       <c r="E149" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>631</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>632</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K149" s="5"/>
       <c r="L149" s="34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M149" s="5"/>
       <c r="N149" s="5"/>
@@ -11551,12 +11617,12 @@
         <v>30</v>
       </c>
       <c r="S149" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T149" s="6">
         <v>53</v>
       </c>
-      <c r="U149" s="6">
+      <c r="U149" s="39">
         <v>45</v>
       </c>
       <c r="W149" s="6">
@@ -11565,25 +11631,25 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="D150" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="E150" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="F150" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="J150" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="J150" s="2" t="s">
+      <c r="L150" s="10" t="s">
         <v>641</v>
-      </c>
-      <c r="L150" s="10" t="s">
-        <v>642</v>
       </c>
       <c r="R150" s="5" t="s">
         <v>30</v>
@@ -11594,7 +11660,7 @@
       <c r="T150" s="6">
         <v>124</v>
       </c>
-      <c r="U150" s="6">
+      <c r="U150" s="39">
         <v>39</v>
       </c>
       <c r="V150" s="6">
@@ -11606,30 +11672,30 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>637</v>
       </c>
       <c r="C151" s="5"/>
       <c r="D151" s="6">
         <v>1854</v>
       </c>
       <c r="E151" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="F151" s="5" t="s">
         <v>643</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>644</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="K151" s="5"/>
       <c r="L151" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="M151" s="5"/>
       <c r="N151" s="5"/>
@@ -11645,7 +11711,7 @@
       <c r="T151" s="6">
         <v>69</v>
       </c>
-      <c r="U151" s="6">
+      <c r="U151" s="39">
         <v>53</v>
       </c>
       <c r="V151" s="6">
@@ -11657,30 +11723,30 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>637</v>
       </c>
       <c r="C152" s="5"/>
       <c r="D152" s="6">
         <v>1857</v>
       </c>
       <c r="E152" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="F152" s="5" t="s">
         <v>647</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>648</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K152" s="5"/>
       <c r="L152" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M152" s="5"/>
       <c r="N152" s="5"/>
@@ -11696,7 +11762,7 @@
       <c r="T152" s="6">
         <v>44</v>
       </c>
-      <c r="U152" s="6">
+      <c r="U152" s="39">
         <v>106</v>
       </c>
       <c r="V152" s="6">
@@ -11708,10 +11774,10 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="B153" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>637</v>
       </c>
       <c r="C153" s="5"/>
       <c r="D153" s="6">
@@ -11727,11 +11793,11 @@
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K153" s="5"/>
       <c r="L153" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M153" s="5"/>
       <c r="N153" s="5"/>
@@ -11747,7 +11813,7 @@
       <c r="T153" s="6">
         <v>88</v>
       </c>
-      <c r="U153" s="6">
+      <c r="U153" s="39">
         <v>104</v>
       </c>
       <c r="V153" s="6">
@@ -11759,30 +11825,30 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>653</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>654</v>
       </c>
       <c r="C154" s="5"/>
       <c r="D154" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K154" s="5"/>
       <c r="L154" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M154" s="5"/>
       <c r="N154" s="5"/>
@@ -11796,38 +11862,38 @@
         <v>31</v>
       </c>
       <c r="T154" s="6" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="W154" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>653</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>654</v>
       </c>
       <c r="C155" s="5"/>
       <c r="D155" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="K155" s="5"/>
       <c r="L155" s="34" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="M155" s="5"/>
       <c r="N155" s="5"/>
@@ -11841,38 +11907,38 @@
         <v>31</v>
       </c>
       <c r="T155" s="6" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="W155" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>653</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>654</v>
       </c>
       <c r="C156" s="5"/>
       <c r="D156" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E156" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K156" s="5"/>
       <c r="L156" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="M156" s="5"/>
       <c r="N156" s="5"/>
@@ -11880,44 +11946,44 @@
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
       <c r="R156" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="S156" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T156" s="6" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="W156" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>653</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>654</v>
       </c>
       <c r="C157" s="5"/>
       <c r="D157" s="6" t="s">
         <v>275</v>
       </c>
       <c r="E157" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="F157" s="5" t="s">
         <v>666</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>667</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K157" s="5"/>
       <c r="L157" s="34" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="M157" s="5"/>
       <c r="N157" s="5"/>
@@ -11933,37 +11999,37 @@
       <c r="T157" s="6">
         <v>350</v>
       </c>
-      <c r="U157" s="6">
+      <c r="U157" s="39">
         <v>600</v>
       </c>
       <c r="V157" s="6">
         <v>500</v>
       </c>
       <c r="W157" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="D158" s="6" t="s">
         <v>670</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>671</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>560</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J158" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L158" s="15" t="s">
         <v>672</v>
-      </c>
-      <c r="L158" s="15" t="s">
-        <v>673</v>
       </c>
       <c r="R158" s="5" t="s">
         <v>30</v>
@@ -11974,7 +12040,7 @@
       <c r="T158" s="6">
         <v>174</v>
       </c>
-      <c r="U158" s="6">
+      <c r="U158" s="39">
         <v>98</v>
       </c>
       <c r="V158" s="6">
@@ -11986,25 +12052,25 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>91</v>
       </c>
       <c r="E159" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="J159" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="J159" s="2" t="s">
+      <c r="L159" s="10" t="s">
         <v>676</v>
-      </c>
-      <c r="L159" s="10" t="s">
-        <v>677</v>
       </c>
       <c r="R159" s="5" t="s">
         <v>30</v>
@@ -12015,7 +12081,7 @@
       <c r="T159" s="6">
         <v>51</v>
       </c>
-      <c r="U159" s="6">
+      <c r="U159" s="39">
         <v>24</v>
       </c>
       <c r="V159" s="6">
@@ -12027,10 +12093,10 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>669</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>670</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="6">
@@ -12040,17 +12106,17 @@
         <v>560</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
       <c r="J160" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K160" s="5"/>
       <c r="L160" s="8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="M160" s="5"/>
       <c r="N160" s="5"/>
@@ -12066,7 +12132,7 @@
       <c r="T160" s="6">
         <v>50.8</v>
       </c>
-      <c r="U160" s="6">
+      <c r="U160" s="39">
         <v>22.5</v>
       </c>
       <c r="V160" s="6">
@@ -12078,10 +12144,10 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>669</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>670</v>
       </c>
       <c r="C161" s="5"/>
       <c r="D161" s="6">
@@ -12091,17 +12157,17 @@
         <v>560</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
       <c r="J161" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="K161" s="5"/>
       <c r="L161" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="M161" s="5"/>
       <c r="N161" s="5"/>
@@ -12117,7 +12183,7 @@
       <c r="T161" s="6">
         <v>39</v>
       </c>
-      <c r="U161" s="6">
+      <c r="U161" s="39">
         <v>46</v>
       </c>
       <c r="V161" s="6">
@@ -12129,30 +12195,30 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>683</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>684</v>
       </c>
       <c r="C162" s="5"/>
       <c r="D162" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="E162" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="F162" s="5" t="s">
         <v>686</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>687</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
       <c r="J162" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K162" s="5"/>
       <c r="L162" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="M162" s="5"/>
       <c r="N162" s="5"/>
@@ -12163,12 +12229,12 @@
         <v>30</v>
       </c>
       <c r="S162" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="T162" s="6">
         <v>78</v>
       </c>
-      <c r="U162" s="6">
+      <c r="U162" s="39">
         <v>239</v>
       </c>
       <c r="V162" s="6">
@@ -12180,30 +12246,30 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>683</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>684</v>
       </c>
       <c r="C163" s="5"/>
       <c r="D163" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E163" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>686</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>687</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
       <c r="J163" s="5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K163" s="5"/>
       <c r="L163" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M163" s="5"/>
       <c r="N163" s="5"/>
@@ -12219,7 +12285,7 @@
       <c r="T163" s="6">
         <v>193</v>
       </c>
-      <c r="U163" s="6">
+      <c r="U163" s="39">
         <v>54</v>
       </c>
       <c r="V163" s="6">
@@ -12231,30 +12297,30 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>683</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>684</v>
       </c>
       <c r="C164" s="5"/>
       <c r="D164" s="6" t="s">
         <v>187</v>
       </c>
       <c r="E164" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="F164" s="5" t="s">
         <v>686</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>687</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K164" s="5"/>
       <c r="L164" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="M164" s="5"/>
       <c r="N164" s="5"/>
@@ -12270,7 +12336,7 @@
       <c r="T164" s="6">
         <v>176</v>
       </c>
-      <c r="U164" s="6">
+      <c r="U164" s="39">
         <v>140</v>
       </c>
       <c r="V164" s="6">
@@ -12282,30 +12348,30 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="27" t="s">
+        <v>682</v>
+      </c>
+      <c r="B165" s="27" t="s">
         <v>683</v>
-      </c>
-      <c r="B165" s="27" t="s">
-        <v>684</v>
       </c>
       <c r="C165" s="27"/>
       <c r="D165" s="37" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E165" s="27" t="s">
+        <v>685</v>
+      </c>
+      <c r="F165" s="27" t="s">
         <v>686</v>
-      </c>
-      <c r="F165" s="27" t="s">
-        <v>687</v>
       </c>
       <c r="G165" s="27"/>
       <c r="H165" s="27"/>
       <c r="I165" s="27"/>
       <c r="J165" s="27" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K165" s="27"/>
       <c r="L165" s="36" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M165" s="27"/>
       <c r="N165" s="27"/>
@@ -12321,10 +12387,10 @@
       <c r="T165" s="37">
         <v>226</v>
       </c>
-      <c r="U165" s="37">
+      <c r="U165" s="40">
         <v>76</v>
       </c>
-      <c r="V165" s="37">
+      <c r="V165" s="6">
         <v>56</v>
       </c>
       <c r="W165" s="37">
@@ -12333,32 +12399,32 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="27" t="s">
+        <v>682</v>
+      </c>
+      <c r="B166" s="27" t="s">
         <v>683</v>
-      </c>
-      <c r="B166" s="27" t="s">
-        <v>684</v>
       </c>
       <c r="C166" s="27"/>
       <c r="D166" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="E166" s="27" t="s">
         <v>699</v>
       </c>
-      <c r="E166" s="27" t="s">
+      <c r="F166" s="27" t="s">
         <v>700</v>
-      </c>
-      <c r="F166" s="27" t="s">
-        <v>701</v>
       </c>
       <c r="G166" s="27"/>
       <c r="H166" s="27"/>
       <c r="I166" s="27"/>
       <c r="J166" s="27" t="s">
+        <v>701</v>
+      </c>
+      <c r="K166" s="27" t="s">
         <v>702</v>
       </c>
-      <c r="K166" s="27" t="s">
+      <c r="L166" s="34" t="s">
         <v>703</v>
-      </c>
-      <c r="L166" s="34" t="s">
-        <v>704</v>
       </c>
       <c r="M166" s="27"/>
       <c r="N166" s="27"/>
@@ -12369,15 +12435,15 @@
         <v>30</v>
       </c>
       <c r="S166" s="27" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="T166" s="37">
         <v>104</v>
       </c>
-      <c r="U166" s="37">
+      <c r="U166" s="40">
         <v>50</v>
       </c>
-      <c r="V166" s="37">
+      <c r="V166" s="6">
         <v>109</v>
       </c>
       <c r="W166" s="37">
@@ -12386,32 +12452,32 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="27" t="s">
+        <v>682</v>
+      </c>
+      <c r="B167" s="27" t="s">
         <v>683</v>
-      </c>
-      <c r="B167" s="27" t="s">
-        <v>684</v>
       </c>
       <c r="C167" s="27"/>
       <c r="D167" s="37" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E167" s="27" t="s">
         <v>154</v>
       </c>
       <c r="F167" s="27" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G167" s="27"/>
       <c r="H167" s="27"/>
       <c r="I167" s="27"/>
       <c r="J167" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="K167" s="27" t="s">
         <v>707</v>
       </c>
-      <c r="K167" s="27" t="s">
+      <c r="L167" s="34" t="s">
         <v>708</v>
-      </c>
-      <c r="L167" s="34" t="s">
-        <v>709</v>
       </c>
       <c r="M167" s="27"/>
       <c r="N167" s="27"/>
@@ -12422,15 +12488,15 @@
         <v>30</v>
       </c>
       <c r="S167" s="27" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="T167" s="37">
         <v>64</v>
       </c>
-      <c r="U167" s="37">
+      <c r="U167" s="40">
         <v>59</v>
       </c>
-      <c r="V167" s="37">
+      <c r="V167" s="6">
         <v>32</v>
       </c>
       <c r="W167" s="37">
@@ -12439,14 +12505,14 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B168" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C168" s="5"/>
       <c r="D168" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>45</v>
@@ -12458,11 +12524,11 @@
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="K168" s="5"/>
       <c r="L168" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="M168" s="5"/>
       <c r="N168" s="5"/>
@@ -12478,7 +12544,7 @@
       <c r="T168" s="6">
         <v>110</v>
       </c>
-      <c r="U168" s="6">
+      <c r="U168" s="39">
         <v>117</v>
       </c>
       <c r="V168" s="6">
@@ -12490,10 +12556,10 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C169" s="5"/>
       <c r="D169" s="6" t="s">
@@ -12509,11 +12575,11 @@
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
       <c r="J169" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K169" s="5"/>
       <c r="L169" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="M169" s="5"/>
       <c r="N169" s="5"/>
@@ -12529,7 +12595,7 @@
       <c r="T169" s="6">
         <v>110</v>
       </c>
-      <c r="U169" s="6">
+      <c r="U169" s="39">
         <v>105</v>
       </c>
       <c r="V169" s="6">
@@ -12541,10 +12607,10 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C170" s="5"/>
       <c r="D170" s="6" t="s">
@@ -12560,11 +12626,11 @@
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="K170" s="5"/>
       <c r="L170" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="M170" s="5"/>
       <c r="N170" s="5"/>
@@ -12580,7 +12646,7 @@
       <c r="T170" s="6">
         <v>164</v>
       </c>
-      <c r="U170" s="6">
+      <c r="U170" s="39">
         <v>52</v>
       </c>
       <c r="V170" s="6">
@@ -12592,10 +12658,10 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="6" t="s">
@@ -12611,11 +12677,11 @@
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="K171" s="5"/>
       <c r="L171" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="M171" s="5"/>
       <c r="N171" s="5"/>
@@ -12631,7 +12697,7 @@
       <c r="T171" s="6">
         <v>215</v>
       </c>
-      <c r="U171" s="6">
+      <c r="U171" s="39">
         <v>97</v>
       </c>
       <c r="V171" s="6">
@@ -12643,14 +12709,14 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C172" s="5"/>
       <c r="D172" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E172" s="5" t="s">
         <v>45</v>
@@ -12662,11 +12728,11 @@
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K172" s="5"/>
       <c r="L172" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="M172" s="5"/>
       <c r="N172" s="5"/>
@@ -12677,12 +12743,12 @@
         <v>30</v>
       </c>
       <c r="S172" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="T172" s="6">
         <v>130</v>
       </c>
-      <c r="U172" s="6">
+      <c r="U172" s="39">
         <v>240</v>
       </c>
       <c r="V172" s="6">
@@ -12694,14 +12760,14 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>45</v>
@@ -12713,11 +12779,11 @@
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="K173" s="5"/>
       <c r="L173" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M173" s="5"/>
       <c r="N173" s="5"/>
@@ -12728,12 +12794,12 @@
         <v>30</v>
       </c>
       <c r="S173" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="T173" s="6">
         <v>136</v>
       </c>
-      <c r="U173" s="6">
+      <c r="U173" s="39">
         <v>230</v>
       </c>
       <c r="V173" s="6">
@@ -12745,30 +12811,30 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="29" t="s">
+        <v>727</v>
+      </c>
+      <c r="B174" s="29" t="s">
         <v>728</v>
-      </c>
-      <c r="B174" s="29" t="s">
-        <v>729</v>
       </c>
       <c r="C174" s="29"/>
       <c r="D174" s="31" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E174" s="29" t="s">
         <v>134</v>
       </c>
       <c r="F174" s="29" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G174" s="29"/>
       <c r="H174" s="29"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K174" s="29"/>
       <c r="L174" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M174" s="29"/>
       <c r="N174" s="29"/>
@@ -12784,10 +12850,10 @@
       <c r="T174" s="31">
         <v>160</v>
       </c>
-      <c r="U174" s="31">
+      <c r="U174" s="41">
         <v>79</v>
       </c>
-      <c r="V174" s="31">
+      <c r="V174" s="6">
         <v>116</v>
       </c>
       <c r="W174" s="31">
@@ -12796,10 +12862,10 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="C175" s="5"/>
       <c r="D175" s="6" t="s">
@@ -12809,17 +12875,17 @@
         <v>134</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K175" s="5"/>
       <c r="L175" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M175" s="5"/>
       <c r="N175" s="5"/>
@@ -12835,7 +12901,7 @@
       <c r="T175" s="6">
         <v>133</v>
       </c>
-      <c r="U175" s="6">
+      <c r="U175" s="39">
         <v>40</v>
       </c>
       <c r="V175" s="6">
@@ -12847,30 +12913,30 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="B176" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="C176" s="5"/>
       <c r="D176" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G176" s="5"/>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
       <c r="J176" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="K176" s="5"/>
       <c r="L176" s="8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="M176" s="5"/>
       <c r="N176" s="5"/>
@@ -12886,7 +12952,7 @@
       <c r="T176" s="6">
         <v>104</v>
       </c>
-      <c r="U176" s="6">
+      <c r="U176" s="39">
         <v>56</v>
       </c>
       <c r="V176" s="6">
@@ -12898,30 +12964,30 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="C177" s="5"/>
       <c r="D177" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="E177" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="F177" s="5" t="s">
         <v>741</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>742</v>
       </c>
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
       <c r="J177" s="5" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K177" s="5"/>
       <c r="L177" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M177" s="5"/>
       <c r="N177" s="5"/>
@@ -12937,7 +13003,7 @@
       <c r="T177" s="6">
         <v>51</v>
       </c>
-      <c r="U177" s="6">
+      <c r="U177" s="39">
         <v>36</v>
       </c>
       <c r="V177" s="6">
@@ -12949,10 +13015,10 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>745</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>746</v>
       </c>
       <c r="C178" s="5"/>
       <c r="D178" s="6" t="s">
@@ -12968,11 +13034,11 @@
       <c r="H178" s="5"/>
       <c r="I178" s="5"/>
       <c r="J178" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="K178" s="5"/>
       <c r="L178" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="M178" s="5"/>
       <c r="N178" s="5"/>
@@ -12988,7 +13054,7 @@
       <c r="T178" s="6">
         <v>184</v>
       </c>
-      <c r="U178" s="6">
+      <c r="U178" s="39">
         <v>77</v>
       </c>
       <c r="V178" s="6">
@@ -13000,10 +13066,10 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>745</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>746</v>
       </c>
       <c r="C179" s="5"/>
       <c r="D179" s="6" t="s">
@@ -13013,17 +13079,17 @@
         <v>45</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G179" s="5"/>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
       <c r="J179" s="5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="K179" s="5"/>
       <c r="L179" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="M179" s="5"/>
       <c r="N179" s="5"/>
@@ -13039,7 +13105,7 @@
       <c r="T179" s="6">
         <v>311</v>
       </c>
-      <c r="U179" s="6">
+      <c r="U179" s="39">
         <v>192</v>
       </c>
       <c r="V179" s="6">
@@ -13051,14 +13117,14 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B180" s="5" t="s">
         <v>745</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>746</v>
       </c>
       <c r="C180" s="5"/>
       <c r="D180" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>45</v>
@@ -13070,11 +13136,11 @@
       <c r="H180" s="5"/>
       <c r="I180" s="5"/>
       <c r="J180" s="5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="K180" s="5"/>
       <c r="L180" s="8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="M180" s="5"/>
       <c r="N180" s="5"/>
@@ -13090,7 +13156,7 @@
       <c r="T180" s="6">
         <v>550</v>
       </c>
-      <c r="U180" s="6">
+      <c r="U180" s="39">
         <v>400</v>
       </c>
       <c r="V180" s="6">
@@ -13102,14 +13168,14 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>745</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>746</v>
       </c>
       <c r="C181" s="5"/>
       <c r="D181" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>45</v>
@@ -13121,11 +13187,11 @@
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
       <c r="J181" s="5" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="K181" s="5"/>
       <c r="L181" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="M181" s="5"/>
       <c r="N181" s="5"/>
@@ -13141,7 +13207,7 @@
       <c r="T181" s="6">
         <v>290</v>
       </c>
-      <c r="U181" s="6">
+      <c r="U181" s="39">
         <v>150</v>
       </c>
       <c r="V181" s="6">
@@ -13153,30 +13219,30 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C182" s="5"/>
       <c r="D182" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="E182" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="F182" s="5" t="s">
         <v>760</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>761</v>
       </c>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
       <c r="J182" s="5" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="K182" s="5"/>
       <c r="L182" s="8" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="M182" s="5"/>
       <c r="N182" s="5"/>
@@ -13192,7 +13258,7 @@
       <c r="T182" s="6">
         <v>235</v>
       </c>
-      <c r="U182" s="6">
+      <c r="U182" s="39">
         <v>94</v>
       </c>
       <c r="V182" s="6">
@@ -13204,30 +13270,30 @@
     </row>
     <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C183" s="5"/>
       <c r="D183" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
       <c r="J183" s="5" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="K183" s="5"/>
       <c r="L183" s="8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M183" s="5"/>
       <c r="N183" s="5"/>
@@ -13243,7 +13309,7 @@
       <c r="T183" s="6">
         <v>57</v>
       </c>
-      <c r="U183" s="6">
+      <c r="U183" s="39">
         <v>43</v>
       </c>
       <c r="V183" s="6">
@@ -13255,30 +13321,30 @@
     </row>
     <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B184" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C184" s="5"/>
       <c r="D184" s="6" t="s">
         <v>203</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G184" s="5"/>
       <c r="H184" s="5"/>
       <c r="I184" s="5"/>
       <c r="J184" s="5" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="K184" s="5"/>
       <c r="L184" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="M184" s="5"/>
       <c r="N184" s="5"/>
@@ -13294,7 +13360,7 @@
       <c r="T184" s="6">
         <v>48</v>
       </c>
-      <c r="U184" s="6">
+      <c r="U184" s="39">
         <v>23</v>
       </c>
       <c r="V184" s="6">
@@ -13306,30 +13372,30 @@
     </row>
     <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C185" s="5"/>
       <c r="D185" s="6" t="s">
         <v>333</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G185" s="5"/>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
       <c r="J185" s="5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K185" s="5"/>
       <c r="L185" s="8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="M185" s="5"/>
       <c r="N185" s="5"/>
@@ -13345,7 +13411,7 @@
       <c r="T185" s="6">
         <v>145</v>
       </c>
-      <c r="U185" s="6">
+      <c r="U185" s="39">
         <v>81</v>
       </c>
       <c r="V185" s="6">
@@ -13357,30 +13423,30 @@
     </row>
     <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C186" s="5"/>
       <c r="D186" s="6">
         <v>1896</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G186" s="5"/>
       <c r="H186" s="5"/>
       <c r="I186" s="5"/>
       <c r="J186" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K186" s="5"/>
       <c r="L186" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M186" s="5"/>
       <c r="N186" s="5"/>
@@ -13396,7 +13462,7 @@
       <c r="T186" s="6">
         <v>59</v>
       </c>
-      <c r="U186" s="6">
+      <c r="U186" s="39">
         <v>26</v>
       </c>
       <c r="V186" s="6">
@@ -13408,17 +13474,17 @@
     </row>
     <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C187" s="5"/>
       <c r="D187" s="6" t="s">
         <v>425</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>205</v>
@@ -13427,11 +13493,11 @@
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
       <c r="J187" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K187" s="5"/>
       <c r="L187" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M187" s="5"/>
       <c r="N187" s="5"/>
@@ -13447,7 +13513,7 @@
       <c r="T187" s="6">
         <v>57</v>
       </c>
-      <c r="U187" s="6">
+      <c r="U187" s="39">
         <v>43</v>
       </c>
       <c r="V187" s="6">
@@ -13459,30 +13525,30 @@
     </row>
     <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B188" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C188" s="5"/>
       <c r="D188" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G188" s="5"/>
       <c r="H188" s="5"/>
       <c r="I188" s="5"/>
       <c r="J188" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K188" s="5"/>
       <c r="L188" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="M188" s="5"/>
       <c r="N188" s="5"/>
@@ -13498,7 +13564,7 @@
       <c r="T188" s="6">
         <v>135</v>
       </c>
-      <c r="U188" s="6">
+      <c r="U188" s="39">
         <v>203</v>
       </c>
       <c r="V188" s="6">
@@ -13510,30 +13576,30 @@
     </row>
     <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B189" s="5" t="s">
         <v>757</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>758</v>
       </c>
       <c r="C189" s="5"/>
       <c r="D189" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G189" s="5"/>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
       <c r="J189" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K189" s="5"/>
       <c r="L189" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="M189" s="5"/>
       <c r="N189" s="5"/>
@@ -13549,7 +13615,7 @@
       <c r="T189" s="6">
         <v>135</v>
       </c>
-      <c r="U189" s="6">
+      <c r="U189" s="39">
         <v>201</v>
       </c>
       <c r="V189" s="6">
@@ -13561,30 +13627,30 @@
     </row>
     <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>782</v>
+        <v>1226</v>
       </c>
       <c r="C190" s="5"/>
       <c r="D190" s="6">
         <v>1886</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G190" s="5"/>
       <c r="H190" s="5"/>
       <c r="I190" s="5"/>
       <c r="J190" s="5" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K190" s="5"/>
       <c r="L190" s="8" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M190" s="5"/>
       <c r="N190" s="5"/>
@@ -13600,7 +13666,7 @@
       <c r="T190" s="6">
         <v>45</v>
       </c>
-      <c r="U190" s="6">
+      <c r="U190" s="39">
         <v>16</v>
       </c>
       <c r="V190" s="6">
@@ -13612,17 +13678,17 @@
     </row>
     <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>782</v>
+        <v>1226</v>
       </c>
       <c r="C191" s="5"/>
       <c r="D191" s="6" t="s">
         <v>91</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>205</v>
@@ -13631,11 +13697,11 @@
       <c r="H191" s="5"/>
       <c r="I191" s="5"/>
       <c r="J191" s="5" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="K191" s="5"/>
       <c r="L191" s="8" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M191" s="5"/>
       <c r="N191" s="5"/>
@@ -13651,7 +13717,7 @@
       <c r="T191" s="6">
         <v>71</v>
       </c>
-      <c r="U191" s="6">
+      <c r="U191" s="39">
         <v>30</v>
       </c>
       <c r="V191" s="6">
@@ -13663,30 +13729,30 @@
     </row>
     <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>782</v>
+        <v>1226</v>
       </c>
       <c r="C192" s="5"/>
       <c r="D192" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
       <c r="I192" s="5"/>
       <c r="J192" s="5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K192" s="5"/>
       <c r="L192" s="8" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="M192" s="5"/>
       <c r="N192" s="5"/>
@@ -13697,12 +13763,12 @@
         <v>30</v>
       </c>
       <c r="S192" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="T192" s="6">
         <v>62</v>
       </c>
-      <c r="U192" s="6">
+      <c r="U192" s="39">
         <v>45</v>
       </c>
       <c r="V192" s="6">
@@ -13714,30 +13780,30 @@
     </row>
     <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>782</v>
+        <v>1226</v>
       </c>
       <c r="C193" s="5"/>
       <c r="D193" s="6" t="s">
         <v>336</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
       <c r="I193" s="5"/>
       <c r="J193" s="5" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="K193" s="5"/>
       <c r="L193" s="8" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="M193" s="5"/>
       <c r="N193" s="5"/>
@@ -13753,7 +13819,7 @@
       <c r="T193" s="6">
         <v>67</v>
       </c>
-      <c r="U193" s="6">
+      <c r="U193" s="39">
         <v>18</v>
       </c>
       <c r="V193" s="6">
@@ -13765,14 +13831,14 @@
     </row>
     <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C194" s="5"/>
       <c r="D194" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E194" s="5" t="s">
         <v>45</v>
@@ -13784,11 +13850,11 @@
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
       <c r="J194" s="5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="K194" s="5"/>
       <c r="L194" s="25" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="M194" s="5"/>
       <c r="N194" s="5"/>
@@ -13804,7 +13870,7 @@
       <c r="T194" s="6">
         <v>163</v>
       </c>
-      <c r="U194" s="6">
+      <c r="U194" s="39">
         <v>251</v>
       </c>
       <c r="V194" s="6">
@@ -13816,10 +13882,10 @@
     </row>
     <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B195" s="16" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C195" s="16"/>
       <c r="D195" s="17" t="s">
@@ -13829,17 +13895,17 @@
         <v>45</v>
       </c>
       <c r="F195" s="16" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="G195" s="16"/>
       <c r="H195" s="16"/>
       <c r="I195" s="16"/>
       <c r="J195" s="16" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="K195" s="16"/>
       <c r="L195" s="9" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="M195" s="16"/>
       <c r="N195" s="16"/>
@@ -13855,7 +13921,7 @@
       <c r="T195" s="17">
         <v>40</v>
       </c>
-      <c r="U195" s="17">
+      <c r="U195" s="44">
         <v>19</v>
       </c>
       <c r="V195" s="17">
@@ -13867,17 +13933,17 @@
     </row>
     <row r="196" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C196" s="5"/>
       <c r="D196" s="6">
         <v>1908</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>205</v>
@@ -13886,11 +13952,11 @@
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
       <c r="J196" s="5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K196" s="5"/>
       <c r="L196" s="9" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="M196" s="5"/>
       <c r="N196" s="5"/>
@@ -13906,7 +13972,7 @@
       <c r="T196" s="6">
         <v>14</v>
       </c>
-      <c r="U196" s="6">
+      <c r="U196" s="39">
         <v>27</v>
       </c>
       <c r="V196" s="6">
@@ -13918,17 +13984,17 @@
     </row>
     <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C197" s="5"/>
       <c r="D197" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>205</v>
@@ -13937,11 +14003,11 @@
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
       <c r="J197" s="5" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="K197" s="5"/>
       <c r="L197" s="9" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="M197" s="5"/>
       <c r="N197" s="5"/>
@@ -13957,7 +14023,7 @@
       <c r="T197" s="6">
         <v>16</v>
       </c>
-      <c r="U197" s="6">
+      <c r="U197" s="39">
         <v>35</v>
       </c>
       <c r="V197" s="6">
@@ -13969,17 +14035,17 @@
     </row>
     <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C198" s="5"/>
       <c r="D198" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>205</v>
@@ -13988,11 +14054,11 @@
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
       <c r="J198" s="5" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="K198" s="5"/>
       <c r="L198" s="9" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="M198" s="5"/>
       <c r="N198" s="5"/>
@@ -14008,7 +14074,7 @@
       <c r="T198" s="6">
         <v>85</v>
       </c>
-      <c r="U198" s="6">
+      <c r="U198" s="39">
         <v>23</v>
       </c>
       <c r="V198" s="6">
@@ -14020,30 +14086,30 @@
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C199" s="5"/>
       <c r="D199" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="F199" s="5" t="s">
         <v>814</v>
-      </c>
-      <c r="E199" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>816</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
       <c r="J199" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="K199" s="5"/>
       <c r="L199" s="9" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="M199" s="5"/>
       <c r="N199" s="5"/>
@@ -14059,7 +14125,7 @@
       <c r="T199" s="6">
         <v>137</v>
       </c>
-      <c r="U199" s="6">
+      <c r="U199" s="39">
         <v>220</v>
       </c>
       <c r="V199" s="6">
@@ -14071,10 +14137,10 @@
     </row>
     <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C200" s="5"/>
       <c r="D200" s="6">
@@ -14090,11 +14156,11 @@
       <c r="H200" s="5"/>
       <c r="I200" s="5"/>
       <c r="J200" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="K200" s="5"/>
       <c r="L200" s="8" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="M200" s="5"/>
       <c r="N200" s="5"/>
@@ -14110,7 +14176,7 @@
       <c r="T200" s="6">
         <v>167</v>
       </c>
-      <c r="U200" s="6">
+      <c r="U200" s="39">
         <v>51</v>
       </c>
       <c r="V200" s="6">
@@ -14122,14 +14188,14 @@
     </row>
     <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C201" s="5"/>
       <c r="D201" s="6" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>73</v>
@@ -14141,11 +14207,11 @@
       <c r="H201" s="5"/>
       <c r="I201" s="5"/>
       <c r="J201" s="5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K201" s="5"/>
       <c r="L201" s="8" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="M201" s="5"/>
       <c r="N201" s="5"/>
@@ -14161,7 +14227,7 @@
       <c r="T201" s="6">
         <v>146</v>
       </c>
-      <c r="U201" s="6">
+      <c r="U201" s="39">
         <v>48</v>
       </c>
       <c r="V201" s="6">
@@ -14173,10 +14239,10 @@
     </row>
     <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C202" s="5"/>
       <c r="D202" s="6">
@@ -14186,17 +14252,17 @@
         <v>426</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
       <c r="I202" s="5"/>
       <c r="J202" s="5" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="K202" s="5"/>
       <c r="L202" s="8" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="M202" s="5"/>
       <c r="N202" s="5"/>
@@ -14212,7 +14278,7 @@
       <c r="T202" s="6">
         <v>62</v>
       </c>
-      <c r="U202" s="6">
+      <c r="U202" s="39">
         <v>48</v>
       </c>
       <c r="V202" s="6">
@@ -14224,10 +14290,10 @@
     </row>
     <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C203" s="5"/>
       <c r="D203" s="6">
@@ -14237,17 +14303,17 @@
         <v>134</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
       <c r="I203" s="5"/>
       <c r="J203" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="K203" s="5"/>
       <c r="L203" s="8" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="M203" s="5"/>
       <c r="N203" s="5"/>
@@ -14263,7 +14329,7 @@
       <c r="T203" s="6">
         <v>168</v>
       </c>
-      <c r="U203" s="6">
+      <c r="U203" s="39">
         <v>58</v>
       </c>
       <c r="V203" s="6">
@@ -14275,10 +14341,10 @@
     </row>
     <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C204" s="5"/>
       <c r="D204" s="6">
@@ -14294,11 +14360,11 @@
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
       <c r="J204" s="5" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="K204" s="5"/>
       <c r="L204" s="8" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="M204" s="5"/>
       <c r="N204" s="5"/>
@@ -14314,7 +14380,7 @@
       <c r="T204" s="6">
         <v>172</v>
       </c>
-      <c r="U204" s="6">
+      <c r="U204" s="39">
         <v>102</v>
       </c>
       <c r="V204" s="6">
@@ -14326,10 +14392,10 @@
     </row>
     <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C205" s="5"/>
       <c r="D205" s="6">
@@ -14345,11 +14411,11 @@
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
       <c r="J205" s="5" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="K205" s="5"/>
       <c r="L205" s="8" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="M205" s="5"/>
       <c r="N205" s="5"/>
@@ -14365,7 +14431,7 @@
       <c r="T205" s="6">
         <v>118</v>
       </c>
-      <c r="U205" s="6">
+      <c r="U205" s="39">
         <v>67</v>
       </c>
       <c r="V205" s="6">
@@ -14377,10 +14443,10 @@
     </row>
     <row r="206" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C206" s="5"/>
       <c r="D206" s="6">
@@ -14396,11 +14462,11 @@
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
       <c r="J206" s="5" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="K206" s="5"/>
       <c r="L206" s="8" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="M206" s="5"/>
       <c r="N206" s="5"/>
@@ -14416,7 +14482,7 @@
       <c r="T206" s="6">
         <v>120</v>
       </c>
-      <c r="U206" s="6">
+      <c r="U206" s="39">
         <v>60</v>
       </c>
       <c r="V206" s="6">
@@ -14428,10 +14494,10 @@
     </row>
     <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C207" s="5"/>
       <c r="D207" s="6">
@@ -14447,11 +14513,11 @@
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
       <c r="J207" s="5" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K207" s="5"/>
       <c r="L207" s="8" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="M207" s="5"/>
       <c r="N207" s="5"/>
@@ -14467,7 +14533,7 @@
       <c r="T207" s="6">
         <v>210</v>
       </c>
-      <c r="U207" s="6">
+      <c r="U207" s="39">
         <v>110</v>
       </c>
       <c r="V207" s="6">
@@ -14479,30 +14545,30 @@
     </row>
     <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C208" s="5"/>
       <c r="D208" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E208" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
       <c r="J208" s="5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K208" s="5"/>
       <c r="L208" s="34" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="M208" s="5"/>
       <c r="N208" s="5"/>
@@ -14518,7 +14584,7 @@
       <c r="T208" s="6">
         <v>330</v>
       </c>
-      <c r="U208" s="6">
+      <c r="U208" s="39">
         <v>120</v>
       </c>
       <c r="V208" s="6">
@@ -14530,10 +14596,10 @@
     </row>
     <row r="209" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C209" s="5"/>
       <c r="D209" s="6" t="s">
@@ -14549,11 +14615,11 @@
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
       <c r="J209" s="5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="K209" s="5"/>
       <c r="L209" s="34" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="M209" s="5"/>
       <c r="N209" s="5"/>
@@ -14569,7 +14635,7 @@
       <c r="T209" s="6">
         <v>90</v>
       </c>
-      <c r="U209" s="6">
+      <c r="U209" s="39">
         <v>60</v>
       </c>
       <c r="V209" s="6">
@@ -14581,36 +14647,39 @@
     </row>
     <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="D210" s="6" t="s">
         <v>847</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="D210" s="6" t="s">
-        <v>849</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F210" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="G210" s="10" t="s">
         <v>850</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="L210" s="10" t="s">
-        <v>852</v>
+        <v>849</v>
+      </c>
+      <c r="L210" s="34" t="s">
+        <v>1223</v>
       </c>
       <c r="R210" s="5" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="S210" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T210" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="U210" s="6">
+        <v>1140</v>
+      </c>
+      <c r="U210" s="39">
         <v>900</v>
       </c>
       <c r="V210" s="6">
@@ -14622,36 +14691,36 @@
     </row>
     <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F211" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="J211" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="L211" s="10" t="s">
         <v>854</v>
       </c>
-      <c r="J211" s="2" t="s">
+      <c r="R211" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="L211" s="10" t="s">
+      <c r="S211" s="5" t="s">
         <v>856</v>
-      </c>
-      <c r="R211" s="5" t="s">
-        <v>857</v>
-      </c>
-      <c r="S211" s="5" t="s">
-        <v>858</v>
       </c>
       <c r="T211" s="6">
         <v>166</v>
       </c>
-      <c r="U211" s="6">
+      <c r="U211" s="39">
         <v>269</v>
       </c>
       <c r="V211" s="6">
@@ -14663,28 +14732,28 @@
     </row>
     <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D212" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="E212" s="2" t="s">
+      <c r="J212" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L212" s="10" t="s">
         <v>860</v>
       </c>
-      <c r="F212" s="2" t="s">
+      <c r="R212" s="5" t="s">
         <v>861</v>
-      </c>
-      <c r="J212" s="2" t="s">
-        <v>1217</v>
-      </c>
-      <c r="L212" s="10" t="s">
-        <v>862</v>
-      </c>
-      <c r="R212" s="5" t="s">
-        <v>863</v>
       </c>
       <c r="S212" s="5" t="s">
         <v>31</v>
@@ -14692,7 +14761,7 @@
       <c r="T212" s="6">
         <v>295</v>
       </c>
-      <c r="U212" s="6">
+      <c r="U212" s="39">
         <v>200</v>
       </c>
       <c r="V212" s="6">
@@ -14704,28 +14773,28 @@
     </row>
     <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>544</v>
       </c>
       <c r="E213" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="J213" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="L213" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="F213" s="2" t="s">
+      <c r="R213" s="5" t="s">
         <v>865</v>
-      </c>
-      <c r="J213" s="2" t="s">
-        <v>1216</v>
-      </c>
-      <c r="L213" s="10" t="s">
-        <v>866</v>
-      </c>
-      <c r="R213" s="5" t="s">
-        <v>867</v>
       </c>
       <c r="S213" s="5" t="s">
         <v>31</v>
@@ -14733,7 +14802,7 @@
       <c r="T213" s="6">
         <v>240</v>
       </c>
-      <c r="U213" s="6">
+      <c r="U213" s="39">
         <v>90</v>
       </c>
       <c r="V213" s="6">
@@ -14745,28 +14814,28 @@
     </row>
     <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F214" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="J214" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K214" t="s">
+        <v>868</v>
+      </c>
+      <c r="L214" s="34" t="s">
         <v>869</v>
-      </c>
-      <c r="J214" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="K214" t="s">
-        <v>870</v>
-      </c>
-      <c r="L214" s="34" t="s">
-        <v>871</v>
       </c>
       <c r="R214" s="5" t="s">
         <v>164</v>
@@ -14775,9 +14844,9 @@
         <v>31</v>
       </c>
       <c r="T214" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="U214" s="6">
+        <v>870</v>
+      </c>
+      <c r="U214" s="39">
         <v>150</v>
       </c>
       <c r="V214" s="6">
@@ -14789,28 +14858,28 @@
     </row>
     <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D215" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="E215" s="2" t="s">
+      <c r="J215" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="K215" t="s">
         <v>874</v>
       </c>
-      <c r="F215" s="2" t="s">
+      <c r="L215" s="34" t="s">
         <v>875</v>
-      </c>
-      <c r="J215" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="K215" t="s">
-        <v>876</v>
-      </c>
-      <c r="L215" s="34" t="s">
-        <v>877</v>
       </c>
       <c r="R215" s="5" t="s">
         <v>164</v>
@@ -14819,9 +14888,9 @@
         <v>31</v>
       </c>
       <c r="T215" s="6" t="s">
-        <v>878</v>
-      </c>
-      <c r="U215" s="6">
+        <v>876</v>
+      </c>
+      <c r="U215" s="39">
         <v>450</v>
       </c>
       <c r="V215" s="6">
@@ -14836,10 +14905,10 @@
         <v>64</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>154</v>
@@ -14848,10 +14917,10 @@
         <v>166</v>
       </c>
       <c r="J216" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="L216" s="10" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="R216" s="5" t="s">
         <v>30</v>
@@ -14862,7 +14931,7 @@
       <c r="T216" s="6">
         <v>180</v>
       </c>
-      <c r="U216" s="6">
+      <c r="U216" s="39">
         <v>60</v>
       </c>
       <c r="V216" s="6">
@@ -14877,10 +14946,10 @@
         <v>64</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>45</v>
@@ -14889,10 +14958,10 @@
         <v>236</v>
       </c>
       <c r="J217" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="L217" s="10" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="R217" s="5" t="s">
         <v>30</v>
@@ -14903,7 +14972,7 @@
       <c r="T217" s="6">
         <v>181</v>
       </c>
-      <c r="U217" s="6">
+      <c r="U217" s="39">
         <v>112</v>
       </c>
       <c r="V217" s="6">
@@ -14918,22 +14987,22 @@
         <v>64</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D218" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="E218" s="2" t="s">
+      <c r="J218" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="L218" s="10" t="s">
         <v>887</v>
-      </c>
-      <c r="J218" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="L218" s="10" t="s">
-        <v>889</v>
       </c>
       <c r="R218" s="5" t="s">
         <v>30</v>
@@ -14944,7 +15013,7 @@
       <c r="T218" s="6">
         <v>217</v>
       </c>
-      <c r="U218" s="6">
+      <c r="U218" s="39">
         <v>255</v>
       </c>
       <c r="V218" s="6">
@@ -14959,7 +15028,7 @@
         <v>64</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>425</v>
@@ -14971,10 +15040,10 @@
         <v>236</v>
       </c>
       <c r="J219" s="2" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="L219" s="10" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="R219" s="5" t="s">
         <v>30</v>
@@ -14985,7 +15054,7 @@
       <c r="T219" s="6">
         <v>270</v>
       </c>
-      <c r="U219" s="6">
+      <c r="U219" s="39">
         <v>120</v>
       </c>
       <c r="V219" s="6">
@@ -15000,11 +15069,11 @@
         <v>64</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C220" s="5"/>
       <c r="D220" s="6" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>45</v>
@@ -15016,11 +15085,11 @@
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="K220" s="5"/>
       <c r="L220" s="25" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M220" s="5"/>
       <c r="N220" s="5"/>
@@ -15036,7 +15105,7 @@
       <c r="T220" s="6">
         <v>189</v>
       </c>
-      <c r="U220" s="6">
+      <c r="U220" s="39">
         <v>98</v>
       </c>
       <c r="V220" s="6">
@@ -15051,7 +15120,7 @@
         <v>64</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C221" s="5"/>
       <c r="D221" s="6" t="s">
@@ -15067,11 +15136,11 @@
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="K221" s="5"/>
       <c r="L221" s="25" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="M221" s="5"/>
       <c r="N221" s="5"/>
@@ -15087,7 +15156,7 @@
       <c r="T221" s="6">
         <v>197</v>
       </c>
-      <c r="U221" s="6">
+      <c r="U221" s="39">
         <v>76</v>
       </c>
       <c r="V221" s="6">
@@ -15102,7 +15171,7 @@
         <v>64</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C222" s="5"/>
       <c r="D222" s="6" t="s">
@@ -15118,11 +15187,11 @@
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="K222" s="5"/>
       <c r="L222" s="25" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="M222" s="5"/>
       <c r="N222" s="5"/>
@@ -15138,7 +15207,7 @@
       <c r="T222" s="6">
         <v>213</v>
       </c>
-      <c r="U222" s="6">
+      <c r="U222" s="39">
         <v>78</v>
       </c>
       <c r="V222" s="6">
@@ -15153,7 +15222,7 @@
         <v>64</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C223" s="5"/>
       <c r="D223" s="6" t="s">
@@ -15169,11 +15238,11 @@
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="K223" s="5"/>
       <c r="L223" s="25" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="M223" s="5"/>
       <c r="N223" s="5"/>
@@ -15189,7 +15258,7 @@
       <c r="T223" s="6">
         <v>74</v>
       </c>
-      <c r="U223" s="6">
+      <c r="U223" s="39">
         <v>60</v>
       </c>
       <c r="V223" s="6">
@@ -15201,30 +15270,30 @@
     </row>
     <row r="224" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>901</v>
+        <v>1225</v>
       </c>
       <c r="C224" s="5"/>
       <c r="D224" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="K224" s="5"/>
       <c r="L224" s="8" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="M224" s="5"/>
       <c r="N224" s="5"/>
@@ -15240,7 +15309,7 @@
       <c r="T224" s="6">
         <v>31</v>
       </c>
-      <c r="U224" s="6">
+      <c r="U224" s="39">
         <v>30</v>
       </c>
       <c r="V224" s="6">
@@ -15252,30 +15321,30 @@
     </row>
     <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>901</v>
+        <v>1225</v>
       </c>
       <c r="C225" s="5"/>
       <c r="D225" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="G225" s="5"/>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="K225" s="5"/>
       <c r="L225" s="8" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="M225" s="5"/>
       <c r="N225" s="5"/>
@@ -15286,12 +15355,12 @@
         <v>30</v>
       </c>
       <c r="S225" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="T225" s="6">
         <v>23</v>
       </c>
-      <c r="U225" s="6">
+      <c r="U225" s="39">
         <v>23</v>
       </c>
       <c r="V225" s="6">
@@ -15303,10 +15372,10 @@
     </row>
     <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>901</v>
+        <v>1225</v>
       </c>
       <c r="C226" s="5"/>
       <c r="D226" s="6" t="s">
@@ -15316,17 +15385,17 @@
         <v>45</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="K226" s="5"/>
       <c r="L226" s="8" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="M226" s="5"/>
       <c r="N226" s="5"/>
@@ -15337,12 +15406,12 @@
         <v>180</v>
       </c>
       <c r="S226" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="T226" s="6">
         <v>48</v>
       </c>
-      <c r="U226" s="6">
+      <c r="U226" s="39">
         <v>46</v>
       </c>
       <c r="V226" s="6">
@@ -15354,10 +15423,10 @@
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>901</v>
+        <v>1225</v>
       </c>
       <c r="C227" s="5"/>
       <c r="D227" s="6" t="s">
@@ -15373,11 +15442,11 @@
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="K227" s="5"/>
       <c r="L227" s="8" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="M227" s="5"/>
       <c r="N227" s="5"/>
@@ -15388,12 +15457,12 @@
         <v>30</v>
       </c>
       <c r="S227" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="T227" s="6">
         <v>23</v>
       </c>
-      <c r="U227" s="6">
+      <c r="U227" s="39">
         <v>18</v>
       </c>
       <c r="V227" s="6">
@@ -15405,32 +15474,32 @@
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>901</v>
+        <v>1225</v>
       </c>
       <c r="C228" s="5"/>
       <c r="D228" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="K228" s="5" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="L228" s="34" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="M228" s="5"/>
       <c r="N228" s="5"/>
@@ -15441,12 +15510,12 @@
         <v>30</v>
       </c>
       <c r="S228" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="T228" s="6">
         <v>36</v>
       </c>
-      <c r="U228" s="6">
+      <c r="U228" s="39">
         <v>25</v>
       </c>
       <c r="V228" s="6">
@@ -15458,32 +15527,32 @@
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>901</v>
+        <v>1225</v>
       </c>
       <c r="C229" s="5"/>
       <c r="D229" s="6" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="K229" s="5" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="L229" s="34" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="M229" s="5"/>
       <c r="N229" s="5"/>
@@ -15494,12 +15563,12 @@
         <v>30</v>
       </c>
       <c r="S229" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="T229" s="6">
         <v>35</v>
       </c>
-      <c r="U229" s="6">
+      <c r="U229" s="39">
         <v>25</v>
       </c>
       <c r="V229" s="6">
@@ -15511,13 +15580,13 @@
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>45</v>
@@ -15526,10 +15595,10 @@
         <v>107</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="L230" s="10" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="R230" s="5" t="s">
         <v>30</v>
@@ -15540,7 +15609,7 @@
       <c r="T230" s="6">
         <v>96</v>
       </c>
-      <c r="U230" s="6">
+      <c r="U230" s="39">
         <v>75</v>
       </c>
       <c r="V230" s="6">
@@ -15552,30 +15621,30 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="19" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B231" s="19" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C231" s="19"/>
       <c r="D231" s="23" t="s">
+        <v>922</v>
+      </c>
+      <c r="E231" s="19" t="s">
         <v>925</v>
       </c>
-      <c r="E231" s="19" t="s">
-        <v>928</v>
-      </c>
       <c r="F231" s="19" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G231" s="19"/>
       <c r="H231" s="19"/>
       <c r="I231" s="19"/>
       <c r="J231" s="19" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="K231" s="19"/>
       <c r="L231" s="20" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="M231" s="21"/>
       <c r="N231" s="21"/>
@@ -15586,12 +15655,12 @@
         <v>30</v>
       </c>
       <c r="S231" s="22" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="T231" s="23">
         <v>82</v>
       </c>
-      <c r="U231" s="23">
+      <c r="U231" s="45">
         <v>88</v>
       </c>
       <c r="V231" s="23">
@@ -15603,13 +15672,13 @@
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>73</v>
@@ -15618,16 +15687,16 @@
         <v>268</v>
       </c>
       <c r="J232" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="L232" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="M232" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="N232" s="10" t="s">
         <v>934</v>
-      </c>
-      <c r="L232" s="10" t="s">
-        <v>935</v>
-      </c>
-      <c r="M232" s="4" t="s">
-        <v>936</v>
-      </c>
-      <c r="N232" s="10" t="s">
-        <v>937</v>
       </c>
       <c r="R232" s="5" t="s">
         <v>30</v>
@@ -15638,7 +15707,7 @@
       <c r="T232" s="6">
         <v>63</v>
       </c>
-      <c r="U232" s="6">
+      <c r="U232" s="39">
         <v>32</v>
       </c>
       <c r="V232" s="6">
@@ -15650,31 +15719,31 @@
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F233" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="J233" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="L233" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="M233" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="N233" s="10" t="s">
         <v>938</v>
-      </c>
-      <c r="J233" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="L233" s="10" t="s">
-        <v>937</v>
-      </c>
-      <c r="M233" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="N233" s="10" t="s">
-        <v>941</v>
       </c>
       <c r="R233" s="5" t="s">
         <v>180</v>
@@ -15685,7 +15754,7 @@
       <c r="T233" s="6">
         <v>1160</v>
       </c>
-      <c r="U233" s="6">
+      <c r="U233" s="39">
         <v>600</v>
       </c>
       <c r="V233" s="6">
@@ -15697,25 +15766,25 @@
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="J234" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="L234" s="10" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="R234" s="5" t="s">
         <v>30</v>
@@ -15726,7 +15795,7 @@
       <c r="T234" s="6">
         <v>315</v>
       </c>
-      <c r="U234" s="6">
+      <c r="U234" s="39">
         <v>175</v>
       </c>
       <c r="V234" s="6">
@@ -15738,25 +15807,25 @@
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D235" s="6" t="s">
         <v>527</v>
       </c>
       <c r="E235" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="J235" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="L235" s="10" t="s">
         <v>946</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="J235" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="L235" s="10" t="s">
-        <v>949</v>
       </c>
       <c r="R235" s="5" t="s">
         <v>30</v>
@@ -15767,7 +15836,7 @@
       <c r="T235" s="6">
         <v>215</v>
       </c>
-      <c r="U235" s="6">
+      <c r="U235" s="39">
         <v>195</v>
       </c>
       <c r="V235" s="6">
@@ -15779,10 +15848,10 @@
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C236" s="5"/>
       <c r="D236" s="6">
@@ -15792,17 +15861,17 @@
         <v>45</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="K236" s="5"/>
       <c r="L236" s="8" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="M236" s="5"/>
       <c r="N236" s="5"/>
@@ -15818,7 +15887,7 @@
       <c r="T236" s="6">
         <v>200</v>
       </c>
-      <c r="U236" s="6">
+      <c r="U236" s="39">
         <v>70</v>
       </c>
       <c r="V236" s="6">
@@ -15830,17 +15899,17 @@
     </row>
     <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C237" s="5"/>
       <c r="D237" s="6">
         <v>1848</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>205</v>
@@ -15849,11 +15918,11 @@
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="K237" s="5"/>
       <c r="L237" s="8" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="M237" s="5"/>
       <c r="N237" s="5"/>
@@ -15869,7 +15938,7 @@
       <c r="T237" s="6">
         <v>253</v>
       </c>
-      <c r="U237" s="6">
+      <c r="U237" s="39">
         <v>120</v>
       </c>
       <c r="V237" s="6">
@@ -15881,10 +15950,10 @@
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>336</v>
@@ -15893,13 +15962,13 @@
         <v>319</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="L238" s="10" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="R238" s="5" t="s">
         <v>180</v>
@@ -15910,7 +15979,7 @@
       <c r="T238" s="6">
         <v>340</v>
       </c>
-      <c r="U238" s="6">
+      <c r="U238" s="39">
         <v>430</v>
       </c>
       <c r="W238" s="6">
@@ -15919,10 +15988,10 @@
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D239" s="6" t="s">
         <v>333</v>
@@ -15937,7 +16006,7 @@
         <v>555</v>
       </c>
       <c r="L239" s="10" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="R239" s="5" t="s">
         <v>30</v>
@@ -15948,7 +16017,7 @@
       <c r="T239" s="6">
         <v>258</v>
       </c>
-      <c r="U239" s="6">
+      <c r="U239" s="39">
         <v>136</v>
       </c>
       <c r="V239" s="6">
@@ -15960,25 +16029,25 @@
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D240" s="6" t="s">
         <v>571</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="L240" s="10" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="R240" s="5" t="s">
         <v>30</v>
@@ -15989,7 +16058,7 @@
       <c r="T240" s="6">
         <v>366</v>
       </c>
-      <c r="U240">
+      <c r="U240" s="33">
         <v>250</v>
       </c>
       <c r="V240" s="6">
@@ -16001,25 +16070,25 @@
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>571</v>
       </c>
       <c r="E241" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="J241" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="L241" s="10" t="s">
         <v>963</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="J241" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="L241" s="10" t="s">
-        <v>966</v>
       </c>
       <c r="R241" s="5" t="s">
         <v>30</v>
@@ -16030,7 +16099,7 @@
       <c r="T241" s="6">
         <v>270</v>
       </c>
-      <c r="U241" s="6">
+      <c r="U241" s="39">
         <v>165</v>
       </c>
       <c r="V241" s="6">
@@ -16042,34 +16111,34 @@
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C242" s="5"/>
       <c r="D242" s="6" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="G242" s="34" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="H242" s="5"/>
       <c r="I242" s="34" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="K242" s="5"/>
       <c r="L242" s="25" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="M242" s="5"/>
       <c r="N242" s="5"/>
@@ -16077,19 +16146,19 @@
       <c r="P242" s="5"/>
       <c r="Q242" s="5"/>
       <c r="R242" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="S242" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="T242" s="6">
-        <v>472</v>
-      </c>
-      <c r="U242" s="6">
-        <v>1295</v>
+      <c r="T242" s="6" t="s">
+        <v>1228</v>
+      </c>
+      <c r="U242" s="39">
+        <v>400</v>
       </c>
       <c r="V242" s="6">
-        <v>935</v>
+        <v>150</v>
       </c>
       <c r="W242" s="6">
         <v>2</v>
@@ -16097,10 +16166,10 @@
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C243" s="5"/>
       <c r="D243" s="6" t="s">
@@ -16110,19 +16179,19 @@
         <v>134</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="G243" s="5"/>
       <c r="H243" s="5"/>
       <c r="I243" s="5"/>
       <c r="J243" s="5" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="K243" s="5" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="L243" s="34" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="M243" s="5"/>
       <c r="N243" s="5"/>
@@ -16133,12 +16202,12 @@
         <v>63</v>
       </c>
       <c r="S243" s="5" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="T243" s="6">
         <v>180</v>
       </c>
-      <c r="U243" s="6">
+      <c r="U243" s="39">
         <v>140</v>
       </c>
       <c r="V243" s="6">
@@ -16150,30 +16219,30 @@
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C244" s="5"/>
       <c r="D244" s="6">
         <v>1888</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="G244" s="5"/>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
       <c r="J244" s="5" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="K244" s="5"/>
       <c r="L244" s="8" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="M244" s="5"/>
       <c r="N244" s="5"/>
@@ -16189,7 +16258,7 @@
       <c r="T244" s="6">
         <v>130</v>
       </c>
-      <c r="U244" s="6">
+      <c r="U244" s="39">
         <v>160</v>
       </c>
       <c r="V244" s="6">
@@ -16201,30 +16270,30 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C245" s="5"/>
       <c r="D245" s="6">
         <v>1878</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="G245" s="5"/>
       <c r="H245" s="5"/>
       <c r="I245" s="5"/>
       <c r="J245" s="5" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="K245" s="5"/>
       <c r="L245" s="8" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="M245" s="5"/>
       <c r="N245" s="5"/>
@@ -16240,7 +16309,7 @@
       <c r="T245" s="6">
         <v>132</v>
       </c>
-      <c r="U245" s="6">
+      <c r="U245" s="39">
         <v>100</v>
       </c>
       <c r="V245" s="6">
@@ -16252,30 +16321,30 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C246" s="5"/>
       <c r="D246" s="6">
         <v>1899</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="G246" s="5"/>
       <c r="H246" s="5"/>
       <c r="I246" s="5"/>
       <c r="J246" s="5" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="K246" s="5"/>
       <c r="L246" s="8" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="M246" s="5"/>
       <c r="N246" s="5"/>
@@ -16291,7 +16360,7 @@
       <c r="T246" s="6">
         <v>280</v>
       </c>
-      <c r="U246" s="6">
+      <c r="U246" s="39">
         <v>130</v>
       </c>
       <c r="V246" s="6">
@@ -16303,30 +16372,30 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C247" s="5"/>
       <c r="D247" s="6">
         <v>1891</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="G247" s="5"/>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="K247" s="5"/>
       <c r="L247" s="8" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M247" s="5"/>
       <c r="N247" s="5"/>
@@ -16342,7 +16411,7 @@
       <c r="T247" s="6">
         <v>107</v>
       </c>
-      <c r="U247" s="6">
+      <c r="U247" s="39">
         <v>135</v>
       </c>
       <c r="V247" s="6">
@@ -16354,34 +16423,34 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C248" s="5"/>
       <c r="D248" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="G248" s="25" t="s">
         <v>990</v>
-      </c>
-      <c r="E248" s="5" t="s">
-        <v>960</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>991</v>
-      </c>
-      <c r="G248" s="25" t="s">
-        <v>993</v>
       </c>
       <c r="H248" s="5"/>
       <c r="I248" s="34" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="J248" s="5" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="K248" s="5"/>
       <c r="L248" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="M248" s="5"/>
       <c r="N248" s="5"/>
@@ -16389,15 +16458,15 @@
       <c r="P248" s="5"/>
       <c r="Q248" s="5"/>
       <c r="R248" s="5" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="S248" s="5" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="T248" s="6">
         <v>730</v>
       </c>
-      <c r="U248" s="6">
+      <c r="U248" s="39">
         <v>3866</v>
       </c>
       <c r="V248" s="6">
@@ -16409,34 +16478,34 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C249" s="5"/>
       <c r="D249" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="G249" s="34" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="H249" s="5"/>
       <c r="I249" s="34" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="K249" s="5"/>
       <c r="L249" s="8" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="M249" s="5"/>
       <c r="N249" s="5"/>
@@ -16444,7 +16513,7 @@
       <c r="P249" s="5"/>
       <c r="Q249" s="5"/>
       <c r="R249" s="5" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="S249" s="5" t="s">
         <v>31</v>
@@ -16452,10 +16521,10 @@
       <c r="T249" s="6">
         <v>670</v>
       </c>
-      <c r="U249">
+      <c r="U249" s="33">
         <v>500</v>
       </c>
-      <c r="V249">
+      <c r="V249" s="3">
         <v>500</v>
       </c>
       <c r="W249" s="6">
@@ -16464,30 +16533,30 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C250" s="5"/>
       <c r="D250" s="6" t="s">
         <v>187</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="G250" s="5"/>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="K250" s="5"/>
       <c r="L250" s="8" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="M250" s="5"/>
       <c r="N250" s="5"/>
@@ -16498,12 +16567,12 @@
         <v>30</v>
       </c>
       <c r="S250" s="5" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="T250" s="6">
         <v>1463</v>
       </c>
-      <c r="U250" s="6">
+      <c r="U250" s="39">
         <v>440</v>
       </c>
       <c r="V250" s="6">
@@ -16515,30 +16584,30 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C251" s="5"/>
       <c r="D251" s="6" t="s">
         <v>193</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="G251" s="5"/>
       <c r="H251" s="5"/>
       <c r="I251" s="5"/>
       <c r="J251" s="5" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="K251" s="5"/>
       <c r="L251" s="8" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="M251" s="5"/>
       <c r="N251" s="5"/>
@@ -16554,7 +16623,7 @@
       <c r="T251" s="6">
         <v>305</v>
       </c>
-      <c r="U251" s="6">
+      <c r="U251" s="39">
         <v>120</v>
       </c>
       <c r="V251" s="6">
@@ -16566,10 +16635,10 @@
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C252" s="5"/>
       <c r="D252" s="6">
@@ -16579,17 +16648,17 @@
         <v>560</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G252" s="5"/>
       <c r="H252" s="5"/>
       <c r="I252" s="5"/>
       <c r="J252" s="5" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="K252" s="5"/>
       <c r="L252" s="8" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="M252" s="5"/>
       <c r="N252" s="5"/>
@@ -16605,7 +16674,7 @@
       <c r="T252" s="6">
         <v>241</v>
       </c>
-      <c r="U252" s="6">
+      <c r="U252" s="39">
         <v>151</v>
       </c>
       <c r="V252" s="6">
@@ -16617,10 +16686,10 @@
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C253" s="5"/>
       <c r="D253" s="6">
@@ -16630,17 +16699,17 @@
         <v>560</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="G253" s="5"/>
       <c r="H253" s="5"/>
       <c r="I253" s="5"/>
       <c r="J253" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="K253" s="5"/>
       <c r="L253" s="8" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="M253" s="5"/>
       <c r="N253" s="5"/>
@@ -16656,7 +16725,7 @@
       <c r="T253" s="6">
         <v>175</v>
       </c>
-      <c r="U253" s="6">
+      <c r="U253" s="39">
         <v>65</v>
       </c>
       <c r="V253" s="6">
@@ -16668,10 +16737,10 @@
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C254" s="5"/>
       <c r="D254" s="6">
@@ -16681,17 +16750,17 @@
         <v>560</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="G254" s="5"/>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
       <c r="J254" s="5" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="K254" s="5"/>
       <c r="L254" s="8" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="M254" s="5"/>
       <c r="N254" s="5"/>
@@ -16707,7 +16776,7 @@
       <c r="T254" s="6">
         <v>195</v>
       </c>
-      <c r="U254" s="6">
+      <c r="U254" s="39">
         <v>90</v>
       </c>
       <c r="V254" s="6">
@@ -16719,10 +16788,10 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C255" s="5"/>
       <c r="D255" s="6">
@@ -16732,17 +16801,17 @@
         <v>560</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
       <c r="I255" s="5"/>
       <c r="J255" s="5" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="K255" s="5"/>
       <c r="L255" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="M255" s="5"/>
       <c r="N255" s="5"/>
@@ -16758,7 +16827,7 @@
       <c r="T255" s="6">
         <v>325</v>
       </c>
-      <c r="U255" s="6">
+      <c r="U255" s="39">
         <v>200</v>
       </c>
       <c r="V255" s="6">
@@ -16770,30 +16839,30 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C256" s="5"/>
       <c r="D256" s="6" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G256" s="5"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
       <c r="J256" s="5" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="K256" s="5"/>
       <c r="L256" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="M256" s="5"/>
       <c r="N256" s="5"/>
@@ -16809,7 +16878,7 @@
       <c r="T256" s="6">
         <v>242</v>
       </c>
-      <c r="U256" s="6">
+      <c r="U256" s="39">
         <v>90</v>
       </c>
       <c r="V256" s="6">
@@ -16821,30 +16890,30 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C257" s="5"/>
       <c r="D257" s="6" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
       <c r="J257" s="5" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="K257" s="5"/>
       <c r="L257" s="8" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="M257" s="5"/>
       <c r="N257" s="5"/>
@@ -16860,7 +16929,7 @@
       <c r="T257" s="6">
         <v>345</v>
       </c>
-      <c r="U257" s="6">
+      <c r="U257" s="39">
         <v>180</v>
       </c>
       <c r="V257" s="6">
@@ -16872,30 +16941,30 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C258" s="5"/>
       <c r="D258" s="6" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
       <c r="J258" s="5" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="K258" s="5"/>
       <c r="L258" s="8" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="M258" s="5"/>
       <c r="N258" s="5"/>
@@ -16906,12 +16975,12 @@
         <v>180</v>
       </c>
       <c r="S258" s="5" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="T258" s="6">
         <v>600</v>
       </c>
-      <c r="U258" s="6">
+      <c r="U258" s="39">
         <v>1000</v>
       </c>
       <c r="V258" s="6">
@@ -16923,30 +16992,30 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C259" s="5"/>
       <c r="D259" s="6" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
       <c r="J259" s="5" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="K259" s="5"/>
       <c r="L259" s="8" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="M259" s="5"/>
       <c r="N259" s="5"/>
@@ -16954,7 +17023,7 @@
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
       <c r="R259" s="5" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="S259" s="5" t="s">
         <v>35</v>
@@ -16962,7 +17031,7 @@
       <c r="T259" s="6">
         <v>93</v>
       </c>
-      <c r="U259" s="6">
+      <c r="U259" s="39">
         <v>118</v>
       </c>
       <c r="V259" s="6">
@@ -16974,30 +17043,30 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C260" s="5"/>
       <c r="D260" s="6" t="s">
         <v>255</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
       <c r="J260" s="5" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="K260" s="5"/>
       <c r="L260" s="8" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="M260" s="5"/>
       <c r="N260" s="5"/>
@@ -17013,7 +17082,7 @@
       <c r="T260" s="6">
         <v>280</v>
       </c>
-      <c r="U260" s="6">
+      <c r="U260" s="39">
         <v>110</v>
       </c>
       <c r="V260" s="6">
@@ -17025,32 +17094,32 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C261" s="5"/>
       <c r="D261" s="6" t="s">
         <v>494</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
       <c r="I261" s="34" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="K261" s="5"/>
       <c r="L261" s="8" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="M261" s="5"/>
       <c r="N261" s="5"/>
@@ -17058,7 +17127,7 @@
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
       <c r="R261" s="5" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="S261" s="5" t="s">
         <v>31</v>
@@ -17066,7 +17135,7 @@
       <c r="T261" s="6">
         <v>400</v>
       </c>
-      <c r="U261" s="6">
+      <c r="U261" s="39">
         <v>350</v>
       </c>
       <c r="V261" s="6">
@@ -17078,30 +17147,30 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C262" s="5"/>
       <c r="D262" s="6" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
       <c r="J262" s="5" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="K262" s="5"/>
       <c r="L262" s="8" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="M262" s="5"/>
       <c r="N262" s="5"/>
@@ -17117,7 +17186,7 @@
       <c r="T262" s="6">
         <v>161</v>
       </c>
-      <c r="U262" s="6">
+      <c r="U262" s="39">
         <v>50</v>
       </c>
       <c r="V262" s="6">
@@ -17129,10 +17198,10 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="27" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B263" s="27" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C263" s="27"/>
       <c r="D263" s="37">
@@ -17142,17 +17211,17 @@
         <v>538</v>
       </c>
       <c r="F263" s="27" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="G263" s="27"/>
       <c r="H263" s="27"/>
       <c r="I263" s="27"/>
       <c r="J263" s="27" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="K263" s="27"/>
       <c r="L263" s="36" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="M263" s="27"/>
       <c r="N263" s="27"/>
@@ -17160,7 +17229,7 @@
       <c r="P263" s="27"/>
       <c r="Q263" s="27"/>
       <c r="R263" s="27" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="S263" s="27" t="s">
         <v>35</v>
@@ -17168,10 +17237,10 @@
       <c r="T263" s="37">
         <v>700</v>
       </c>
-      <c r="U263" s="37">
+      <c r="U263" s="40">
         <v>450</v>
       </c>
-      <c r="V263" s="37">
+      <c r="V263" s="6">
         <v>2000</v>
       </c>
       <c r="W263" s="37">
@@ -17180,10 +17249,10 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C264" s="5"/>
       <c r="D264" s="6">
@@ -17199,11 +17268,11 @@
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
       <c r="J264" s="5" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="K264" s="5"/>
       <c r="L264" s="8" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="M264" s="5"/>
       <c r="N264" s="5"/>
@@ -17219,7 +17288,7 @@
       <c r="T264" s="3">
         <v>110</v>
       </c>
-      <c r="U264" s="3">
+      <c r="U264" s="46">
         <v>106</v>
       </c>
       <c r="V264" s="3">
@@ -17231,10 +17300,10 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C265" s="5"/>
       <c r="D265" s="6">
@@ -17244,17 +17313,17 @@
         <v>26</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
       <c r="J265" s="5" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="K265" s="5"/>
       <c r="L265" s="8" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="M265" s="5"/>
       <c r="N265" s="5"/>
@@ -17262,15 +17331,15 @@
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
       <c r="R265" s="5" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="S265" s="5" t="s">
         <v>31</v>
       </c>
       <c r="T265" s="3" t="s">
-        <v>1149</v>
-      </c>
-      <c r="U265" s="3">
+        <v>1145</v>
+      </c>
+      <c r="U265" s="46">
         <v>580</v>
       </c>
       <c r="V265" s="3">
@@ -17282,30 +17351,30 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C266" s="5"/>
       <c r="D266" s="6">
         <v>1899</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
       <c r="J266" s="5" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="K266" s="5"/>
       <c r="L266" s="8" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="M266" s="5"/>
       <c r="N266" s="5"/>
@@ -17316,12 +17385,12 @@
         <v>30</v>
       </c>
       <c r="S266" s="5" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="T266" s="3">
         <v>49</v>
       </c>
-      <c r="U266" s="3">
+      <c r="U266" s="46">
         <v>42</v>
       </c>
       <c r="V266" s="3">
@@ -17333,10 +17402,10 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C267" s="5"/>
       <c r="D267" s="6">
@@ -17346,17 +17415,17 @@
         <v>560</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
       <c r="I267" s="5"/>
       <c r="J267" s="5" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="K267" s="5"/>
       <c r="L267" s="8" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="M267" s="5"/>
       <c r="N267" s="5"/>
@@ -17372,7 +17441,7 @@
       <c r="T267" s="3">
         <v>59</v>
       </c>
-      <c r="U267" s="3">
+      <c r="U267" s="46">
         <v>36</v>
       </c>
       <c r="V267" s="3">
@@ -17384,30 +17453,30 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="29" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B268" s="29" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C268" s="29"/>
       <c r="D268" s="31">
         <v>1847</v>
       </c>
       <c r="E268" s="29" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="F268" s="29" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="G268" s="29"/>
       <c r="H268" s="29"/>
       <c r="I268" s="29"/>
       <c r="J268" s="29" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="K268" s="29"/>
       <c r="L268" s="30" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="M268" s="29"/>
       <c r="N268" s="29"/>
@@ -17423,10 +17492,10 @@
       <c r="T268" s="31">
         <v>208</v>
       </c>
-      <c r="U268" s="31">
+      <c r="U268" s="41">
         <v>120</v>
       </c>
-      <c r="V268" s="31">
+      <c r="V268" s="6">
         <v>126</v>
       </c>
       <c r="W268" s="31">
@@ -17435,30 +17504,30 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C269" s="5"/>
       <c r="D269" s="6">
         <v>1868</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
       <c r="J269" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="K269" s="5"/>
       <c r="L269" s="8" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="M269" s="5"/>
       <c r="N269" s="5"/>
@@ -17474,7 +17543,7 @@
       <c r="T269" s="6">
         <v>162</v>
       </c>
-      <c r="U269" s="6">
+      <c r="U269" s="39">
         <v>73</v>
       </c>
       <c r="V269" s="6">
@@ -17486,10 +17555,10 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C270" s="5"/>
       <c r="D270" s="6">
@@ -17505,11 +17574,11 @@
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
       <c r="J270" s="5" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="K270" s="5"/>
       <c r="L270" s="8" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="M270" s="5"/>
       <c r="N270" s="5"/>
@@ -17525,7 +17594,7 @@
       <c r="T270" s="6">
         <v>239</v>
       </c>
-      <c r="U270" s="6">
+      <c r="U270" s="39">
         <v>323</v>
       </c>
       <c r="V270" s="6">
@@ -17537,30 +17606,30 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C271" s="5"/>
       <c r="D271" s="6">
         <v>1856</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="G271" s="5"/>
       <c r="H271" s="5"/>
       <c r="I271" s="5"/>
       <c r="J271" s="5" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="K271" s="5"/>
       <c r="L271" s="8" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="M271" s="5"/>
       <c r="N271" s="5"/>
@@ -17576,7 +17645,7 @@
       <c r="T271" s="6">
         <v>220</v>
       </c>
-      <c r="U271" s="6">
+      <c r="U271" s="39">
         <v>90</v>
       </c>
       <c r="V271" s="6">
@@ -17588,30 +17657,30 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C272" s="5"/>
       <c r="D272" s="6">
         <v>1858</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G272" s="5"/>
       <c r="H272" s="5"/>
       <c r="I272" s="5"/>
       <c r="J272" s="5" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="K272" s="5"/>
       <c r="L272" s="8" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="M272" s="5"/>
       <c r="N272" s="5"/>
@@ -17627,7 +17696,7 @@
       <c r="T272" s="6">
         <v>220</v>
       </c>
-      <c r="U272" s="6">
+      <c r="U272" s="39">
         <v>90</v>
       </c>
       <c r="V272" s="6">
@@ -17639,30 +17708,30 @@
     </row>
     <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C273" s="5"/>
       <c r="D273" s="6">
         <v>1862</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G273" s="5"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5"/>
       <c r="J273" s="5" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="K273" s="5"/>
       <c r="L273" s="34" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="M273" s="5"/>
       <c r="N273" s="5"/>
@@ -17678,7 +17747,7 @@
       <c r="T273" s="6">
         <v>200</v>
       </c>
-      <c r="U273" s="6">
+      <c r="U273" s="39">
         <v>150</v>
       </c>
       <c r="V273" s="6">
@@ -17690,13 +17759,13 @@
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>154</v>
@@ -17705,10 +17774,10 @@
         <v>166</v>
       </c>
       <c r="J274" s="2" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="L274" s="10" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="R274" s="5" t="s">
         <v>30</v>
@@ -17719,7 +17788,7 @@
       <c r="T274" s="6">
         <v>105</v>
       </c>
-      <c r="U274" s="6">
+      <c r="U274" s="39">
         <v>68</v>
       </c>
       <c r="V274" s="6">
@@ -17731,42 +17800,42 @@
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D275" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G275" s="34" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I275" s="34" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L275" s="10" t="s">
         <v>1089</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="F275" s="2" t="s">
+      <c r="R275" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="S275" s="5" t="s">
         <v>1090</v>
-      </c>
-      <c r="G275" s="34" t="s">
-        <v>1175</v>
-      </c>
-      <c r="I275" s="34" t="s">
-        <v>1174</v>
-      </c>
-      <c r="J275" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="L275" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="R275" s="5" t="s">
-        <v>1173</v>
-      </c>
-      <c r="S275" s="5" t="s">
-        <v>1093</v>
       </c>
       <c r="T275" s="6">
         <v>900</v>
       </c>
-      <c r="U275" s="6">
+      <c r="U275" s="39">
         <v>2500</v>
       </c>
       <c r="W275" s="6">
@@ -17775,14 +17844,14 @@
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C276" s="5"/>
       <c r="D276" s="6" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="E276" s="5" t="s">
         <v>154</v>
@@ -17794,11 +17863,11 @@
       <c r="H276" s="5"/>
       <c r="I276" s="5"/>
       <c r="J276" s="5" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="K276" s="5"/>
       <c r="L276" s="8" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="M276" s="5"/>
       <c r="N276" s="5"/>
@@ -17814,7 +17883,7 @@
       <c r="T276" s="6">
         <v>183</v>
       </c>
-      <c r="U276" s="6">
+      <c r="U276" s="39">
         <v>67</v>
       </c>
       <c r="V276" s="6">
@@ -17826,30 +17895,30 @@
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C277" s="5"/>
       <c r="D277" s="6">
         <v>1897</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="G277" s="5"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
       <c r="J277" s="5" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="K277" s="5"/>
       <c r="L277" s="8" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="M277" s="5"/>
       <c r="N277" s="5"/>
@@ -17865,7 +17934,7 @@
       <c r="T277" s="6">
         <v>58</v>
       </c>
-      <c r="U277" s="6">
+      <c r="U277" s="39">
         <v>30</v>
       </c>
       <c r="V277" s="6">
@@ -17877,25 +17946,25 @@
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="L278" s="10" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="R278" s="5" t="s">
         <v>30</v>
@@ -17906,7 +17975,7 @@
       <c r="T278" s="6">
         <v>230</v>
       </c>
-      <c r="U278" s="6">
+      <c r="U278" s="39">
         <v>80</v>
       </c>
       <c r="V278" s="6">
@@ -17918,10 +17987,10 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C279" s="5"/>
       <c r="D279" s="6" t="s">
@@ -17931,17 +18000,17 @@
         <v>134</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G279" s="5"/>
       <c r="H279" s="5"/>
       <c r="I279" s="5"/>
       <c r="J279" s="5" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="K279" s="5"/>
       <c r="L279" s="8" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="M279" s="5"/>
       <c r="N279" s="5"/>
@@ -17957,7 +18026,7 @@
       <c r="T279" s="6">
         <v>32</v>
       </c>
-      <c r="U279" s="6">
+      <c r="U279" s="39">
         <v>28</v>
       </c>
       <c r="V279" s="6">
@@ -17969,30 +18038,30 @@
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C280" s="5"/>
       <c r="D280" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="G280" s="5"/>
       <c r="H280" s="5"/>
       <c r="I280" s="5"/>
       <c r="J280" s="5" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="K280" s="5"/>
       <c r="L280" s="8" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="M280" s="5"/>
       <c r="N280" s="5"/>
@@ -18008,7 +18077,7 @@
       <c r="T280" s="6">
         <v>240</v>
       </c>
-      <c r="U280" s="6">
+      <c r="U280" s="39">
         <v>100</v>
       </c>
       <c r="V280" s="6">
@@ -18020,30 +18089,30 @@
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C281" s="5"/>
       <c r="D281" s="6" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>319</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="G281" s="5"/>
       <c r="H281" s="5"/>
       <c r="I281" s="5"/>
       <c r="J281" s="5" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="K281" s="5"/>
       <c r="L281" s="8" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="M281" s="5"/>
       <c r="N281" s="5"/>
@@ -18059,7 +18128,7 @@
       <c r="T281" s="6">
         <v>260</v>
       </c>
-      <c r="U281" s="6">
+      <c r="U281" s="39">
         <v>130</v>
       </c>
       <c r="V281" s="6">
@@ -18071,14 +18140,14 @@
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C282" s="5"/>
       <c r="D282" s="6" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>73</v>
@@ -18090,11 +18159,11 @@
       <c r="H282" s="5"/>
       <c r="I282" s="5"/>
       <c r="J282" s="5" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="K282" s="5"/>
       <c r="L282" s="8" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="M282" s="5"/>
       <c r="N282" s="5"/>
@@ -18110,7 +18179,7 @@
       <c r="T282" s="6">
         <v>141</v>
       </c>
-      <c r="U282" s="6">
+      <c r="U282" s="39">
         <v>84</v>
       </c>
       <c r="V282" s="6">
@@ -18122,30 +18191,30 @@
     </row>
     <row r="283" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C283" s="5"/>
       <c r="D283" s="6" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>538</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="G283" s="5"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
       <c r="J283" s="5" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="K283" s="5"/>
       <c r="L283" s="8" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="M283" s="5"/>
       <c r="N283" s="5"/>
@@ -18161,7 +18230,7 @@
       <c r="T283" s="6">
         <v>150</v>
       </c>
-      <c r="U283" s="6">
+      <c r="U283" s="39">
         <v>130</v>
       </c>
       <c r="V283" s="6">
@@ -18173,14 +18242,14 @@
     </row>
     <row r="284" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C284" s="5"/>
       <c r="D284" s="6" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="E284" s="5" t="s">
         <v>73</v>
@@ -18192,11 +18261,11 @@
       <c r="H284" s="5"/>
       <c r="I284" s="5"/>
       <c r="J284" s="5" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="K284" s="5"/>
       <c r="L284" s="8" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="M284" s="5"/>
       <c r="N284" s="5"/>
@@ -18212,7 +18281,7 @@
       <c r="T284" s="6">
         <v>209</v>
       </c>
-      <c r="U284" s="6">
+      <c r="U284" s="39">
         <v>68</v>
       </c>
       <c r="V284" s="6">
@@ -18224,10 +18293,10 @@
     </row>
     <row r="285" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C285" s="5"/>
       <c r="D285" s="6" t="s">
@@ -18243,11 +18312,11 @@
       <c r="H285" s="5"/>
       <c r="I285" s="5"/>
       <c r="J285" s="5" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="K285" s="5"/>
       <c r="L285" s="8" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="M285" s="5"/>
       <c r="N285" s="5"/>
@@ -18263,7 +18332,7 @@
       <c r="T285" s="6">
         <v>135</v>
       </c>
-      <c r="U285" s="6">
+      <c r="U285" s="39">
         <v>70</v>
       </c>
       <c r="V285" s="6">
@@ -18278,7 +18347,7 @@
         <v>401</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>1128</v>
+        <v>1224</v>
       </c>
       <c r="C286" s="5"/>
       <c r="D286" s="6">
@@ -18288,17 +18357,17 @@
         <v>560</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G286" s="5"/>
       <c r="H286" s="5"/>
       <c r="I286" s="5"/>
       <c r="J286" s="5" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="K286" s="5"/>
       <c r="L286" s="8" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="M286" s="5"/>
       <c r="N286" s="5"/>
@@ -18314,7 +18383,7 @@
       <c r="T286" s="6">
         <v>72</v>
       </c>
-      <c r="U286" s="6">
+      <c r="U286" s="39">
         <v>50</v>
       </c>
       <c r="V286" s="6">
@@ -18329,7 +18398,7 @@
         <v>401</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>1128</v>
+        <v>1224</v>
       </c>
       <c r="C287" s="5"/>
       <c r="D287" s="6" t="s">
@@ -18339,17 +18408,17 @@
         <v>560</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
       <c r="I287" s="5"/>
       <c r="J287" s="5" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="K287" s="5"/>
       <c r="L287" s="8" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="M287" s="5"/>
       <c r="N287" s="5"/>
@@ -18365,7 +18434,7 @@
       <c r="T287" s="6">
         <v>260</v>
       </c>
-      <c r="U287" s="6">
+      <c r="U287" s="39">
         <v>100</v>
       </c>
       <c r="V287" s="6">
@@ -18380,27 +18449,27 @@
         <v>401</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>1128</v>
+        <v>1224</v>
       </c>
       <c r="C288" s="5"/>
       <c r="D288" s="6" t="s">
         <v>550</v>
       </c>
       <c r="E288" s="5" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="G288" s="5"/>
       <c r="H288" s="5"/>
       <c r="I288" s="5"/>
       <c r="J288" s="5" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="K288" s="5"/>
       <c r="L288" s="8" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="M288" s="5"/>
       <c r="N288" s="5"/>
@@ -18416,7 +18485,7 @@
       <c r="T288" s="6">
         <v>470</v>
       </c>
-      <c r="U288" s="6">
+      <c r="U288" s="39">
         <v>180</v>
       </c>
       <c r="V288" s="6">
@@ -18431,7 +18500,7 @@
         <v>401</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>1128</v>
+        <v>1224</v>
       </c>
       <c r="C289" s="5"/>
       <c r="D289" s="6">
@@ -18441,17 +18510,17 @@
         <v>560</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5"/>
       <c r="J289" s="5" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="K289" s="5"/>
       <c r="L289" s="8" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="M289" s="5"/>
       <c r="N289" s="5"/>
@@ -18467,7 +18536,7 @@
       <c r="T289" s="6">
         <v>175</v>
       </c>
-      <c r="U289" s="6">
+      <c r="U289" s="39">
         <v>90</v>
       </c>
       <c r="V289" s="6">
@@ -18686,7 +18755,7 @@
     <hyperlink ref="L207" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
     <hyperlink ref="L208" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
     <hyperlink ref="L209" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="L210" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="G210" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
     <hyperlink ref="L211" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
     <hyperlink ref="L212" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
     <hyperlink ref="L213" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
@@ -18793,6 +18862,7 @@
     <hyperlink ref="G94" r:id="rId311" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DF7BF212-7779-47A4-83B7-AF2917EECFFC}"/>
     <hyperlink ref="I49" r:id="rId312" xr:uid="{C89E209D-9483-4F74-AAF2-ED4B186D5B23}"/>
     <hyperlink ref="G49" r:id="rId313" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{537B7F22-4511-405B-B10F-9A6222040DED}"/>
+    <hyperlink ref="L210" r:id="rId314" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg/1280px-Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FC182F38-7808-4BE6-A1AF-73C1E69D109F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
